--- a/cypress/fixtures/CapJuntaDir.xlsx
+++ b/cypress/fixtures/CapJuntaDir.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Junta Directiva " sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Junta Directiva" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>

--- a/cypress/fixtures/CapJuntaDir.xlsx
+++ b/cypress/fixtures/CapJuntaDir.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>AuthPor</t>
   </si>
@@ -70,19 +70,16 @@
     <t>12/11/2026</t>
   </si>
   <si>
-    <t>Perez</t>
+    <t>Plata</t>
   </si>
   <si>
-    <t>Lopez</t>
+    <t>Juan</t>
   </si>
   <si>
     <t>Carlos</t>
   </si>
   <si>
-    <t>Roberto</t>
-  </si>
-  <si>
-    <t>Ismael</t>
+    <t>Pin</t>
   </si>
   <si>
     <t>Representante legal</t>
@@ -155,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -177,9 +174,15 @@
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -394,7 +397,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="4" max="4" width="10.88"/>
-    <col customWidth="1" min="5" max="5" width="14.75"/>
+    <col customWidth="1" min="5" max="5" width="15.63"/>
     <col customWidth="1" min="6" max="6" width="17.38"/>
     <col customWidth="1" min="7" max="7" width="9.25"/>
     <col customWidth="1" min="8" max="8" width="14.25"/>
@@ -472,8 +475,8 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 8))) &amp; ((RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 5)) + 1000) &amp; ""0"&amp;"0"""),"010119973404700")</f>
-        <v>010119973404700</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""),3))) &amp; ""2 "" &amp; (RIGHT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 10)) "),"0102 1997 33101")</f>
+        <v>0102 1997 33101</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>
@@ -481,23 +484,23 @@
       <c r="G2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -519,7 +522,7 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="9"/>
+      <c r="F3" s="10"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -547,7 +550,7 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="9"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -575,7 +578,7 @@
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="9"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
@@ -603,7 +606,7 @@
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="9"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -631,7 +634,7 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="9"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -659,7 +662,7 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="9"/>
+      <c r="F8" s="10"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -685,9 +688,9 @@
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="D9" s="11"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="9"/>
+      <c r="F9" s="10"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
@@ -715,7 +718,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="9"/>
+      <c r="F10" s="10"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -743,7 +746,7 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="9"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
@@ -771,7 +774,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="9"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
@@ -799,7 +802,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="9"/>
+      <c r="F13" s="10"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
@@ -827,7 +830,7 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="9"/>
+      <c r="F14" s="10"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -855,7 +858,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="9"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
@@ -883,7 +886,7 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="9"/>
+      <c r="F16" s="10"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
@@ -911,7 +914,7 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="9"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
@@ -939,7 +942,7 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="9"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -967,7 +970,7 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="9"/>
+      <c r="F19" s="10"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
@@ -995,7 +998,7 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="9"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -1023,7 +1026,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="9"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -1051,7 +1054,7 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="9"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -1079,7 +1082,7 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="9"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
@@ -1107,7 +1110,7 @@
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="9"/>
+      <c r="F24" s="10"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -1135,7 +1138,7 @@
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="9"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
@@ -1163,7 +1166,7 @@
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="9"/>
+      <c r="F26" s="10"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -1191,7 +1194,7 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="9"/>
+      <c r="F27" s="10"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
@@ -1219,7 +1222,7 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="9"/>
+      <c r="F28" s="10"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -1247,7 +1250,7 @@
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="9"/>
+      <c r="F29" s="10"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
@@ -1275,7 +1278,7 @@
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="9"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -1303,7 +1306,7 @@
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="9"/>
+      <c r="F31" s="10"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
@@ -1331,7 +1334,7 @@
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="9"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
@@ -1359,7 +1362,7 @@
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
-      <c r="F33" s="9"/>
+      <c r="F33" s="10"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
@@ -1387,7 +1390,7 @@
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
-      <c r="F34" s="9"/>
+      <c r="F34" s="10"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
@@ -1415,7 +1418,7 @@
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
-      <c r="F35" s="9"/>
+      <c r="F35" s="10"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
@@ -1443,7 +1446,7 @@
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
-      <c r="F36" s="9"/>
+      <c r="F36" s="10"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
@@ -1471,7 +1474,7 @@
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
-      <c r="F37" s="9"/>
+      <c r="F37" s="10"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
@@ -1499,7 +1502,7 @@
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
-      <c r="F38" s="9"/>
+      <c r="F38" s="10"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -1527,7 +1530,7 @@
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
-      <c r="F39" s="9"/>
+      <c r="F39" s="10"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
@@ -1555,7 +1558,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
-      <c r="F40" s="9"/>
+      <c r="F40" s="10"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -1583,7 +1586,7 @@
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
-      <c r="F41" s="9"/>
+      <c r="F41" s="10"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
@@ -1611,7 +1614,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="9"/>
+      <c r="F42" s="10"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
@@ -1639,7 +1642,7 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
-      <c r="F43" s="9"/>
+      <c r="F43" s="10"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
@@ -1667,7 +1670,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
-      <c r="F44" s="9"/>
+      <c r="F44" s="10"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
@@ -1695,7 +1698,7 @@
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
-      <c r="F45" s="9"/>
+      <c r="F45" s="10"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
@@ -1723,7 +1726,7 @@
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
-      <c r="F46" s="9"/>
+      <c r="F46" s="10"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
@@ -1751,7 +1754,7 @@
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
-      <c r="F47" s="9"/>
+      <c r="F47" s="10"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
@@ -1779,7 +1782,7 @@
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
-      <c r="F48" s="9"/>
+      <c r="F48" s="10"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
@@ -1807,7 +1810,7 @@
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
-      <c r="F49" s="9"/>
+      <c r="F49" s="10"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
@@ -1835,7 +1838,7 @@
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
-      <c r="F50" s="9"/>
+      <c r="F50" s="10"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
@@ -1863,7 +1866,7 @@
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
-      <c r="F51" s="9"/>
+      <c r="F51" s="10"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
@@ -1891,7 +1894,7 @@
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
-      <c r="F52" s="9"/>
+      <c r="F52" s="10"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
@@ -1919,7 +1922,7 @@
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
-      <c r="F53" s="9"/>
+      <c r="F53" s="10"/>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
@@ -1947,7 +1950,7 @@
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
-      <c r="F54" s="9"/>
+      <c r="F54" s="10"/>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
@@ -1975,7 +1978,7 @@
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
-      <c r="F55" s="9"/>
+      <c r="F55" s="10"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
@@ -2003,7 +2006,7 @@
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
-      <c r="F56" s="9"/>
+      <c r="F56" s="10"/>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
@@ -2031,7 +2034,7 @@
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
-      <c r="F57" s="9"/>
+      <c r="F57" s="10"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
@@ -2059,7 +2062,7 @@
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
-      <c r="F58" s="9"/>
+      <c r="F58" s="10"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
@@ -2087,7 +2090,7 @@
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
-      <c r="F59" s="9"/>
+      <c r="F59" s="10"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
@@ -2115,7 +2118,7 @@
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
-      <c r="F60" s="9"/>
+      <c r="F60" s="10"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
@@ -2143,7 +2146,7 @@
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
-      <c r="F61" s="9"/>
+      <c r="F61" s="10"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
@@ -2171,7 +2174,7 @@
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
-      <c r="F62" s="9"/>
+      <c r="F62" s="10"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
@@ -2199,7 +2202,7 @@
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
-      <c r="F63" s="9"/>
+      <c r="F63" s="10"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
@@ -2227,7 +2230,7 @@
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
-      <c r="F64" s="9"/>
+      <c r="F64" s="10"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
@@ -2255,7 +2258,7 @@
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
-      <c r="F65" s="9"/>
+      <c r="F65" s="10"/>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
@@ -2283,7 +2286,7 @@
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
-      <c r="F66" s="9"/>
+      <c r="F66" s="10"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
@@ -2311,7 +2314,7 @@
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
-      <c r="F67" s="9"/>
+      <c r="F67" s="10"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
@@ -2339,7 +2342,7 @@
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
-      <c r="F68" s="9"/>
+      <c r="F68" s="10"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
@@ -2367,7 +2370,7 @@
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
-      <c r="F69" s="9"/>
+      <c r="F69" s="10"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -2395,7 +2398,7 @@
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
-      <c r="F70" s="9"/>
+      <c r="F70" s="10"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
@@ -2423,7 +2426,7 @@
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
-      <c r="F71" s="9"/>
+      <c r="F71" s="10"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
@@ -2451,7 +2454,7 @@
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
-      <c r="F72" s="9"/>
+      <c r="F72" s="10"/>
       <c r="G72" s="6"/>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
@@ -2479,7 +2482,7 @@
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
-      <c r="F73" s="9"/>
+      <c r="F73" s="10"/>
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
@@ -2507,7 +2510,7 @@
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
-      <c r="F74" s="9"/>
+      <c r="F74" s="10"/>
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
@@ -2535,7 +2538,7 @@
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
-      <c r="F75" s="9"/>
+      <c r="F75" s="10"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
@@ -2563,7 +2566,7 @@
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
-      <c r="F76" s="9"/>
+      <c r="F76" s="10"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
@@ -2591,7 +2594,7 @@
       <c r="C77" s="6"/>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
-      <c r="F77" s="9"/>
+      <c r="F77" s="10"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
@@ -2619,7 +2622,7 @@
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
-      <c r="F78" s="9"/>
+      <c r="F78" s="10"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
@@ -2647,7 +2650,7 @@
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
-      <c r="F79" s="9"/>
+      <c r="F79" s="10"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
@@ -2675,7 +2678,7 @@
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
-      <c r="F80" s="9"/>
+      <c r="F80" s="10"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
@@ -2703,7 +2706,7 @@
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
-      <c r="F81" s="9"/>
+      <c r="F81" s="10"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
       <c r="I81" s="6"/>
@@ -2731,7 +2734,7 @@
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
-      <c r="F82" s="9"/>
+      <c r="F82" s="10"/>
       <c r="G82" s="6"/>
       <c r="H82" s="6"/>
       <c r="I82" s="6"/>
@@ -2759,7 +2762,7 @@
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
-      <c r="F83" s="9"/>
+      <c r="F83" s="10"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
@@ -2787,7 +2790,7 @@
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
-      <c r="F84" s="9"/>
+      <c r="F84" s="10"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
       <c r="I84" s="6"/>
@@ -2815,7 +2818,7 @@
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
-      <c r="F85" s="9"/>
+      <c r="F85" s="10"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
@@ -2843,7 +2846,7 @@
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
-      <c r="F86" s="9"/>
+      <c r="F86" s="10"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
@@ -2871,7 +2874,7 @@
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
-      <c r="F87" s="9"/>
+      <c r="F87" s="10"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
       <c r="I87" s="6"/>
@@ -2899,7 +2902,7 @@
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
-      <c r="F88" s="9"/>
+      <c r="F88" s="10"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
       <c r="I88" s="6"/>
@@ -2927,7 +2930,7 @@
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
-      <c r="F89" s="9"/>
+      <c r="F89" s="10"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
       <c r="I89" s="6"/>
@@ -2955,7 +2958,7 @@
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
-      <c r="F90" s="9"/>
+      <c r="F90" s="10"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
       <c r="I90" s="6"/>
@@ -2983,7 +2986,7 @@
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
-      <c r="F91" s="9"/>
+      <c r="F91" s="10"/>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
@@ -3011,7 +3014,7 @@
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
-      <c r="F92" s="9"/>
+      <c r="F92" s="10"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
@@ -3039,7 +3042,7 @@
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
-      <c r="F93" s="9"/>
+      <c r="F93" s="10"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
       <c r="I93" s="6"/>
@@ -3067,7 +3070,7 @@
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
-      <c r="F94" s="9"/>
+      <c r="F94" s="10"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
@@ -3095,7 +3098,7 @@
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
-      <c r="F95" s="9"/>
+      <c r="F95" s="10"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
@@ -3123,7 +3126,7 @@
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
-      <c r="F96" s="9"/>
+      <c r="F96" s="10"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
@@ -3151,7 +3154,7 @@
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
-      <c r="F97" s="9"/>
+      <c r="F97" s="10"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
@@ -3179,7 +3182,7 @@
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
-      <c r="F98" s="9"/>
+      <c r="F98" s="10"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
@@ -3207,7 +3210,7 @@
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
-      <c r="F99" s="9"/>
+      <c r="F99" s="10"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
       <c r="I99" s="6"/>
@@ -3235,7 +3238,7 @@
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
-      <c r="F100" s="9"/>
+      <c r="F100" s="10"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
       <c r="I100" s="6"/>
@@ -3263,7 +3266,7 @@
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
-      <c r="F101" s="9"/>
+      <c r="F101" s="10"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
@@ -3291,7 +3294,7 @@
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
-      <c r="F102" s="9"/>
+      <c r="F102" s="10"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
@@ -3319,7 +3322,7 @@
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
-      <c r="F103" s="9"/>
+      <c r="F103" s="10"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
       <c r="I103" s="6"/>
@@ -3347,7 +3350,7 @@
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
-      <c r="F104" s="9"/>
+      <c r="F104" s="10"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
@@ -3375,7 +3378,7 @@
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
-      <c r="F105" s="9"/>
+      <c r="F105" s="10"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
@@ -3403,7 +3406,7 @@
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
-      <c r="F106" s="9"/>
+      <c r="F106" s="10"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
@@ -3431,7 +3434,7 @@
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
-      <c r="F107" s="9"/>
+      <c r="F107" s="10"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
@@ -3459,7 +3462,7 @@
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
-      <c r="F108" s="9"/>
+      <c r="F108" s="10"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
@@ -3487,7 +3490,7 @@
       <c r="C109" s="6"/>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
-      <c r="F109" s="9"/>
+      <c r="F109" s="10"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
@@ -3515,7 +3518,7 @@
       <c r="C110" s="6"/>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
-      <c r="F110" s="9"/>
+      <c r="F110" s="10"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
@@ -3543,7 +3546,7 @@
       <c r="C111" s="6"/>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
-      <c r="F111" s="9"/>
+      <c r="F111" s="10"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
@@ -3571,7 +3574,7 @@
       <c r="C112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
-      <c r="F112" s="9"/>
+      <c r="F112" s="10"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
@@ -3599,7 +3602,7 @@
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
-      <c r="F113" s="9"/>
+      <c r="F113" s="10"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
@@ -3627,7 +3630,7 @@
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
-      <c r="F114" s="9"/>
+      <c r="F114" s="10"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
@@ -3655,7 +3658,7 @@
       <c r="C115" s="6"/>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
-      <c r="F115" s="9"/>
+      <c r="F115" s="10"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
@@ -3683,7 +3686,7 @@
       <c r="C116" s="6"/>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
-      <c r="F116" s="9"/>
+      <c r="F116" s="10"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
@@ -3711,7 +3714,7 @@
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
-      <c r="F117" s="9"/>
+      <c r="F117" s="10"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
@@ -3739,7 +3742,7 @@
       <c r="C118" s="6"/>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
-      <c r="F118" s="9"/>
+      <c r="F118" s="10"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
@@ -3767,7 +3770,7 @@
       <c r="C119" s="6"/>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
-      <c r="F119" s="9"/>
+      <c r="F119" s="10"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
@@ -3795,7 +3798,7 @@
       <c r="C120" s="6"/>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
-      <c r="F120" s="9"/>
+      <c r="F120" s="10"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
@@ -3823,7 +3826,7 @@
       <c r="C121" s="6"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
-      <c r="F121" s="9"/>
+      <c r="F121" s="10"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
@@ -3851,7 +3854,7 @@
       <c r="C122" s="6"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
-      <c r="F122" s="9"/>
+      <c r="F122" s="10"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
@@ -3879,7 +3882,7 @@
       <c r="C123" s="6"/>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
-      <c r="F123" s="9"/>
+      <c r="F123" s="10"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
@@ -3907,7 +3910,7 @@
       <c r="C124" s="6"/>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
-      <c r="F124" s="9"/>
+      <c r="F124" s="10"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
@@ -3935,7 +3938,7 @@
       <c r="C125" s="6"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
-      <c r="F125" s="9"/>
+      <c r="F125" s="10"/>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
@@ -3963,7 +3966,7 @@
       <c r="C126" s="6"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
-      <c r="F126" s="9"/>
+      <c r="F126" s="10"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
@@ -3991,7 +3994,7 @@
       <c r="C127" s="6"/>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
-      <c r="F127" s="9"/>
+      <c r="F127" s="10"/>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
@@ -4019,7 +4022,7 @@
       <c r="C128" s="6"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
-      <c r="F128" s="9"/>
+      <c r="F128" s="10"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
@@ -4047,7 +4050,7 @@
       <c r="C129" s="6"/>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
-      <c r="F129" s="9"/>
+      <c r="F129" s="10"/>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
@@ -4075,7 +4078,7 @@
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
-      <c r="F130" s="9"/>
+      <c r="F130" s="10"/>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
@@ -4103,7 +4106,7 @@
       <c r="C131" s="6"/>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
-      <c r="F131" s="9"/>
+      <c r="F131" s="10"/>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
@@ -4131,7 +4134,7 @@
       <c r="C132" s="6"/>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
-      <c r="F132" s="9"/>
+      <c r="F132" s="10"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
@@ -4159,7 +4162,7 @@
       <c r="C133" s="6"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
-      <c r="F133" s="9"/>
+      <c r="F133" s="10"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
@@ -4187,7 +4190,7 @@
       <c r="C134" s="6"/>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
-      <c r="F134" s="9"/>
+      <c r="F134" s="10"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
@@ -4215,7 +4218,7 @@
       <c r="C135" s="6"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
-      <c r="F135" s="9"/>
+      <c r="F135" s="10"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
@@ -4243,7 +4246,7 @@
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
-      <c r="F136" s="9"/>
+      <c r="F136" s="10"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
@@ -4271,7 +4274,7 @@
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
-      <c r="F137" s="9"/>
+      <c r="F137" s="10"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
@@ -4299,7 +4302,7 @@
       <c r="C138" s="6"/>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
-      <c r="F138" s="9"/>
+      <c r="F138" s="10"/>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
@@ -4327,7 +4330,7 @@
       <c r="C139" s="6"/>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
-      <c r="F139" s="9"/>
+      <c r="F139" s="10"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
@@ -4355,7 +4358,7 @@
       <c r="C140" s="6"/>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
-      <c r="F140" s="9"/>
+      <c r="F140" s="10"/>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
@@ -4383,7 +4386,7 @@
       <c r="C141" s="6"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
-      <c r="F141" s="9"/>
+      <c r="F141" s="10"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
@@ -4411,7 +4414,7 @@
       <c r="C142" s="6"/>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
-      <c r="F142" s="9"/>
+      <c r="F142" s="10"/>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
@@ -4439,7 +4442,7 @@
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
-      <c r="F143" s="9"/>
+      <c r="F143" s="10"/>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
@@ -4467,7 +4470,7 @@
       <c r="C144" s="6"/>
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
-      <c r="F144" s="9"/>
+      <c r="F144" s="10"/>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
       <c r="I144" s="6"/>
@@ -4495,7 +4498,7 @@
       <c r="C145" s="6"/>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
-      <c r="F145" s="9"/>
+      <c r="F145" s="10"/>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
@@ -4523,7 +4526,7 @@
       <c r="C146" s="6"/>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
-      <c r="F146" s="9"/>
+      <c r="F146" s="10"/>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
@@ -4551,7 +4554,7 @@
       <c r="C147" s="6"/>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
-      <c r="F147" s="9"/>
+      <c r="F147" s="10"/>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
@@ -4579,7 +4582,7 @@
       <c r="C148" s="6"/>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
-      <c r="F148" s="9"/>
+      <c r="F148" s="10"/>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
@@ -4607,7 +4610,7 @@
       <c r="C149" s="6"/>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
-      <c r="F149" s="9"/>
+      <c r="F149" s="10"/>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
@@ -4635,7 +4638,7 @@
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
-      <c r="F150" s="9"/>
+      <c r="F150" s="10"/>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
@@ -4663,7 +4666,7 @@
       <c r="C151" s="6"/>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
-      <c r="F151" s="9"/>
+      <c r="F151" s="10"/>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
@@ -4691,7 +4694,7 @@
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
-      <c r="F152" s="9"/>
+      <c r="F152" s="10"/>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
@@ -4719,7 +4722,7 @@
       <c r="C153" s="6"/>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
-      <c r="F153" s="9"/>
+      <c r="F153" s="10"/>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
@@ -4747,7 +4750,7 @@
       <c r="C154" s="6"/>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
-      <c r="F154" s="9"/>
+      <c r="F154" s="10"/>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
@@ -4775,7 +4778,7 @@
       <c r="C155" s="6"/>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
-      <c r="F155" s="9"/>
+      <c r="F155" s="10"/>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
       <c r="I155" s="6"/>
@@ -4803,7 +4806,7 @@
       <c r="C156" s="6"/>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
-      <c r="F156" s="9"/>
+      <c r="F156" s="10"/>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
       <c r="I156" s="6"/>
@@ -4831,7 +4834,7 @@
       <c r="C157" s="6"/>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
-      <c r="F157" s="9"/>
+      <c r="F157" s="10"/>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
       <c r="I157" s="6"/>
@@ -4859,7 +4862,7 @@
       <c r="C158" s="6"/>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
-      <c r="F158" s="9"/>
+      <c r="F158" s="10"/>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
@@ -4887,7 +4890,7 @@
       <c r="C159" s="6"/>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
-      <c r="F159" s="9"/>
+      <c r="F159" s="10"/>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
@@ -4915,7 +4918,7 @@
       <c r="C160" s="6"/>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
-      <c r="F160" s="9"/>
+      <c r="F160" s="10"/>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
@@ -4943,7 +4946,7 @@
       <c r="C161" s="6"/>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
-      <c r="F161" s="9"/>
+      <c r="F161" s="10"/>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
@@ -4971,7 +4974,7 @@
       <c r="C162" s="6"/>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
-      <c r="F162" s="9"/>
+      <c r="F162" s="10"/>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
@@ -4999,7 +5002,7 @@
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
-      <c r="F163" s="9"/>
+      <c r="F163" s="10"/>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
       <c r="I163" s="6"/>
@@ -5027,7 +5030,7 @@
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
-      <c r="F164" s="9"/>
+      <c r="F164" s="10"/>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
       <c r="I164" s="6"/>
@@ -5055,7 +5058,7 @@
       <c r="C165" s="6"/>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
-      <c r="F165" s="9"/>
+      <c r="F165" s="10"/>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
       <c r="I165" s="6"/>
@@ -5083,7 +5086,7 @@
       <c r="C166" s="6"/>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
-      <c r="F166" s="9"/>
+      <c r="F166" s="10"/>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
@@ -5111,7 +5114,7 @@
       <c r="C167" s="6"/>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
-      <c r="F167" s="9"/>
+      <c r="F167" s="10"/>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
@@ -5139,7 +5142,7 @@
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
-      <c r="F168" s="9"/>
+      <c r="F168" s="10"/>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
@@ -5167,7 +5170,7 @@
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
-      <c r="F169" s="9"/>
+      <c r="F169" s="10"/>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
@@ -5195,7 +5198,7 @@
       <c r="C170" s="6"/>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
-      <c r="F170" s="9"/>
+      <c r="F170" s="10"/>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
       <c r="I170" s="6"/>
@@ -5223,7 +5226,7 @@
       <c r="C171" s="6"/>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
-      <c r="F171" s="9"/>
+      <c r="F171" s="10"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="6"/>
@@ -5251,7 +5254,7 @@
       <c r="C172" s="6"/>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
-      <c r="F172" s="9"/>
+      <c r="F172" s="10"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
       <c r="I172" s="6"/>
@@ -5279,7 +5282,7 @@
       <c r="C173" s="6"/>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
-      <c r="F173" s="9"/>
+      <c r="F173" s="10"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
@@ -5307,7 +5310,7 @@
       <c r="C174" s="6"/>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
-      <c r="F174" s="9"/>
+      <c r="F174" s="10"/>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
       <c r="I174" s="6"/>
@@ -5335,7 +5338,7 @@
       <c r="C175" s="6"/>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
-      <c r="F175" s="9"/>
+      <c r="F175" s="10"/>
       <c r="G175" s="6"/>
       <c r="H175" s="6"/>
       <c r="I175" s="6"/>
@@ -5363,7 +5366,7 @@
       <c r="C176" s="6"/>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
-      <c r="F176" s="9"/>
+      <c r="F176" s="10"/>
       <c r="G176" s="6"/>
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
@@ -5391,7 +5394,7 @@
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
-      <c r="F177" s="9"/>
+      <c r="F177" s="10"/>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
@@ -5419,7 +5422,7 @@
       <c r="C178" s="6"/>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
-      <c r="F178" s="9"/>
+      <c r="F178" s="10"/>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
@@ -5447,7 +5450,7 @@
       <c r="C179" s="6"/>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
-      <c r="F179" s="9"/>
+      <c r="F179" s="10"/>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
       <c r="I179" s="6"/>
@@ -5475,7 +5478,7 @@
       <c r="C180" s="6"/>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
-      <c r="F180" s="9"/>
+      <c r="F180" s="10"/>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
       <c r="I180" s="6"/>
@@ -5503,7 +5506,7 @@
       <c r="C181" s="6"/>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
-      <c r="F181" s="9"/>
+      <c r="F181" s="10"/>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
@@ -5531,7 +5534,7 @@
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
-      <c r="F182" s="9"/>
+      <c r="F182" s="10"/>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
       <c r="I182" s="6"/>
@@ -5559,7 +5562,7 @@
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
-      <c r="F183" s="9"/>
+      <c r="F183" s="10"/>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
       <c r="I183" s="6"/>
@@ -5587,7 +5590,7 @@
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
-      <c r="F184" s="9"/>
+      <c r="F184" s="10"/>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
       <c r="I184" s="6"/>
@@ -5615,7 +5618,7 @@
       <c r="C185" s="6"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
-      <c r="F185" s="9"/>
+      <c r="F185" s="10"/>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
       <c r="I185" s="6"/>
@@ -5643,7 +5646,7 @@
       <c r="C186" s="6"/>
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
-      <c r="F186" s="9"/>
+      <c r="F186" s="10"/>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
       <c r="I186" s="6"/>
@@ -5671,7 +5674,7 @@
       <c r="C187" s="6"/>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="9"/>
+      <c r="F187" s="10"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
@@ -5699,7 +5702,7 @@
       <c r="C188" s="6"/>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="9"/>
+      <c r="F188" s="10"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
@@ -5727,7 +5730,7 @@
       <c r="C189" s="6"/>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
-      <c r="F189" s="9"/>
+      <c r="F189" s="10"/>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
@@ -5755,7 +5758,7 @@
       <c r="C190" s="6"/>
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
-      <c r="F190" s="9"/>
+      <c r="F190" s="10"/>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
@@ -5783,7 +5786,7 @@
       <c r="C191" s="6"/>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
-      <c r="F191" s="9"/>
+      <c r="F191" s="10"/>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
@@ -5811,7 +5814,7 @@
       <c r="C192" s="6"/>
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
-      <c r="F192" s="9"/>
+      <c r="F192" s="10"/>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
@@ -5839,7 +5842,7 @@
       <c r="C193" s="6"/>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
-      <c r="F193" s="9"/>
+      <c r="F193" s="10"/>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
@@ -5867,7 +5870,7 @@
       <c r="C194" s="6"/>
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
-      <c r="F194" s="9"/>
+      <c r="F194" s="10"/>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
@@ -5895,7 +5898,7 @@
       <c r="C195" s="6"/>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
-      <c r="F195" s="9"/>
+      <c r="F195" s="10"/>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
@@ -5923,7 +5926,7 @@
       <c r="C196" s="6"/>
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
-      <c r="F196" s="9"/>
+      <c r="F196" s="10"/>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
@@ -5951,7 +5954,7 @@
       <c r="C197" s="6"/>
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
-      <c r="F197" s="9"/>
+      <c r="F197" s="10"/>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
       <c r="I197" s="6"/>
@@ -5979,7 +5982,7 @@
       <c r="C198" s="6"/>
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
-      <c r="F198" s="9"/>
+      <c r="F198" s="10"/>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
       <c r="I198" s="6"/>
@@ -6007,7 +6010,7 @@
       <c r="C199" s="6"/>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
-      <c r="F199" s="9"/>
+      <c r="F199" s="10"/>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
       <c r="I199" s="6"/>
@@ -6035,7 +6038,7 @@
       <c r="C200" s="6"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
-      <c r="F200" s="9"/>
+      <c r="F200" s="10"/>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
       <c r="I200" s="6"/>
@@ -6063,7 +6066,7 @@
       <c r="C201" s="6"/>
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
-      <c r="F201" s="9"/>
+      <c r="F201" s="10"/>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
       <c r="I201" s="6"/>
@@ -6091,7 +6094,7 @@
       <c r="C202" s="6"/>
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
-      <c r="F202" s="9"/>
+      <c r="F202" s="10"/>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
       <c r="I202" s="6"/>
@@ -6119,7 +6122,7 @@
       <c r="C203" s="6"/>
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
-      <c r="F203" s="9"/>
+      <c r="F203" s="10"/>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
       <c r="I203" s="6"/>
@@ -6147,7 +6150,7 @@
       <c r="C204" s="6"/>
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
-      <c r="F204" s="9"/>
+      <c r="F204" s="10"/>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
       <c r="I204" s="6"/>
@@ -6175,7 +6178,7 @@
       <c r="C205" s="6"/>
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
-      <c r="F205" s="9"/>
+      <c r="F205" s="10"/>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
       <c r="I205" s="6"/>
@@ -6203,7 +6206,7 @@
       <c r="C206" s="6"/>
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
-      <c r="F206" s="9"/>
+      <c r="F206" s="10"/>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
       <c r="I206" s="6"/>
@@ -6231,7 +6234,7 @@
       <c r="C207" s="6"/>
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
-      <c r="F207" s="9"/>
+      <c r="F207" s="10"/>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
       <c r="I207" s="6"/>
@@ -6259,7 +6262,7 @@
       <c r="C208" s="6"/>
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
-      <c r="F208" s="9"/>
+      <c r="F208" s="10"/>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
       <c r="I208" s="6"/>
@@ -6287,7 +6290,7 @@
       <c r="C209" s="6"/>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
-      <c r="F209" s="9"/>
+      <c r="F209" s="10"/>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
       <c r="I209" s="6"/>
@@ -6315,7 +6318,7 @@
       <c r="C210" s="6"/>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
-      <c r="F210" s="9"/>
+      <c r="F210" s="10"/>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
       <c r="I210" s="6"/>
@@ -6343,7 +6346,7 @@
       <c r="C211" s="6"/>
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
-      <c r="F211" s="9"/>
+      <c r="F211" s="10"/>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
       <c r="I211" s="6"/>
@@ -6371,7 +6374,7 @@
       <c r="C212" s="6"/>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
-      <c r="F212" s="9"/>
+      <c r="F212" s="10"/>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
       <c r="I212" s="6"/>
@@ -6399,7 +6402,7 @@
       <c r="C213" s="6"/>
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
-      <c r="F213" s="9"/>
+      <c r="F213" s="10"/>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
       <c r="I213" s="6"/>
@@ -6427,7 +6430,7 @@
       <c r="C214" s="6"/>
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
-      <c r="F214" s="9"/>
+      <c r="F214" s="10"/>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
       <c r="I214" s="6"/>
@@ -6455,7 +6458,7 @@
       <c r="C215" s="6"/>
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
-      <c r="F215" s="9"/>
+      <c r="F215" s="10"/>
       <c r="G215" s="6"/>
       <c r="H215" s="6"/>
       <c r="I215" s="6"/>
@@ -6483,7 +6486,7 @@
       <c r="C216" s="6"/>
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
-      <c r="F216" s="9"/>
+      <c r="F216" s="10"/>
       <c r="G216" s="6"/>
       <c r="H216" s="6"/>
       <c r="I216" s="6"/>
@@ -6511,7 +6514,7 @@
       <c r="C217" s="6"/>
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
-      <c r="F217" s="9"/>
+      <c r="F217" s="10"/>
       <c r="G217" s="6"/>
       <c r="H217" s="6"/>
       <c r="I217" s="6"/>
@@ -6539,7 +6542,7 @@
       <c r="C218" s="6"/>
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
-      <c r="F218" s="9"/>
+      <c r="F218" s="10"/>
       <c r="G218" s="6"/>
       <c r="H218" s="6"/>
       <c r="I218" s="6"/>
@@ -6567,7 +6570,7 @@
       <c r="C219" s="6"/>
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
-      <c r="F219" s="9"/>
+      <c r="F219" s="10"/>
       <c r="G219" s="6"/>
       <c r="H219" s="6"/>
       <c r="I219" s="6"/>
@@ -6595,7 +6598,7 @@
       <c r="C220" s="6"/>
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
-      <c r="F220" s="9"/>
+      <c r="F220" s="10"/>
       <c r="G220" s="6"/>
       <c r="H220" s="6"/>
       <c r="I220" s="6"/>
@@ -6623,7 +6626,7 @@
       <c r="C221" s="6"/>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
-      <c r="F221" s="9"/>
+      <c r="F221" s="10"/>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
@@ -6651,7 +6654,7 @@
       <c r="C222" s="6"/>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
-      <c r="F222" s="9"/>
+      <c r="F222" s="10"/>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
       <c r="I222" s="6"/>
@@ -6679,7 +6682,7 @@
       <c r="C223" s="6"/>
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
-      <c r="F223" s="9"/>
+      <c r="F223" s="10"/>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
       <c r="I223" s="6"/>
@@ -6707,7 +6710,7 @@
       <c r="C224" s="6"/>
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
-      <c r="F224" s="9"/>
+      <c r="F224" s="10"/>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
       <c r="I224" s="6"/>
@@ -6735,7 +6738,7 @@
       <c r="C225" s="6"/>
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
-      <c r="F225" s="9"/>
+      <c r="F225" s="10"/>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
       <c r="I225" s="6"/>
@@ -6763,7 +6766,7 @@
       <c r="C226" s="6"/>
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
-      <c r="F226" s="9"/>
+      <c r="F226" s="10"/>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
       <c r="I226" s="6"/>
@@ -6791,7 +6794,7 @@
       <c r="C227" s="6"/>
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
-      <c r="F227" s="9"/>
+      <c r="F227" s="10"/>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
       <c r="I227" s="6"/>
@@ -6819,7 +6822,7 @@
       <c r="C228" s="6"/>
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
-      <c r="F228" s="9"/>
+      <c r="F228" s="10"/>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
       <c r="I228" s="6"/>
@@ -6847,7 +6850,7 @@
       <c r="C229" s="6"/>
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
-      <c r="F229" s="9"/>
+      <c r="F229" s="10"/>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
       <c r="I229" s="6"/>
@@ -6875,7 +6878,7 @@
       <c r="C230" s="6"/>
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
-      <c r="F230" s="9"/>
+      <c r="F230" s="10"/>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
       <c r="I230" s="6"/>
@@ -6903,7 +6906,7 @@
       <c r="C231" s="6"/>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
-      <c r="F231" s="9"/>
+      <c r="F231" s="10"/>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
       <c r="I231" s="6"/>
@@ -6931,7 +6934,7 @@
       <c r="C232" s="6"/>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
-      <c r="F232" s="9"/>
+      <c r="F232" s="10"/>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
       <c r="I232" s="6"/>
@@ -6959,7 +6962,7 @@
       <c r="C233" s="6"/>
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
-      <c r="F233" s="9"/>
+      <c r="F233" s="10"/>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
       <c r="I233" s="6"/>
@@ -6987,7 +6990,7 @@
       <c r="C234" s="6"/>
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
-      <c r="F234" s="9"/>
+      <c r="F234" s="10"/>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
       <c r="I234" s="6"/>
@@ -7015,7 +7018,7 @@
       <c r="C235" s="6"/>
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
-      <c r="F235" s="9"/>
+      <c r="F235" s="10"/>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
       <c r="I235" s="6"/>
@@ -7043,7 +7046,7 @@
       <c r="C236" s="6"/>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
-      <c r="F236" s="9"/>
+      <c r="F236" s="10"/>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
       <c r="I236" s="6"/>
@@ -7071,7 +7074,7 @@
       <c r="C237" s="6"/>
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
-      <c r="F237" s="9"/>
+      <c r="F237" s="10"/>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
       <c r="I237" s="6"/>
@@ -7099,7 +7102,7 @@
       <c r="C238" s="6"/>
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
-      <c r="F238" s="9"/>
+      <c r="F238" s="10"/>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
       <c r="I238" s="6"/>
@@ -7127,7 +7130,7 @@
       <c r="C239" s="6"/>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
-      <c r="F239" s="9"/>
+      <c r="F239" s="10"/>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
       <c r="I239" s="6"/>
@@ -7155,7 +7158,7 @@
       <c r="C240" s="6"/>
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
-      <c r="F240" s="9"/>
+      <c r="F240" s="10"/>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
       <c r="I240" s="6"/>
@@ -7183,7 +7186,7 @@
       <c r="C241" s="6"/>
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
-      <c r="F241" s="9"/>
+      <c r="F241" s="10"/>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
       <c r="I241" s="6"/>
@@ -7211,7 +7214,7 @@
       <c r="C242" s="6"/>
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
-      <c r="F242" s="9"/>
+      <c r="F242" s="10"/>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
       <c r="I242" s="6"/>
@@ -7239,7 +7242,7 @@
       <c r="C243" s="6"/>
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
-      <c r="F243" s="9"/>
+      <c r="F243" s="10"/>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
       <c r="I243" s="6"/>
@@ -7267,7 +7270,7 @@
       <c r="C244" s="6"/>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
-      <c r="F244" s="9"/>
+      <c r="F244" s="10"/>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
       <c r="I244" s="6"/>
@@ -7295,7 +7298,7 @@
       <c r="C245" s="6"/>
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
-      <c r="F245" s="9"/>
+      <c r="F245" s="10"/>
       <c r="G245" s="6"/>
       <c r="H245" s="6"/>
       <c r="I245" s="6"/>
@@ -7323,7 +7326,7 @@
       <c r="C246" s="6"/>
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
-      <c r="F246" s="9"/>
+      <c r="F246" s="10"/>
       <c r="G246" s="6"/>
       <c r="H246" s="6"/>
       <c r="I246" s="6"/>
@@ -7351,7 +7354,7 @@
       <c r="C247" s="6"/>
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
-      <c r="F247" s="9"/>
+      <c r="F247" s="10"/>
       <c r="G247" s="6"/>
       <c r="H247" s="6"/>
       <c r="I247" s="6"/>
@@ -7379,7 +7382,7 @@
       <c r="C248" s="6"/>
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
-      <c r="F248" s="9"/>
+      <c r="F248" s="10"/>
       <c r="G248" s="6"/>
       <c r="H248" s="6"/>
       <c r="I248" s="6"/>
@@ -7407,7 +7410,7 @@
       <c r="C249" s="6"/>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
-      <c r="F249" s="9"/>
+      <c r="F249" s="10"/>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
       <c r="I249" s="6"/>
@@ -7435,7 +7438,7 @@
       <c r="C250" s="6"/>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
-      <c r="F250" s="9"/>
+      <c r="F250" s="10"/>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
       <c r="I250" s="6"/>
@@ -7463,7 +7466,7 @@
       <c r="C251" s="6"/>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
-      <c r="F251" s="9"/>
+      <c r="F251" s="10"/>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
       <c r="I251" s="6"/>
@@ -7491,7 +7494,7 @@
       <c r="C252" s="6"/>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
-      <c r="F252" s="9"/>
+      <c r="F252" s="10"/>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
       <c r="I252" s="6"/>
@@ -7519,7 +7522,7 @@
       <c r="C253" s="6"/>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
-      <c r="F253" s="9"/>
+      <c r="F253" s="10"/>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
       <c r="I253" s="6"/>
@@ -7547,7 +7550,7 @@
       <c r="C254" s="6"/>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
-      <c r="F254" s="9"/>
+      <c r="F254" s="10"/>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
       <c r="I254" s="6"/>
@@ -7575,7 +7578,7 @@
       <c r="C255" s="6"/>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
-      <c r="F255" s="9"/>
+      <c r="F255" s="10"/>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
       <c r="I255" s="6"/>
@@ -7603,7 +7606,7 @@
       <c r="C256" s="6"/>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
-      <c r="F256" s="9"/>
+      <c r="F256" s="10"/>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
@@ -7631,7 +7634,7 @@
       <c r="C257" s="6"/>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
-      <c r="F257" s="9"/>
+      <c r="F257" s="10"/>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
       <c r="I257" s="6"/>
@@ -7659,7 +7662,7 @@
       <c r="C258" s="6"/>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
-      <c r="F258" s="9"/>
+      <c r="F258" s="10"/>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
       <c r="I258" s="6"/>
@@ -7687,7 +7690,7 @@
       <c r="C259" s="6"/>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
-      <c r="F259" s="9"/>
+      <c r="F259" s="10"/>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
       <c r="I259" s="6"/>
@@ -7715,7 +7718,7 @@
       <c r="C260" s="6"/>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
-      <c r="F260" s="9"/>
+      <c r="F260" s="10"/>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
       <c r="I260" s="6"/>
@@ -7743,7 +7746,7 @@
       <c r="C261" s="6"/>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
-      <c r="F261" s="9"/>
+      <c r="F261" s="10"/>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
       <c r="I261" s="6"/>
@@ -7771,7 +7774,7 @@
       <c r="C262" s="6"/>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
-      <c r="F262" s="9"/>
+      <c r="F262" s="10"/>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
       <c r="I262" s="6"/>
@@ -7799,7 +7802,7 @@
       <c r="C263" s="6"/>
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
-      <c r="F263" s="9"/>
+      <c r="F263" s="10"/>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
       <c r="I263" s="6"/>
@@ -7827,7 +7830,7 @@
       <c r="C264" s="6"/>
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
-      <c r="F264" s="9"/>
+      <c r="F264" s="10"/>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
       <c r="I264" s="6"/>
@@ -7855,7 +7858,7 @@
       <c r="C265" s="6"/>
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
-      <c r="F265" s="9"/>
+      <c r="F265" s="10"/>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
       <c r="I265" s="6"/>
@@ -7883,7 +7886,7 @@
       <c r="C266" s="6"/>
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
-      <c r="F266" s="9"/>
+      <c r="F266" s="10"/>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
       <c r="I266" s="6"/>
@@ -7911,7 +7914,7 @@
       <c r="C267" s="6"/>
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
-      <c r="F267" s="9"/>
+      <c r="F267" s="10"/>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
       <c r="I267" s="6"/>
@@ -7939,7 +7942,7 @@
       <c r="C268" s="6"/>
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
-      <c r="F268" s="9"/>
+      <c r="F268" s="10"/>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
       <c r="I268" s="6"/>
@@ -7967,7 +7970,7 @@
       <c r="C269" s="6"/>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
-      <c r="F269" s="9"/>
+      <c r="F269" s="10"/>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
       <c r="I269" s="6"/>
@@ -7995,7 +7998,7 @@
       <c r="C270" s="6"/>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
-      <c r="F270" s="9"/>
+      <c r="F270" s="10"/>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
       <c r="I270" s="6"/>
@@ -8023,7 +8026,7 @@
       <c r="C271" s="6"/>
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
-      <c r="F271" s="9"/>
+      <c r="F271" s="10"/>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
       <c r="I271" s="6"/>
@@ -8051,7 +8054,7 @@
       <c r="C272" s="6"/>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
-      <c r="F272" s="9"/>
+      <c r="F272" s="10"/>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
       <c r="I272" s="6"/>
@@ -8079,7 +8082,7 @@
       <c r="C273" s="6"/>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
-      <c r="F273" s="9"/>
+      <c r="F273" s="10"/>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
       <c r="I273" s="6"/>
@@ -8107,7 +8110,7 @@
       <c r="C274" s="6"/>
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
-      <c r="F274" s="9"/>
+      <c r="F274" s="10"/>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
       <c r="I274" s="6"/>
@@ -8135,7 +8138,7 @@
       <c r="C275" s="6"/>
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
-      <c r="F275" s="9"/>
+      <c r="F275" s="10"/>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
       <c r="I275" s="6"/>
@@ -8163,7 +8166,7 @@
       <c r="C276" s="6"/>
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
-      <c r="F276" s="9"/>
+      <c r="F276" s="10"/>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
       <c r="I276" s="6"/>
@@ -8191,7 +8194,7 @@
       <c r="C277" s="6"/>
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
-      <c r="F277" s="9"/>
+      <c r="F277" s="10"/>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
       <c r="I277" s="6"/>
@@ -8219,7 +8222,7 @@
       <c r="C278" s="6"/>
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
-      <c r="F278" s="9"/>
+      <c r="F278" s="10"/>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
       <c r="I278" s="6"/>
@@ -8247,7 +8250,7 @@
       <c r="C279" s="6"/>
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
-      <c r="F279" s="9"/>
+      <c r="F279" s="10"/>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
       <c r="I279" s="6"/>
@@ -8275,7 +8278,7 @@
       <c r="C280" s="6"/>
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
-      <c r="F280" s="9"/>
+      <c r="F280" s="10"/>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
       <c r="I280" s="6"/>
@@ -8303,7 +8306,7 @@
       <c r="C281" s="6"/>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
-      <c r="F281" s="9"/>
+      <c r="F281" s="10"/>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
       <c r="I281" s="6"/>
@@ -8331,7 +8334,7 @@
       <c r="C282" s="6"/>
       <c r="D282" s="6"/>
       <c r="E282" s="6"/>
-      <c r="F282" s="9"/>
+      <c r="F282" s="10"/>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
       <c r="I282" s="6"/>
@@ -8359,7 +8362,7 @@
       <c r="C283" s="6"/>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
-      <c r="F283" s="9"/>
+      <c r="F283" s="10"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
@@ -8387,7 +8390,7 @@
       <c r="C284" s="6"/>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
-      <c r="F284" s="9"/>
+      <c r="F284" s="10"/>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
@@ -8415,7 +8418,7 @@
       <c r="C285" s="6"/>
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
-      <c r="F285" s="9"/>
+      <c r="F285" s="10"/>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
       <c r="I285" s="6"/>
@@ -8443,7 +8446,7 @@
       <c r="C286" s="6"/>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
-      <c r="F286" s="9"/>
+      <c r="F286" s="10"/>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
       <c r="I286" s="6"/>
@@ -8471,7 +8474,7 @@
       <c r="C287" s="6"/>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
-      <c r="F287" s="9"/>
+      <c r="F287" s="10"/>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
       <c r="I287" s="6"/>
@@ -8499,7 +8502,7 @@
       <c r="C288" s="6"/>
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
-      <c r="F288" s="9"/>
+      <c r="F288" s="10"/>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
       <c r="I288" s="6"/>
@@ -8527,7 +8530,7 @@
       <c r="C289" s="6"/>
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
-      <c r="F289" s="9"/>
+      <c r="F289" s="10"/>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
       <c r="I289" s="6"/>
@@ -8555,7 +8558,7 @@
       <c r="C290" s="6"/>
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
-      <c r="F290" s="9"/>
+      <c r="F290" s="10"/>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
       <c r="I290" s="6"/>
@@ -8583,7 +8586,7 @@
       <c r="C291" s="6"/>
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
-      <c r="F291" s="9"/>
+      <c r="F291" s="10"/>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
       <c r="I291" s="6"/>
@@ -8611,7 +8614,7 @@
       <c r="C292" s="6"/>
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
-      <c r="F292" s="9"/>
+      <c r="F292" s="10"/>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
       <c r="I292" s="6"/>
@@ -8639,7 +8642,7 @@
       <c r="C293" s="6"/>
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
-      <c r="F293" s="9"/>
+      <c r="F293" s="10"/>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
       <c r="I293" s="6"/>
@@ -8667,7 +8670,7 @@
       <c r="C294" s="6"/>
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
-      <c r="F294" s="9"/>
+      <c r="F294" s="10"/>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
       <c r="I294" s="6"/>
@@ -8695,7 +8698,7 @@
       <c r="C295" s="6"/>
       <c r="D295" s="6"/>
       <c r="E295" s="6"/>
-      <c r="F295" s="9"/>
+      <c r="F295" s="10"/>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
       <c r="I295" s="6"/>
@@ -8723,7 +8726,7 @@
       <c r="C296" s="6"/>
       <c r="D296" s="6"/>
       <c r="E296" s="6"/>
-      <c r="F296" s="9"/>
+      <c r="F296" s="10"/>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
       <c r="I296" s="6"/>
@@ -8751,7 +8754,7 @@
       <c r="C297" s="6"/>
       <c r="D297" s="6"/>
       <c r="E297" s="6"/>
-      <c r="F297" s="9"/>
+      <c r="F297" s="10"/>
       <c r="G297" s="6"/>
       <c r="H297" s="6"/>
       <c r="I297" s="6"/>
@@ -8779,7 +8782,7 @@
       <c r="C298" s="6"/>
       <c r="D298" s="6"/>
       <c r="E298" s="6"/>
-      <c r="F298" s="9"/>
+      <c r="F298" s="10"/>
       <c r="G298" s="6"/>
       <c r="H298" s="6"/>
       <c r="I298" s="6"/>
@@ -8807,7 +8810,7 @@
       <c r="C299" s="6"/>
       <c r="D299" s="6"/>
       <c r="E299" s="6"/>
-      <c r="F299" s="9"/>
+      <c r="F299" s="10"/>
       <c r="G299" s="6"/>
       <c r="H299" s="6"/>
       <c r="I299" s="6"/>
@@ -8835,7 +8838,7 @@
       <c r="C300" s="6"/>
       <c r="D300" s="6"/>
       <c r="E300" s="6"/>
-      <c r="F300" s="9"/>
+      <c r="F300" s="10"/>
       <c r="G300" s="6"/>
       <c r="H300" s="6"/>
       <c r="I300" s="6"/>
@@ -8863,7 +8866,7 @@
       <c r="C301" s="6"/>
       <c r="D301" s="6"/>
       <c r="E301" s="6"/>
-      <c r="F301" s="9"/>
+      <c r="F301" s="10"/>
       <c r="G301" s="6"/>
       <c r="H301" s="6"/>
       <c r="I301" s="6"/>
@@ -8891,7 +8894,7 @@
       <c r="C302" s="6"/>
       <c r="D302" s="6"/>
       <c r="E302" s="6"/>
-      <c r="F302" s="9"/>
+      <c r="F302" s="10"/>
       <c r="G302" s="6"/>
       <c r="H302" s="6"/>
       <c r="I302" s="6"/>
@@ -8919,7 +8922,7 @@
       <c r="C303" s="6"/>
       <c r="D303" s="6"/>
       <c r="E303" s="6"/>
-      <c r="F303" s="9"/>
+      <c r="F303" s="10"/>
       <c r="G303" s="6"/>
       <c r="H303" s="6"/>
       <c r="I303" s="6"/>
@@ -8947,7 +8950,7 @@
       <c r="C304" s="6"/>
       <c r="D304" s="6"/>
       <c r="E304" s="6"/>
-      <c r="F304" s="9"/>
+      <c r="F304" s="10"/>
       <c r="G304" s="6"/>
       <c r="H304" s="6"/>
       <c r="I304" s="6"/>
@@ -8975,7 +8978,7 @@
       <c r="C305" s="6"/>
       <c r="D305" s="6"/>
       <c r="E305" s="6"/>
-      <c r="F305" s="9"/>
+      <c r="F305" s="10"/>
       <c r="G305" s="6"/>
       <c r="H305" s="6"/>
       <c r="I305" s="6"/>
@@ -9003,7 +9006,7 @@
       <c r="C306" s="6"/>
       <c r="D306" s="6"/>
       <c r="E306" s="6"/>
-      <c r="F306" s="9"/>
+      <c r="F306" s="10"/>
       <c r="G306" s="6"/>
       <c r="H306" s="6"/>
       <c r="I306" s="6"/>
@@ -9031,7 +9034,7 @@
       <c r="C307" s="6"/>
       <c r="D307" s="6"/>
       <c r="E307" s="6"/>
-      <c r="F307" s="9"/>
+      <c r="F307" s="10"/>
       <c r="G307" s="6"/>
       <c r="H307" s="6"/>
       <c r="I307" s="6"/>
@@ -9059,7 +9062,7 @@
       <c r="C308" s="6"/>
       <c r="D308" s="6"/>
       <c r="E308" s="6"/>
-      <c r="F308" s="9"/>
+      <c r="F308" s="10"/>
       <c r="G308" s="6"/>
       <c r="H308" s="6"/>
       <c r="I308" s="6"/>
@@ -9087,7 +9090,7 @@
       <c r="C309" s="6"/>
       <c r="D309" s="6"/>
       <c r="E309" s="6"/>
-      <c r="F309" s="9"/>
+      <c r="F309" s="10"/>
       <c r="G309" s="6"/>
       <c r="H309" s="6"/>
       <c r="I309" s="6"/>
@@ -9115,7 +9118,7 @@
       <c r="C310" s="6"/>
       <c r="D310" s="6"/>
       <c r="E310" s="6"/>
-      <c r="F310" s="9"/>
+      <c r="F310" s="10"/>
       <c r="G310" s="6"/>
       <c r="H310" s="6"/>
       <c r="I310" s="6"/>
@@ -9143,7 +9146,7 @@
       <c r="C311" s="6"/>
       <c r="D311" s="6"/>
       <c r="E311" s="6"/>
-      <c r="F311" s="9"/>
+      <c r="F311" s="10"/>
       <c r="G311" s="6"/>
       <c r="H311" s="6"/>
       <c r="I311" s="6"/>
@@ -9171,7 +9174,7 @@
       <c r="C312" s="6"/>
       <c r="D312" s="6"/>
       <c r="E312" s="6"/>
-      <c r="F312" s="9"/>
+      <c r="F312" s="10"/>
       <c r="G312" s="6"/>
       <c r="H312" s="6"/>
       <c r="I312" s="6"/>
@@ -9199,7 +9202,7 @@
       <c r="C313" s="6"/>
       <c r="D313" s="6"/>
       <c r="E313" s="6"/>
-      <c r="F313" s="9"/>
+      <c r="F313" s="10"/>
       <c r="G313" s="6"/>
       <c r="H313" s="6"/>
       <c r="I313" s="6"/>
@@ -9227,7 +9230,7 @@
       <c r="C314" s="6"/>
       <c r="D314" s="6"/>
       <c r="E314" s="6"/>
-      <c r="F314" s="9"/>
+      <c r="F314" s="10"/>
       <c r="G314" s="6"/>
       <c r="H314" s="6"/>
       <c r="I314" s="6"/>
@@ -9255,7 +9258,7 @@
       <c r="C315" s="6"/>
       <c r="D315" s="6"/>
       <c r="E315" s="6"/>
-      <c r="F315" s="9"/>
+      <c r="F315" s="10"/>
       <c r="G315" s="6"/>
       <c r="H315" s="6"/>
       <c r="I315" s="6"/>
@@ -9283,7 +9286,7 @@
       <c r="C316" s="6"/>
       <c r="D316" s="6"/>
       <c r="E316" s="6"/>
-      <c r="F316" s="9"/>
+      <c r="F316" s="10"/>
       <c r="G316" s="6"/>
       <c r="H316" s="6"/>
       <c r="I316" s="6"/>
@@ -9311,7 +9314,7 @@
       <c r="C317" s="6"/>
       <c r="D317" s="6"/>
       <c r="E317" s="6"/>
-      <c r="F317" s="9"/>
+      <c r="F317" s="10"/>
       <c r="G317" s="6"/>
       <c r="H317" s="6"/>
       <c r="I317" s="6"/>
@@ -9339,7 +9342,7 @@
       <c r="C318" s="6"/>
       <c r="D318" s="6"/>
       <c r="E318" s="6"/>
-      <c r="F318" s="9"/>
+      <c r="F318" s="10"/>
       <c r="G318" s="6"/>
       <c r="H318" s="6"/>
       <c r="I318" s="6"/>
@@ -9367,7 +9370,7 @@
       <c r="C319" s="6"/>
       <c r="D319" s="6"/>
       <c r="E319" s="6"/>
-      <c r="F319" s="9"/>
+      <c r="F319" s="10"/>
       <c r="G319" s="6"/>
       <c r="H319" s="6"/>
       <c r="I319" s="6"/>
@@ -9395,7 +9398,7 @@
       <c r="C320" s="6"/>
       <c r="D320" s="6"/>
       <c r="E320" s="6"/>
-      <c r="F320" s="9"/>
+      <c r="F320" s="10"/>
       <c r="G320" s="6"/>
       <c r="H320" s="6"/>
       <c r="I320" s="6"/>
@@ -9423,7 +9426,7 @@
       <c r="C321" s="6"/>
       <c r="D321" s="6"/>
       <c r="E321" s="6"/>
-      <c r="F321" s="9"/>
+      <c r="F321" s="10"/>
       <c r="G321" s="6"/>
       <c r="H321" s="6"/>
       <c r="I321" s="6"/>
@@ -9451,7 +9454,7 @@
       <c r="C322" s="6"/>
       <c r="D322" s="6"/>
       <c r="E322" s="6"/>
-      <c r="F322" s="9"/>
+      <c r="F322" s="10"/>
       <c r="G322" s="6"/>
       <c r="H322" s="6"/>
       <c r="I322" s="6"/>
@@ -9479,7 +9482,7 @@
       <c r="C323" s="6"/>
       <c r="D323" s="6"/>
       <c r="E323" s="6"/>
-      <c r="F323" s="9"/>
+      <c r="F323" s="10"/>
       <c r="G323" s="6"/>
       <c r="H323" s="6"/>
       <c r="I323" s="6"/>
@@ -9507,7 +9510,7 @@
       <c r="C324" s="6"/>
       <c r="D324" s="6"/>
       <c r="E324" s="6"/>
-      <c r="F324" s="9"/>
+      <c r="F324" s="10"/>
       <c r="G324" s="6"/>
       <c r="H324" s="6"/>
       <c r="I324" s="6"/>
@@ -9535,7 +9538,7 @@
       <c r="C325" s="6"/>
       <c r="D325" s="6"/>
       <c r="E325" s="6"/>
-      <c r="F325" s="9"/>
+      <c r="F325" s="10"/>
       <c r="G325" s="6"/>
       <c r="H325" s="6"/>
       <c r="I325" s="6"/>
@@ -9563,7 +9566,7 @@
       <c r="C326" s="6"/>
       <c r="D326" s="6"/>
       <c r="E326" s="6"/>
-      <c r="F326" s="9"/>
+      <c r="F326" s="10"/>
       <c r="G326" s="6"/>
       <c r="H326" s="6"/>
       <c r="I326" s="6"/>
@@ -9591,7 +9594,7 @@
       <c r="C327" s="6"/>
       <c r="D327" s="6"/>
       <c r="E327" s="6"/>
-      <c r="F327" s="9"/>
+      <c r="F327" s="10"/>
       <c r="G327" s="6"/>
       <c r="H327" s="6"/>
       <c r="I327" s="6"/>
@@ -9619,7 +9622,7 @@
       <c r="C328" s="6"/>
       <c r="D328" s="6"/>
       <c r="E328" s="6"/>
-      <c r="F328" s="9"/>
+      <c r="F328" s="10"/>
       <c r="G328" s="6"/>
       <c r="H328" s="6"/>
       <c r="I328" s="6"/>
@@ -9647,7 +9650,7 @@
       <c r="C329" s="6"/>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
-      <c r="F329" s="9"/>
+      <c r="F329" s="10"/>
       <c r="G329" s="6"/>
       <c r="H329" s="6"/>
       <c r="I329" s="6"/>
@@ -9675,7 +9678,7 @@
       <c r="C330" s="6"/>
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
-      <c r="F330" s="9"/>
+      <c r="F330" s="10"/>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
       <c r="I330" s="6"/>
@@ -9703,7 +9706,7 @@
       <c r="C331" s="6"/>
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
-      <c r="F331" s="9"/>
+      <c r="F331" s="10"/>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
       <c r="I331" s="6"/>
@@ -9731,7 +9734,7 @@
       <c r="C332" s="6"/>
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
-      <c r="F332" s="9"/>
+      <c r="F332" s="10"/>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
       <c r="I332" s="6"/>
@@ -9759,7 +9762,7 @@
       <c r="C333" s="6"/>
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
-      <c r="F333" s="9"/>
+      <c r="F333" s="10"/>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
       <c r="I333" s="6"/>
@@ -9787,7 +9790,7 @@
       <c r="C334" s="6"/>
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
-      <c r="F334" s="9"/>
+      <c r="F334" s="10"/>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
       <c r="I334" s="6"/>
@@ -9815,7 +9818,7 @@
       <c r="C335" s="6"/>
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
-      <c r="F335" s="9"/>
+      <c r="F335" s="10"/>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
       <c r="I335" s="6"/>
@@ -9843,7 +9846,7 @@
       <c r="C336" s="6"/>
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
-      <c r="F336" s="9"/>
+      <c r="F336" s="10"/>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
       <c r="I336" s="6"/>
@@ -9871,7 +9874,7 @@
       <c r="C337" s="6"/>
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
-      <c r="F337" s="9"/>
+      <c r="F337" s="10"/>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
       <c r="I337" s="6"/>
@@ -9899,7 +9902,7 @@
       <c r="C338" s="6"/>
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
-      <c r="F338" s="9"/>
+      <c r="F338" s="10"/>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
       <c r="I338" s="6"/>
@@ -9927,7 +9930,7 @@
       <c r="C339" s="6"/>
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
-      <c r="F339" s="9"/>
+      <c r="F339" s="10"/>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
       <c r="I339" s="6"/>
@@ -9955,7 +9958,7 @@
       <c r="C340" s="6"/>
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
-      <c r="F340" s="9"/>
+      <c r="F340" s="10"/>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
       <c r="I340" s="6"/>
@@ -9983,7 +9986,7 @@
       <c r="C341" s="6"/>
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
-      <c r="F341" s="9"/>
+      <c r="F341" s="10"/>
       <c r="G341" s="6"/>
       <c r="H341" s="6"/>
       <c r="I341" s="6"/>
@@ -10011,7 +10014,7 @@
       <c r="C342" s="6"/>
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
-      <c r="F342" s="9"/>
+      <c r="F342" s="10"/>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
       <c r="I342" s="6"/>
@@ -10039,7 +10042,7 @@
       <c r="C343" s="6"/>
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
-      <c r="F343" s="9"/>
+      <c r="F343" s="10"/>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
       <c r="I343" s="6"/>
@@ -10067,7 +10070,7 @@
       <c r="C344" s="6"/>
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
-      <c r="F344" s="9"/>
+      <c r="F344" s="10"/>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
       <c r="I344" s="6"/>
@@ -10095,7 +10098,7 @@
       <c r="C345" s="6"/>
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
-      <c r="F345" s="9"/>
+      <c r="F345" s="10"/>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
       <c r="I345" s="6"/>
@@ -10123,7 +10126,7 @@
       <c r="C346" s="6"/>
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
-      <c r="F346" s="9"/>
+      <c r="F346" s="10"/>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
       <c r="I346" s="6"/>
@@ -10151,7 +10154,7 @@
       <c r="C347" s="6"/>
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
-      <c r="F347" s="9"/>
+      <c r="F347" s="10"/>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
       <c r="I347" s="6"/>
@@ -10179,7 +10182,7 @@
       <c r="C348" s="6"/>
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
-      <c r="F348" s="9"/>
+      <c r="F348" s="10"/>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
       <c r="I348" s="6"/>
@@ -10207,7 +10210,7 @@
       <c r="C349" s="6"/>
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
-      <c r="F349" s="9"/>
+      <c r="F349" s="10"/>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
       <c r="I349" s="6"/>
@@ -10235,7 +10238,7 @@
       <c r="C350" s="6"/>
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
-      <c r="F350" s="9"/>
+      <c r="F350" s="10"/>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
       <c r="I350" s="6"/>
@@ -10263,7 +10266,7 @@
       <c r="C351" s="6"/>
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
-      <c r="F351" s="9"/>
+      <c r="F351" s="10"/>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
       <c r="I351" s="6"/>
@@ -10291,7 +10294,7 @@
       <c r="C352" s="6"/>
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
-      <c r="F352" s="9"/>
+      <c r="F352" s="10"/>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
       <c r="I352" s="6"/>
@@ -10319,7 +10322,7 @@
       <c r="C353" s="6"/>
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
-      <c r="F353" s="9"/>
+      <c r="F353" s="10"/>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
       <c r="I353" s="6"/>
@@ -10347,7 +10350,7 @@
       <c r="C354" s="6"/>
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
-      <c r="F354" s="9"/>
+      <c r="F354" s="10"/>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
       <c r="I354" s="6"/>
@@ -10375,7 +10378,7 @@
       <c r="C355" s="6"/>
       <c r="D355" s="6"/>
       <c r="E355" s="6"/>
-      <c r="F355" s="9"/>
+      <c r="F355" s="10"/>
       <c r="G355" s="6"/>
       <c r="H355" s="6"/>
       <c r="I355" s="6"/>
@@ -10403,7 +10406,7 @@
       <c r="C356" s="6"/>
       <c r="D356" s="6"/>
       <c r="E356" s="6"/>
-      <c r="F356" s="9"/>
+      <c r="F356" s="10"/>
       <c r="G356" s="6"/>
       <c r="H356" s="6"/>
       <c r="I356" s="6"/>
@@ -10431,7 +10434,7 @@
       <c r="C357" s="6"/>
       <c r="D357" s="6"/>
       <c r="E357" s="6"/>
-      <c r="F357" s="9"/>
+      <c r="F357" s="10"/>
       <c r="G357" s="6"/>
       <c r="H357" s="6"/>
       <c r="I357" s="6"/>
@@ -10459,7 +10462,7 @@
       <c r="C358" s="6"/>
       <c r="D358" s="6"/>
       <c r="E358" s="6"/>
-      <c r="F358" s="9"/>
+      <c r="F358" s="10"/>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
       <c r="I358" s="6"/>
@@ -10487,7 +10490,7 @@
       <c r="C359" s="6"/>
       <c r="D359" s="6"/>
       <c r="E359" s="6"/>
-      <c r="F359" s="9"/>
+      <c r="F359" s="10"/>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
       <c r="I359" s="6"/>
@@ -10515,7 +10518,7 @@
       <c r="C360" s="6"/>
       <c r="D360" s="6"/>
       <c r="E360" s="6"/>
-      <c r="F360" s="9"/>
+      <c r="F360" s="10"/>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
       <c r="I360" s="6"/>
@@ -10543,7 +10546,7 @@
       <c r="C361" s="6"/>
       <c r="D361" s="6"/>
       <c r="E361" s="6"/>
-      <c r="F361" s="9"/>
+      <c r="F361" s="10"/>
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
       <c r="I361" s="6"/>
@@ -10571,7 +10574,7 @@
       <c r="C362" s="6"/>
       <c r="D362" s="6"/>
       <c r="E362" s="6"/>
-      <c r="F362" s="9"/>
+      <c r="F362" s="10"/>
       <c r="G362" s="6"/>
       <c r="H362" s="6"/>
       <c r="I362" s="6"/>
@@ -10599,7 +10602,7 @@
       <c r="C363" s="6"/>
       <c r="D363" s="6"/>
       <c r="E363" s="6"/>
-      <c r="F363" s="9"/>
+      <c r="F363" s="10"/>
       <c r="G363" s="6"/>
       <c r="H363" s="6"/>
       <c r="I363" s="6"/>
@@ -10627,7 +10630,7 @@
       <c r="C364" s="6"/>
       <c r="D364" s="6"/>
       <c r="E364" s="6"/>
-      <c r="F364" s="9"/>
+      <c r="F364" s="10"/>
       <c r="G364" s="6"/>
       <c r="H364" s="6"/>
       <c r="I364" s="6"/>
@@ -10655,7 +10658,7 @@
       <c r="C365" s="6"/>
       <c r="D365" s="6"/>
       <c r="E365" s="6"/>
-      <c r="F365" s="9"/>
+      <c r="F365" s="10"/>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
       <c r="I365" s="6"/>
@@ -10683,7 +10686,7 @@
       <c r="C366" s="6"/>
       <c r="D366" s="6"/>
       <c r="E366" s="6"/>
-      <c r="F366" s="9"/>
+      <c r="F366" s="10"/>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
       <c r="I366" s="6"/>
@@ -10711,7 +10714,7 @@
       <c r="C367" s="6"/>
       <c r="D367" s="6"/>
       <c r="E367" s="6"/>
-      <c r="F367" s="9"/>
+      <c r="F367" s="10"/>
       <c r="G367" s="6"/>
       <c r="H367" s="6"/>
       <c r="I367" s="6"/>
@@ -10739,7 +10742,7 @@
       <c r="C368" s="6"/>
       <c r="D368" s="6"/>
       <c r="E368" s="6"/>
-      <c r="F368" s="9"/>
+      <c r="F368" s="10"/>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
       <c r="I368" s="6"/>
@@ -10767,7 +10770,7 @@
       <c r="C369" s="6"/>
       <c r="D369" s="6"/>
       <c r="E369" s="6"/>
-      <c r="F369" s="9"/>
+      <c r="F369" s="10"/>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
       <c r="I369" s="6"/>
@@ -10795,7 +10798,7 @@
       <c r="C370" s="6"/>
       <c r="D370" s="6"/>
       <c r="E370" s="6"/>
-      <c r="F370" s="9"/>
+      <c r="F370" s="10"/>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
       <c r="I370" s="6"/>
@@ -10823,7 +10826,7 @@
       <c r="C371" s="6"/>
       <c r="D371" s="6"/>
       <c r="E371" s="6"/>
-      <c r="F371" s="9"/>
+      <c r="F371" s="10"/>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
       <c r="I371" s="6"/>
@@ -10851,7 +10854,7 @@
       <c r="C372" s="6"/>
       <c r="D372" s="6"/>
       <c r="E372" s="6"/>
-      <c r="F372" s="9"/>
+      <c r="F372" s="10"/>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
       <c r="I372" s="6"/>
@@ -10879,7 +10882,7 @@
       <c r="C373" s="6"/>
       <c r="D373" s="6"/>
       <c r="E373" s="6"/>
-      <c r="F373" s="9"/>
+      <c r="F373" s="10"/>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
       <c r="I373" s="6"/>
@@ -10907,7 +10910,7 @@
       <c r="C374" s="6"/>
       <c r="D374" s="6"/>
       <c r="E374" s="6"/>
-      <c r="F374" s="9"/>
+      <c r="F374" s="10"/>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
       <c r="I374" s="6"/>
@@ -10935,7 +10938,7 @@
       <c r="C375" s="6"/>
       <c r="D375" s="6"/>
       <c r="E375" s="6"/>
-      <c r="F375" s="9"/>
+      <c r="F375" s="10"/>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
       <c r="I375" s="6"/>
@@ -10963,7 +10966,7 @@
       <c r="C376" s="6"/>
       <c r="D376" s="6"/>
       <c r="E376" s="6"/>
-      <c r="F376" s="9"/>
+      <c r="F376" s="10"/>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
       <c r="I376" s="6"/>
@@ -10991,7 +10994,7 @@
       <c r="C377" s="6"/>
       <c r="D377" s="6"/>
       <c r="E377" s="6"/>
-      <c r="F377" s="9"/>
+      <c r="F377" s="10"/>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
       <c r="I377" s="6"/>
@@ -11019,7 +11022,7 @@
       <c r="C378" s="6"/>
       <c r="D378" s="6"/>
       <c r="E378" s="6"/>
-      <c r="F378" s="9"/>
+      <c r="F378" s="10"/>
       <c r="G378" s="6"/>
       <c r="H378" s="6"/>
       <c r="I378" s="6"/>
@@ -11047,7 +11050,7 @@
       <c r="C379" s="6"/>
       <c r="D379" s="6"/>
       <c r="E379" s="6"/>
-      <c r="F379" s="9"/>
+      <c r="F379" s="10"/>
       <c r="G379" s="6"/>
       <c r="H379" s="6"/>
       <c r="I379" s="6"/>
@@ -11075,7 +11078,7 @@
       <c r="C380" s="6"/>
       <c r="D380" s="6"/>
       <c r="E380" s="6"/>
-      <c r="F380" s="9"/>
+      <c r="F380" s="10"/>
       <c r="G380" s="6"/>
       <c r="H380" s="6"/>
       <c r="I380" s="6"/>
@@ -11103,7 +11106,7 @@
       <c r="C381" s="6"/>
       <c r="D381" s="6"/>
       <c r="E381" s="6"/>
-      <c r="F381" s="9"/>
+      <c r="F381" s="10"/>
       <c r="G381" s="6"/>
       <c r="H381" s="6"/>
       <c r="I381" s="6"/>
@@ -11131,7 +11134,7 @@
       <c r="C382" s="6"/>
       <c r="D382" s="6"/>
       <c r="E382" s="6"/>
-      <c r="F382" s="9"/>
+      <c r="F382" s="10"/>
       <c r="G382" s="6"/>
       <c r="H382" s="6"/>
       <c r="I382" s="6"/>
@@ -11159,7 +11162,7 @@
       <c r="C383" s="6"/>
       <c r="D383" s="6"/>
       <c r="E383" s="6"/>
-      <c r="F383" s="9"/>
+      <c r="F383" s="10"/>
       <c r="G383" s="6"/>
       <c r="H383" s="6"/>
       <c r="I383" s="6"/>
@@ -11187,7 +11190,7 @@
       <c r="C384" s="6"/>
       <c r="D384" s="6"/>
       <c r="E384" s="6"/>
-      <c r="F384" s="9"/>
+      <c r="F384" s="10"/>
       <c r="G384" s="6"/>
       <c r="H384" s="6"/>
       <c r="I384" s="6"/>
@@ -11215,7 +11218,7 @@
       <c r="C385" s="6"/>
       <c r="D385" s="6"/>
       <c r="E385" s="6"/>
-      <c r="F385" s="9"/>
+      <c r="F385" s="10"/>
       <c r="G385" s="6"/>
       <c r="H385" s="6"/>
       <c r="I385" s="6"/>
@@ -11243,7 +11246,7 @@
       <c r="C386" s="6"/>
       <c r="D386" s="6"/>
       <c r="E386" s="6"/>
-      <c r="F386" s="9"/>
+      <c r="F386" s="10"/>
       <c r="G386" s="6"/>
       <c r="H386" s="6"/>
       <c r="I386" s="6"/>
@@ -11271,7 +11274,7 @@
       <c r="C387" s="6"/>
       <c r="D387" s="6"/>
       <c r="E387" s="6"/>
-      <c r="F387" s="9"/>
+      <c r="F387" s="10"/>
       <c r="G387" s="6"/>
       <c r="H387" s="6"/>
       <c r="I387" s="6"/>
@@ -11299,7 +11302,7 @@
       <c r="C388" s="6"/>
       <c r="D388" s="6"/>
       <c r="E388" s="6"/>
-      <c r="F388" s="9"/>
+      <c r="F388" s="10"/>
       <c r="G388" s="6"/>
       <c r="H388" s="6"/>
       <c r="I388" s="6"/>
@@ -11327,7 +11330,7 @@
       <c r="C389" s="6"/>
       <c r="D389" s="6"/>
       <c r="E389" s="6"/>
-      <c r="F389" s="9"/>
+      <c r="F389" s="10"/>
       <c r="G389" s="6"/>
       <c r="H389" s="6"/>
       <c r="I389" s="6"/>
@@ -11355,7 +11358,7 @@
       <c r="C390" s="6"/>
       <c r="D390" s="6"/>
       <c r="E390" s="6"/>
-      <c r="F390" s="9"/>
+      <c r="F390" s="10"/>
       <c r="G390" s="6"/>
       <c r="H390" s="6"/>
       <c r="I390" s="6"/>
@@ -11383,7 +11386,7 @@
       <c r="C391" s="6"/>
       <c r="D391" s="6"/>
       <c r="E391" s="6"/>
-      <c r="F391" s="9"/>
+      <c r="F391" s="10"/>
       <c r="G391" s="6"/>
       <c r="H391" s="6"/>
       <c r="I391" s="6"/>
@@ -11411,7 +11414,7 @@
       <c r="C392" s="6"/>
       <c r="D392" s="6"/>
       <c r="E392" s="6"/>
-      <c r="F392" s="9"/>
+      <c r="F392" s="10"/>
       <c r="G392" s="6"/>
       <c r="H392" s="6"/>
       <c r="I392" s="6"/>
@@ -11439,7 +11442,7 @@
       <c r="C393" s="6"/>
       <c r="D393" s="6"/>
       <c r="E393" s="6"/>
-      <c r="F393" s="9"/>
+      <c r="F393" s="10"/>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
       <c r="I393" s="6"/>
@@ -11467,7 +11470,7 @@
       <c r="C394" s="6"/>
       <c r="D394" s="6"/>
       <c r="E394" s="6"/>
-      <c r="F394" s="9"/>
+      <c r="F394" s="10"/>
       <c r="G394" s="6"/>
       <c r="H394" s="6"/>
       <c r="I394" s="6"/>
@@ -11495,7 +11498,7 @@
       <c r="C395" s="6"/>
       <c r="D395" s="6"/>
       <c r="E395" s="6"/>
-      <c r="F395" s="9"/>
+      <c r="F395" s="10"/>
       <c r="G395" s="6"/>
       <c r="H395" s="6"/>
       <c r="I395" s="6"/>
@@ -11523,7 +11526,7 @@
       <c r="C396" s="6"/>
       <c r="D396" s="6"/>
       <c r="E396" s="6"/>
-      <c r="F396" s="9"/>
+      <c r="F396" s="10"/>
       <c r="G396" s="6"/>
       <c r="H396" s="6"/>
       <c r="I396" s="6"/>
@@ -11551,7 +11554,7 @@
       <c r="C397" s="6"/>
       <c r="D397" s="6"/>
       <c r="E397" s="6"/>
-      <c r="F397" s="9"/>
+      <c r="F397" s="10"/>
       <c r="G397" s="6"/>
       <c r="H397" s="6"/>
       <c r="I397" s="6"/>
@@ -11579,7 +11582,7 @@
       <c r="C398" s="6"/>
       <c r="D398" s="6"/>
       <c r="E398" s="6"/>
-      <c r="F398" s="9"/>
+      <c r="F398" s="10"/>
       <c r="G398" s="6"/>
       <c r="H398" s="6"/>
       <c r="I398" s="6"/>
@@ -11607,7 +11610,7 @@
       <c r="C399" s="6"/>
       <c r="D399" s="6"/>
       <c r="E399" s="6"/>
-      <c r="F399" s="9"/>
+      <c r="F399" s="10"/>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
       <c r="I399" s="6"/>
@@ -11635,7 +11638,7 @@
       <c r="C400" s="6"/>
       <c r="D400" s="6"/>
       <c r="E400" s="6"/>
-      <c r="F400" s="9"/>
+      <c r="F400" s="10"/>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
       <c r="I400" s="6"/>
@@ -11663,7 +11666,7 @@
       <c r="C401" s="6"/>
       <c r="D401" s="6"/>
       <c r="E401" s="6"/>
-      <c r="F401" s="9"/>
+      <c r="F401" s="10"/>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
       <c r="I401" s="6"/>
@@ -11691,7 +11694,7 @@
       <c r="C402" s="6"/>
       <c r="D402" s="6"/>
       <c r="E402" s="6"/>
-      <c r="F402" s="9"/>
+      <c r="F402" s="10"/>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
       <c r="I402" s="6"/>
@@ -11719,7 +11722,7 @@
       <c r="C403" s="6"/>
       <c r="D403" s="6"/>
       <c r="E403" s="6"/>
-      <c r="F403" s="9"/>
+      <c r="F403" s="10"/>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
       <c r="I403" s="6"/>
@@ -11747,7 +11750,7 @@
       <c r="C404" s="6"/>
       <c r="D404" s="6"/>
       <c r="E404" s="6"/>
-      <c r="F404" s="9"/>
+      <c r="F404" s="10"/>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
       <c r="I404" s="6"/>
@@ -11775,7 +11778,7 @@
       <c r="C405" s="6"/>
       <c r="D405" s="6"/>
       <c r="E405" s="6"/>
-      <c r="F405" s="9"/>
+      <c r="F405" s="10"/>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
       <c r="I405" s="6"/>
@@ -11803,7 +11806,7 @@
       <c r="C406" s="6"/>
       <c r="D406" s="6"/>
       <c r="E406" s="6"/>
-      <c r="F406" s="9"/>
+      <c r="F406" s="10"/>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
       <c r="I406" s="6"/>
@@ -11831,7 +11834,7 @@
       <c r="C407" s="6"/>
       <c r="D407" s="6"/>
       <c r="E407" s="6"/>
-      <c r="F407" s="9"/>
+      <c r="F407" s="10"/>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
       <c r="I407" s="6"/>
@@ -11859,7 +11862,7 @@
       <c r="C408" s="6"/>
       <c r="D408" s="6"/>
       <c r="E408" s="6"/>
-      <c r="F408" s="9"/>
+      <c r="F408" s="10"/>
       <c r="G408" s="6"/>
       <c r="H408" s="6"/>
       <c r="I408" s="6"/>
@@ -11887,7 +11890,7 @@
       <c r="C409" s="6"/>
       <c r="D409" s="6"/>
       <c r="E409" s="6"/>
-      <c r="F409" s="9"/>
+      <c r="F409" s="10"/>
       <c r="G409" s="6"/>
       <c r="H409" s="6"/>
       <c r="I409" s="6"/>
@@ -11915,7 +11918,7 @@
       <c r="C410" s="6"/>
       <c r="D410" s="6"/>
       <c r="E410" s="6"/>
-      <c r="F410" s="9"/>
+      <c r="F410" s="10"/>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
       <c r="I410" s="6"/>
@@ -11943,7 +11946,7 @@
       <c r="C411" s="6"/>
       <c r="D411" s="6"/>
       <c r="E411" s="6"/>
-      <c r="F411" s="9"/>
+      <c r="F411" s="10"/>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
       <c r="I411" s="6"/>
@@ -11971,7 +11974,7 @@
       <c r="C412" s="6"/>
       <c r="D412" s="6"/>
       <c r="E412" s="6"/>
-      <c r="F412" s="9"/>
+      <c r="F412" s="10"/>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
       <c r="I412" s="6"/>
@@ -11999,7 +12002,7 @@
       <c r="C413" s="6"/>
       <c r="D413" s="6"/>
       <c r="E413" s="6"/>
-      <c r="F413" s="9"/>
+      <c r="F413" s="10"/>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
       <c r="I413" s="6"/>
@@ -12027,7 +12030,7 @@
       <c r="C414" s="6"/>
       <c r="D414" s="6"/>
       <c r="E414" s="6"/>
-      <c r="F414" s="9"/>
+      <c r="F414" s="10"/>
       <c r="G414" s="6"/>
       <c r="H414" s="6"/>
       <c r="I414" s="6"/>
@@ -12055,7 +12058,7 @@
       <c r="C415" s="6"/>
       <c r="D415" s="6"/>
       <c r="E415" s="6"/>
-      <c r="F415" s="9"/>
+      <c r="F415" s="10"/>
       <c r="G415" s="6"/>
       <c r="H415" s="6"/>
       <c r="I415" s="6"/>
@@ -12083,7 +12086,7 @@
       <c r="C416" s="6"/>
       <c r="D416" s="6"/>
       <c r="E416" s="6"/>
-      <c r="F416" s="9"/>
+      <c r="F416" s="10"/>
       <c r="G416" s="6"/>
       <c r="H416" s="6"/>
       <c r="I416" s="6"/>
@@ -12111,7 +12114,7 @@
       <c r="C417" s="6"/>
       <c r="D417" s="6"/>
       <c r="E417" s="6"/>
-      <c r="F417" s="9"/>
+      <c r="F417" s="10"/>
       <c r="G417" s="6"/>
       <c r="H417" s="6"/>
       <c r="I417" s="6"/>
@@ -12139,7 +12142,7 @@
       <c r="C418" s="6"/>
       <c r="D418" s="6"/>
       <c r="E418" s="6"/>
-      <c r="F418" s="9"/>
+      <c r="F418" s="10"/>
       <c r="G418" s="6"/>
       <c r="H418" s="6"/>
       <c r="I418" s="6"/>
@@ -12167,7 +12170,7 @@
       <c r="C419" s="6"/>
       <c r="D419" s="6"/>
       <c r="E419" s="6"/>
-      <c r="F419" s="9"/>
+      <c r="F419" s="10"/>
       <c r="G419" s="6"/>
       <c r="H419" s="6"/>
       <c r="I419" s="6"/>
@@ -12195,7 +12198,7 @@
       <c r="C420" s="6"/>
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
-      <c r="F420" s="9"/>
+      <c r="F420" s="10"/>
       <c r="G420" s="6"/>
       <c r="H420" s="6"/>
       <c r="I420" s="6"/>
@@ -12223,7 +12226,7 @@
       <c r="C421" s="6"/>
       <c r="D421" s="6"/>
       <c r="E421" s="6"/>
-      <c r="F421" s="9"/>
+      <c r="F421" s="10"/>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
       <c r="I421" s="6"/>
@@ -12251,7 +12254,7 @@
       <c r="C422" s="6"/>
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
-      <c r="F422" s="9"/>
+      <c r="F422" s="10"/>
       <c r="G422" s="6"/>
       <c r="H422" s="6"/>
       <c r="I422" s="6"/>
@@ -12279,7 +12282,7 @@
       <c r="C423" s="6"/>
       <c r="D423" s="6"/>
       <c r="E423" s="6"/>
-      <c r="F423" s="9"/>
+      <c r="F423" s="10"/>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
       <c r="I423" s="6"/>
@@ -12307,7 +12310,7 @@
       <c r="C424" s="6"/>
       <c r="D424" s="6"/>
       <c r="E424" s="6"/>
-      <c r="F424" s="9"/>
+      <c r="F424" s="10"/>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
       <c r="I424" s="6"/>
@@ -12335,7 +12338,7 @@
       <c r="C425" s="6"/>
       <c r="D425" s="6"/>
       <c r="E425" s="6"/>
-      <c r="F425" s="9"/>
+      <c r="F425" s="10"/>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
       <c r="I425" s="6"/>
@@ -12363,7 +12366,7 @@
       <c r="C426" s="6"/>
       <c r="D426" s="6"/>
       <c r="E426" s="6"/>
-      <c r="F426" s="9"/>
+      <c r="F426" s="10"/>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
       <c r="I426" s="6"/>
@@ -12391,7 +12394,7 @@
       <c r="C427" s="6"/>
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
-      <c r="F427" s="9"/>
+      <c r="F427" s="10"/>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
       <c r="I427" s="6"/>
@@ -12419,7 +12422,7 @@
       <c r="C428" s="6"/>
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
-      <c r="F428" s="9"/>
+      <c r="F428" s="10"/>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
       <c r="I428" s="6"/>
@@ -12447,7 +12450,7 @@
       <c r="C429" s="6"/>
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
-      <c r="F429" s="9"/>
+      <c r="F429" s="10"/>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
       <c r="I429" s="6"/>
@@ -12475,7 +12478,7 @@
       <c r="C430" s="6"/>
       <c r="D430" s="6"/>
       <c r="E430" s="6"/>
-      <c r="F430" s="9"/>
+      <c r="F430" s="10"/>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
       <c r="I430" s="6"/>
@@ -12503,7 +12506,7 @@
       <c r="C431" s="6"/>
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
-      <c r="F431" s="9"/>
+      <c r="F431" s="10"/>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
       <c r="I431" s="6"/>
@@ -12531,7 +12534,7 @@
       <c r="C432" s="6"/>
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
-      <c r="F432" s="9"/>
+      <c r="F432" s="10"/>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
       <c r="I432" s="6"/>
@@ -12559,7 +12562,7 @@
       <c r="C433" s="6"/>
       <c r="D433" s="6"/>
       <c r="E433" s="6"/>
-      <c r="F433" s="9"/>
+      <c r="F433" s="10"/>
       <c r="G433" s="6"/>
       <c r="H433" s="6"/>
       <c r="I433" s="6"/>
@@ -12587,7 +12590,7 @@
       <c r="C434" s="6"/>
       <c r="D434" s="6"/>
       <c r="E434" s="6"/>
-      <c r="F434" s="9"/>
+      <c r="F434" s="10"/>
       <c r="G434" s="6"/>
       <c r="H434" s="6"/>
       <c r="I434" s="6"/>
@@ -12615,7 +12618,7 @@
       <c r="C435" s="6"/>
       <c r="D435" s="6"/>
       <c r="E435" s="6"/>
-      <c r="F435" s="9"/>
+      <c r="F435" s="10"/>
       <c r="G435" s="6"/>
       <c r="H435" s="6"/>
       <c r="I435" s="6"/>
@@ -12643,7 +12646,7 @@
       <c r="C436" s="6"/>
       <c r="D436" s="6"/>
       <c r="E436" s="6"/>
-      <c r="F436" s="9"/>
+      <c r="F436" s="10"/>
       <c r="G436" s="6"/>
       <c r="H436" s="6"/>
       <c r="I436" s="6"/>
@@ -12671,7 +12674,7 @@
       <c r="C437" s="6"/>
       <c r="D437" s="6"/>
       <c r="E437" s="6"/>
-      <c r="F437" s="9"/>
+      <c r="F437" s="10"/>
       <c r="G437" s="6"/>
       <c r="H437" s="6"/>
       <c r="I437" s="6"/>
@@ -12699,7 +12702,7 @@
       <c r="C438" s="6"/>
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
-      <c r="F438" s="9"/>
+      <c r="F438" s="10"/>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
       <c r="I438" s="6"/>
@@ -12727,7 +12730,7 @@
       <c r="C439" s="6"/>
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
-      <c r="F439" s="9"/>
+      <c r="F439" s="10"/>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
       <c r="I439" s="6"/>
@@ -12755,7 +12758,7 @@
       <c r="C440" s="6"/>
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
-      <c r="F440" s="9"/>
+      <c r="F440" s="10"/>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
       <c r="I440" s="6"/>
@@ -12783,7 +12786,7 @@
       <c r="C441" s="6"/>
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
-      <c r="F441" s="9"/>
+      <c r="F441" s="10"/>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
       <c r="I441" s="6"/>
@@ -12811,7 +12814,7 @@
       <c r="C442" s="6"/>
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
-      <c r="F442" s="9"/>
+      <c r="F442" s="10"/>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
       <c r="I442" s="6"/>
@@ -12839,7 +12842,7 @@
       <c r="C443" s="6"/>
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
-      <c r="F443" s="9"/>
+      <c r="F443" s="10"/>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
       <c r="I443" s="6"/>
@@ -12867,7 +12870,7 @@
       <c r="C444" s="6"/>
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
-      <c r="F444" s="9"/>
+      <c r="F444" s="10"/>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
       <c r="I444" s="6"/>
@@ -12895,7 +12898,7 @@
       <c r="C445" s="6"/>
       <c r="D445" s="6"/>
       <c r="E445" s="6"/>
-      <c r="F445" s="9"/>
+      <c r="F445" s="10"/>
       <c r="G445" s="6"/>
       <c r="H445" s="6"/>
       <c r="I445" s="6"/>
@@ -12923,7 +12926,7 @@
       <c r="C446" s="6"/>
       <c r="D446" s="6"/>
       <c r="E446" s="6"/>
-      <c r="F446" s="9"/>
+      <c r="F446" s="10"/>
       <c r="G446" s="6"/>
       <c r="H446" s="6"/>
       <c r="I446" s="6"/>
@@ -12951,7 +12954,7 @@
       <c r="C447" s="6"/>
       <c r="D447" s="6"/>
       <c r="E447" s="6"/>
-      <c r="F447" s="9"/>
+      <c r="F447" s="10"/>
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
       <c r="I447" s="6"/>
@@ -12979,7 +12982,7 @@
       <c r="C448" s="6"/>
       <c r="D448" s="6"/>
       <c r="E448" s="6"/>
-      <c r="F448" s="9"/>
+      <c r="F448" s="10"/>
       <c r="G448" s="6"/>
       <c r="H448" s="6"/>
       <c r="I448" s="6"/>
@@ -13007,7 +13010,7 @@
       <c r="C449" s="6"/>
       <c r="D449" s="6"/>
       <c r="E449" s="6"/>
-      <c r="F449" s="9"/>
+      <c r="F449" s="10"/>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
       <c r="I449" s="6"/>
@@ -13035,7 +13038,7 @@
       <c r="C450" s="6"/>
       <c r="D450" s="6"/>
       <c r="E450" s="6"/>
-      <c r="F450" s="9"/>
+      <c r="F450" s="10"/>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
       <c r="I450" s="6"/>
@@ -13063,7 +13066,7 @@
       <c r="C451" s="6"/>
       <c r="D451" s="6"/>
       <c r="E451" s="6"/>
-      <c r="F451" s="9"/>
+      <c r="F451" s="10"/>
       <c r="G451" s="6"/>
       <c r="H451" s="6"/>
       <c r="I451" s="6"/>
@@ -13091,7 +13094,7 @@
       <c r="C452" s="6"/>
       <c r="D452" s="6"/>
       <c r="E452" s="6"/>
-      <c r="F452" s="9"/>
+      <c r="F452" s="10"/>
       <c r="G452" s="6"/>
       <c r="H452" s="6"/>
       <c r="I452" s="6"/>
@@ -13119,7 +13122,7 @@
       <c r="C453" s="6"/>
       <c r="D453" s="6"/>
       <c r="E453" s="6"/>
-      <c r="F453" s="9"/>
+      <c r="F453" s="10"/>
       <c r="G453" s="6"/>
       <c r="H453" s="6"/>
       <c r="I453" s="6"/>
@@ -13147,7 +13150,7 @@
       <c r="C454" s="6"/>
       <c r="D454" s="6"/>
       <c r="E454" s="6"/>
-      <c r="F454" s="9"/>
+      <c r="F454" s="10"/>
       <c r="G454" s="6"/>
       <c r="H454" s="6"/>
       <c r="I454" s="6"/>
@@ -13175,7 +13178,7 @@
       <c r="C455" s="6"/>
       <c r="D455" s="6"/>
       <c r="E455" s="6"/>
-      <c r="F455" s="9"/>
+      <c r="F455" s="10"/>
       <c r="G455" s="6"/>
       <c r="H455" s="6"/>
       <c r="I455" s="6"/>
@@ -13203,7 +13206,7 @@
       <c r="C456" s="6"/>
       <c r="D456" s="6"/>
       <c r="E456" s="6"/>
-      <c r="F456" s="9"/>
+      <c r="F456" s="10"/>
       <c r="G456" s="6"/>
       <c r="H456" s="6"/>
       <c r="I456" s="6"/>
@@ -13231,7 +13234,7 @@
       <c r="C457" s="6"/>
       <c r="D457" s="6"/>
       <c r="E457" s="6"/>
-      <c r="F457" s="9"/>
+      <c r="F457" s="10"/>
       <c r="G457" s="6"/>
       <c r="H457" s="6"/>
       <c r="I457" s="6"/>
@@ -13259,7 +13262,7 @@
       <c r="C458" s="6"/>
       <c r="D458" s="6"/>
       <c r="E458" s="6"/>
-      <c r="F458" s="9"/>
+      <c r="F458" s="10"/>
       <c r="G458" s="6"/>
       <c r="H458" s="6"/>
       <c r="I458" s="6"/>
@@ -13287,7 +13290,7 @@
       <c r="C459" s="6"/>
       <c r="D459" s="6"/>
       <c r="E459" s="6"/>
-      <c r="F459" s="9"/>
+      <c r="F459" s="10"/>
       <c r="G459" s="6"/>
       <c r="H459" s="6"/>
       <c r="I459" s="6"/>
@@ -13315,7 +13318,7 @@
       <c r="C460" s="6"/>
       <c r="D460" s="6"/>
       <c r="E460" s="6"/>
-      <c r="F460" s="9"/>
+      <c r="F460" s="10"/>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
       <c r="I460" s="6"/>
@@ -13343,7 +13346,7 @@
       <c r="C461" s="6"/>
       <c r="D461" s="6"/>
       <c r="E461" s="6"/>
-      <c r="F461" s="9"/>
+      <c r="F461" s="10"/>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
       <c r="I461" s="6"/>
@@ -13371,7 +13374,7 @@
       <c r="C462" s="6"/>
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
-      <c r="F462" s="9"/>
+      <c r="F462" s="10"/>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
       <c r="I462" s="6"/>
@@ -13399,7 +13402,7 @@
       <c r="C463" s="6"/>
       <c r="D463" s="6"/>
       <c r="E463" s="6"/>
-      <c r="F463" s="9"/>
+      <c r="F463" s="10"/>
       <c r="G463" s="6"/>
       <c r="H463" s="6"/>
       <c r="I463" s="6"/>
@@ -13427,7 +13430,7 @@
       <c r="C464" s="6"/>
       <c r="D464" s="6"/>
       <c r="E464" s="6"/>
-      <c r="F464" s="9"/>
+      <c r="F464" s="10"/>
       <c r="G464" s="6"/>
       <c r="H464" s="6"/>
       <c r="I464" s="6"/>
@@ -13455,7 +13458,7 @@
       <c r="C465" s="6"/>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
-      <c r="F465" s="9"/>
+      <c r="F465" s="10"/>
       <c r="G465" s="6"/>
       <c r="H465" s="6"/>
       <c r="I465" s="6"/>
@@ -13483,7 +13486,7 @@
       <c r="C466" s="6"/>
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
-      <c r="F466" s="9"/>
+      <c r="F466" s="10"/>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
       <c r="I466" s="6"/>
@@ -13511,7 +13514,7 @@
       <c r="C467" s="6"/>
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
-      <c r="F467" s="9"/>
+      <c r="F467" s="10"/>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
       <c r="I467" s="6"/>
@@ -13539,7 +13542,7 @@
       <c r="C468" s="6"/>
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
-      <c r="F468" s="9"/>
+      <c r="F468" s="10"/>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
       <c r="I468" s="6"/>
@@ -13567,7 +13570,7 @@
       <c r="C469" s="6"/>
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
-      <c r="F469" s="9"/>
+      <c r="F469" s="10"/>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
       <c r="I469" s="6"/>
@@ -13595,7 +13598,7 @@
       <c r="C470" s="6"/>
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
-      <c r="F470" s="9"/>
+      <c r="F470" s="10"/>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
       <c r="I470" s="6"/>
@@ -13623,7 +13626,7 @@
       <c r="C471" s="6"/>
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
-      <c r="F471" s="9"/>
+      <c r="F471" s="10"/>
       <c r="G471" s="6"/>
       <c r="H471" s="6"/>
       <c r="I471" s="6"/>
@@ -13651,7 +13654,7 @@
       <c r="C472" s="6"/>
       <c r="D472" s="6"/>
       <c r="E472" s="6"/>
-      <c r="F472" s="9"/>
+      <c r="F472" s="10"/>
       <c r="G472" s="6"/>
       <c r="H472" s="6"/>
       <c r="I472" s="6"/>
@@ -13679,7 +13682,7 @@
       <c r="C473" s="6"/>
       <c r="D473" s="6"/>
       <c r="E473" s="6"/>
-      <c r="F473" s="9"/>
+      <c r="F473" s="10"/>
       <c r="G473" s="6"/>
       <c r="H473" s="6"/>
       <c r="I473" s="6"/>
@@ -13707,7 +13710,7 @@
       <c r="C474" s="6"/>
       <c r="D474" s="6"/>
       <c r="E474" s="6"/>
-      <c r="F474" s="9"/>
+      <c r="F474" s="10"/>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
       <c r="I474" s="6"/>
@@ -13735,7 +13738,7 @@
       <c r="C475" s="6"/>
       <c r="D475" s="6"/>
       <c r="E475" s="6"/>
-      <c r="F475" s="9"/>
+      <c r="F475" s="10"/>
       <c r="G475" s="6"/>
       <c r="H475" s="6"/>
       <c r="I475" s="6"/>
@@ -13763,7 +13766,7 @@
       <c r="C476" s="6"/>
       <c r="D476" s="6"/>
       <c r="E476" s="6"/>
-      <c r="F476" s="9"/>
+      <c r="F476" s="10"/>
       <c r="G476" s="6"/>
       <c r="H476" s="6"/>
       <c r="I476" s="6"/>
@@ -13791,7 +13794,7 @@
       <c r="C477" s="6"/>
       <c r="D477" s="6"/>
       <c r="E477" s="6"/>
-      <c r="F477" s="9"/>
+      <c r="F477" s="10"/>
       <c r="G477" s="6"/>
       <c r="H477" s="6"/>
       <c r="I477" s="6"/>
@@ -13819,7 +13822,7 @@
       <c r="C478" s="6"/>
       <c r="D478" s="6"/>
       <c r="E478" s="6"/>
-      <c r="F478" s="9"/>
+      <c r="F478" s="10"/>
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
       <c r="I478" s="6"/>
@@ -13847,7 +13850,7 @@
       <c r="C479" s="6"/>
       <c r="D479" s="6"/>
       <c r="E479" s="6"/>
-      <c r="F479" s="9"/>
+      <c r="F479" s="10"/>
       <c r="G479" s="6"/>
       <c r="H479" s="6"/>
       <c r="I479" s="6"/>
@@ -13875,7 +13878,7 @@
       <c r="C480" s="6"/>
       <c r="D480" s="6"/>
       <c r="E480" s="6"/>
-      <c r="F480" s="9"/>
+      <c r="F480" s="10"/>
       <c r="G480" s="6"/>
       <c r="H480" s="6"/>
       <c r="I480" s="6"/>
@@ -13903,7 +13906,7 @@
       <c r="C481" s="6"/>
       <c r="D481" s="6"/>
       <c r="E481" s="6"/>
-      <c r="F481" s="9"/>
+      <c r="F481" s="10"/>
       <c r="G481" s="6"/>
       <c r="H481" s="6"/>
       <c r="I481" s="6"/>
@@ -13931,7 +13934,7 @@
       <c r="C482" s="6"/>
       <c r="D482" s="6"/>
       <c r="E482" s="6"/>
-      <c r="F482" s="9"/>
+      <c r="F482" s="10"/>
       <c r="G482" s="6"/>
       <c r="H482" s="6"/>
       <c r="I482" s="6"/>
@@ -13959,7 +13962,7 @@
       <c r="C483" s="6"/>
       <c r="D483" s="6"/>
       <c r="E483" s="6"/>
-      <c r="F483" s="9"/>
+      <c r="F483" s="10"/>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
       <c r="I483" s="6"/>
@@ -13987,7 +13990,7 @@
       <c r="C484" s="6"/>
       <c r="D484" s="6"/>
       <c r="E484" s="6"/>
-      <c r="F484" s="9"/>
+      <c r="F484" s="10"/>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
       <c r="I484" s="6"/>
@@ -14015,7 +14018,7 @@
       <c r="C485" s="6"/>
       <c r="D485" s="6"/>
       <c r="E485" s="6"/>
-      <c r="F485" s="9"/>
+      <c r="F485" s="10"/>
       <c r="G485" s="6"/>
       <c r="H485" s="6"/>
       <c r="I485" s="6"/>
@@ -14043,7 +14046,7 @@
       <c r="C486" s="6"/>
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
-      <c r="F486" s="9"/>
+      <c r="F486" s="10"/>
       <c r="G486" s="6"/>
       <c r="H486" s="6"/>
       <c r="I486" s="6"/>
@@ -14071,7 +14074,7 @@
       <c r="C487" s="6"/>
       <c r="D487" s="6"/>
       <c r="E487" s="6"/>
-      <c r="F487" s="9"/>
+      <c r="F487" s="10"/>
       <c r="G487" s="6"/>
       <c r="H487" s="6"/>
       <c r="I487" s="6"/>
@@ -14099,7 +14102,7 @@
       <c r="C488" s="6"/>
       <c r="D488" s="6"/>
       <c r="E488" s="6"/>
-      <c r="F488" s="9"/>
+      <c r="F488" s="10"/>
       <c r="G488" s="6"/>
       <c r="H488" s="6"/>
       <c r="I488" s="6"/>
@@ -14127,7 +14130,7 @@
       <c r="C489" s="6"/>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
-      <c r="F489" s="9"/>
+      <c r="F489" s="10"/>
       <c r="G489" s="6"/>
       <c r="H489" s="6"/>
       <c r="I489" s="6"/>
@@ -14155,7 +14158,7 @@
       <c r="C490" s="6"/>
       <c r="D490" s="6"/>
       <c r="E490" s="6"/>
-      <c r="F490" s="9"/>
+      <c r="F490" s="10"/>
       <c r="G490" s="6"/>
       <c r="H490" s="6"/>
       <c r="I490" s="6"/>
@@ -14183,7 +14186,7 @@
       <c r="C491" s="6"/>
       <c r="D491" s="6"/>
       <c r="E491" s="6"/>
-      <c r="F491" s="9"/>
+      <c r="F491" s="10"/>
       <c r="G491" s="6"/>
       <c r="H491" s="6"/>
       <c r="I491" s="6"/>
@@ -14211,7 +14214,7 @@
       <c r="C492" s="6"/>
       <c r="D492" s="6"/>
       <c r="E492" s="6"/>
-      <c r="F492" s="9"/>
+      <c r="F492" s="10"/>
       <c r="G492" s="6"/>
       <c r="H492" s="6"/>
       <c r="I492" s="6"/>
@@ -14239,7 +14242,7 @@
       <c r="C493" s="6"/>
       <c r="D493" s="6"/>
       <c r="E493" s="6"/>
-      <c r="F493" s="9"/>
+      <c r="F493" s="10"/>
       <c r="G493" s="6"/>
       <c r="H493" s="6"/>
       <c r="I493" s="6"/>
@@ -14267,7 +14270,7 @@
       <c r="C494" s="6"/>
       <c r="D494" s="6"/>
       <c r="E494" s="6"/>
-      <c r="F494" s="9"/>
+      <c r="F494" s="10"/>
       <c r="G494" s="6"/>
       <c r="H494" s="6"/>
       <c r="I494" s="6"/>
@@ -14295,7 +14298,7 @@
       <c r="C495" s="6"/>
       <c r="D495" s="6"/>
       <c r="E495" s="6"/>
-      <c r="F495" s="9"/>
+      <c r="F495" s="10"/>
       <c r="G495" s="6"/>
       <c r="H495" s="6"/>
       <c r="I495" s="6"/>
@@ -14323,7 +14326,7 @@
       <c r="C496" s="6"/>
       <c r="D496" s="6"/>
       <c r="E496" s="6"/>
-      <c r="F496" s="9"/>
+      <c r="F496" s="10"/>
       <c r="G496" s="6"/>
       <c r="H496" s="6"/>
       <c r="I496" s="6"/>
@@ -14351,7 +14354,7 @@
       <c r="C497" s="6"/>
       <c r="D497" s="6"/>
       <c r="E497" s="6"/>
-      <c r="F497" s="9"/>
+      <c r="F497" s="10"/>
       <c r="G497" s="6"/>
       <c r="H497" s="6"/>
       <c r="I497" s="6"/>
@@ -14379,7 +14382,7 @@
       <c r="C498" s="6"/>
       <c r="D498" s="6"/>
       <c r="E498" s="6"/>
-      <c r="F498" s="9"/>
+      <c r="F498" s="10"/>
       <c r="G498" s="6"/>
       <c r="H498" s="6"/>
       <c r="I498" s="6"/>
@@ -14407,7 +14410,7 @@
       <c r="C499" s="6"/>
       <c r="D499" s="6"/>
       <c r="E499" s="6"/>
-      <c r="F499" s="9"/>
+      <c r="F499" s="10"/>
       <c r="G499" s="6"/>
       <c r="H499" s="6"/>
       <c r="I499" s="6"/>
@@ -14435,7 +14438,7 @@
       <c r="C500" s="6"/>
       <c r="D500" s="6"/>
       <c r="E500" s="6"/>
-      <c r="F500" s="9"/>
+      <c r="F500" s="10"/>
       <c r="G500" s="6"/>
       <c r="H500" s="6"/>
       <c r="I500" s="6"/>
@@ -14463,7 +14466,7 @@
       <c r="C501" s="6"/>
       <c r="D501" s="6"/>
       <c r="E501" s="6"/>
-      <c r="F501" s="9"/>
+      <c r="F501" s="10"/>
       <c r="G501" s="6"/>
       <c r="H501" s="6"/>
       <c r="I501" s="6"/>
@@ -14491,7 +14494,7 @@
       <c r="C502" s="6"/>
       <c r="D502" s="6"/>
       <c r="E502" s="6"/>
-      <c r="F502" s="9"/>
+      <c r="F502" s="10"/>
       <c r="G502" s="6"/>
       <c r="H502" s="6"/>
       <c r="I502" s="6"/>
@@ -14519,7 +14522,7 @@
       <c r="C503" s="6"/>
       <c r="D503" s="6"/>
       <c r="E503" s="6"/>
-      <c r="F503" s="9"/>
+      <c r="F503" s="10"/>
       <c r="G503" s="6"/>
       <c r="H503" s="6"/>
       <c r="I503" s="6"/>
@@ -14547,7 +14550,7 @@
       <c r="C504" s="6"/>
       <c r="D504" s="6"/>
       <c r="E504" s="6"/>
-      <c r="F504" s="9"/>
+      <c r="F504" s="10"/>
       <c r="G504" s="6"/>
       <c r="H504" s="6"/>
       <c r="I504" s="6"/>
@@ -14575,7 +14578,7 @@
       <c r="C505" s="6"/>
       <c r="D505" s="6"/>
       <c r="E505" s="6"/>
-      <c r="F505" s="9"/>
+      <c r="F505" s="10"/>
       <c r="G505" s="6"/>
       <c r="H505" s="6"/>
       <c r="I505" s="6"/>
@@ -14603,7 +14606,7 @@
       <c r="C506" s="6"/>
       <c r="D506" s="6"/>
       <c r="E506" s="6"/>
-      <c r="F506" s="9"/>
+      <c r="F506" s="10"/>
       <c r="G506" s="6"/>
       <c r="H506" s="6"/>
       <c r="I506" s="6"/>
@@ -14631,7 +14634,7 @@
       <c r="C507" s="6"/>
       <c r="D507" s="6"/>
       <c r="E507" s="6"/>
-      <c r="F507" s="9"/>
+      <c r="F507" s="10"/>
       <c r="G507" s="6"/>
       <c r="H507" s="6"/>
       <c r="I507" s="6"/>
@@ -14659,7 +14662,7 @@
       <c r="C508" s="6"/>
       <c r="D508" s="6"/>
       <c r="E508" s="6"/>
-      <c r="F508" s="9"/>
+      <c r="F508" s="10"/>
       <c r="G508" s="6"/>
       <c r="H508" s="6"/>
       <c r="I508" s="6"/>
@@ -14687,7 +14690,7 @@
       <c r="C509" s="6"/>
       <c r="D509" s="6"/>
       <c r="E509" s="6"/>
-      <c r="F509" s="9"/>
+      <c r="F509" s="10"/>
       <c r="G509" s="6"/>
       <c r="H509" s="6"/>
       <c r="I509" s="6"/>
@@ -14715,7 +14718,7 @@
       <c r="C510" s="6"/>
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
-      <c r="F510" s="9"/>
+      <c r="F510" s="10"/>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
       <c r="I510" s="6"/>
@@ -14743,7 +14746,7 @@
       <c r="C511" s="6"/>
       <c r="D511" s="6"/>
       <c r="E511" s="6"/>
-      <c r="F511" s="9"/>
+      <c r="F511" s="10"/>
       <c r="G511" s="6"/>
       <c r="H511" s="6"/>
       <c r="I511" s="6"/>
@@ -14771,7 +14774,7 @@
       <c r="C512" s="6"/>
       <c r="D512" s="6"/>
       <c r="E512" s="6"/>
-      <c r="F512" s="9"/>
+      <c r="F512" s="10"/>
       <c r="G512" s="6"/>
       <c r="H512" s="6"/>
       <c r="I512" s="6"/>
@@ -14799,7 +14802,7 @@
       <c r="C513" s="6"/>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
-      <c r="F513" s="9"/>
+      <c r="F513" s="10"/>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
       <c r="I513" s="6"/>
@@ -14827,7 +14830,7 @@
       <c r="C514" s="6"/>
       <c r="D514" s="6"/>
       <c r="E514" s="6"/>
-      <c r="F514" s="9"/>
+      <c r="F514" s="10"/>
       <c r="G514" s="6"/>
       <c r="H514" s="6"/>
       <c r="I514" s="6"/>
@@ -14855,7 +14858,7 @@
       <c r="C515" s="6"/>
       <c r="D515" s="6"/>
       <c r="E515" s="6"/>
-      <c r="F515" s="9"/>
+      <c r="F515" s="10"/>
       <c r="G515" s="6"/>
       <c r="H515" s="6"/>
       <c r="I515" s="6"/>
@@ -14883,7 +14886,7 @@
       <c r="C516" s="6"/>
       <c r="D516" s="6"/>
       <c r="E516" s="6"/>
-      <c r="F516" s="9"/>
+      <c r="F516" s="10"/>
       <c r="G516" s="6"/>
       <c r="H516" s="6"/>
       <c r="I516" s="6"/>
@@ -14911,7 +14914,7 @@
       <c r="C517" s="6"/>
       <c r="D517" s="6"/>
       <c r="E517" s="6"/>
-      <c r="F517" s="9"/>
+      <c r="F517" s="10"/>
       <c r="G517" s="6"/>
       <c r="H517" s="6"/>
       <c r="I517" s="6"/>
@@ -14939,7 +14942,7 @@
       <c r="C518" s="6"/>
       <c r="D518" s="6"/>
       <c r="E518" s="6"/>
-      <c r="F518" s="9"/>
+      <c r="F518" s="10"/>
       <c r="G518" s="6"/>
       <c r="H518" s="6"/>
       <c r="I518" s="6"/>
@@ -14967,7 +14970,7 @@
       <c r="C519" s="6"/>
       <c r="D519" s="6"/>
       <c r="E519" s="6"/>
-      <c r="F519" s="9"/>
+      <c r="F519" s="10"/>
       <c r="G519" s="6"/>
       <c r="H519" s="6"/>
       <c r="I519" s="6"/>
@@ -14995,7 +14998,7 @@
       <c r="C520" s="6"/>
       <c r="D520" s="6"/>
       <c r="E520" s="6"/>
-      <c r="F520" s="9"/>
+      <c r="F520" s="10"/>
       <c r="G520" s="6"/>
       <c r="H520" s="6"/>
       <c r="I520" s="6"/>
@@ -15023,7 +15026,7 @@
       <c r="C521" s="6"/>
       <c r="D521" s="6"/>
       <c r="E521" s="6"/>
-      <c r="F521" s="9"/>
+      <c r="F521" s="10"/>
       <c r="G521" s="6"/>
       <c r="H521" s="6"/>
       <c r="I521" s="6"/>
@@ -15051,7 +15054,7 @@
       <c r="C522" s="6"/>
       <c r="D522" s="6"/>
       <c r="E522" s="6"/>
-      <c r="F522" s="9"/>
+      <c r="F522" s="10"/>
       <c r="G522" s="6"/>
       <c r="H522" s="6"/>
       <c r="I522" s="6"/>
@@ -15079,7 +15082,7 @@
       <c r="C523" s="6"/>
       <c r="D523" s="6"/>
       <c r="E523" s="6"/>
-      <c r="F523" s="9"/>
+      <c r="F523" s="10"/>
       <c r="G523" s="6"/>
       <c r="H523" s="6"/>
       <c r="I523" s="6"/>
@@ -15107,7 +15110,7 @@
       <c r="C524" s="6"/>
       <c r="D524" s="6"/>
       <c r="E524" s="6"/>
-      <c r="F524" s="9"/>
+      <c r="F524" s="10"/>
       <c r="G524" s="6"/>
       <c r="H524" s="6"/>
       <c r="I524" s="6"/>
@@ -15135,7 +15138,7 @@
       <c r="C525" s="6"/>
       <c r="D525" s="6"/>
       <c r="E525" s="6"/>
-      <c r="F525" s="9"/>
+      <c r="F525" s="10"/>
       <c r="G525" s="6"/>
       <c r="H525" s="6"/>
       <c r="I525" s="6"/>
@@ -15163,7 +15166,7 @@
       <c r="C526" s="6"/>
       <c r="D526" s="6"/>
       <c r="E526" s="6"/>
-      <c r="F526" s="9"/>
+      <c r="F526" s="10"/>
       <c r="G526" s="6"/>
       <c r="H526" s="6"/>
       <c r="I526" s="6"/>
@@ -15191,7 +15194,7 @@
       <c r="C527" s="6"/>
       <c r="D527" s="6"/>
       <c r="E527" s="6"/>
-      <c r="F527" s="9"/>
+      <c r="F527" s="10"/>
       <c r="G527" s="6"/>
       <c r="H527" s="6"/>
       <c r="I527" s="6"/>
@@ -15219,7 +15222,7 @@
       <c r="C528" s="6"/>
       <c r="D528" s="6"/>
       <c r="E528" s="6"/>
-      <c r="F528" s="9"/>
+      <c r="F528" s="10"/>
       <c r="G528" s="6"/>
       <c r="H528" s="6"/>
       <c r="I528" s="6"/>
@@ -15247,7 +15250,7 @@
       <c r="C529" s="6"/>
       <c r="D529" s="6"/>
       <c r="E529" s="6"/>
-      <c r="F529" s="9"/>
+      <c r="F529" s="10"/>
       <c r="G529" s="6"/>
       <c r="H529" s="6"/>
       <c r="I529" s="6"/>
@@ -15275,7 +15278,7 @@
       <c r="C530" s="6"/>
       <c r="D530" s="6"/>
       <c r="E530" s="6"/>
-      <c r="F530" s="9"/>
+      <c r="F530" s="10"/>
       <c r="G530" s="6"/>
       <c r="H530" s="6"/>
       <c r="I530" s="6"/>
@@ -15303,7 +15306,7 @@
       <c r="C531" s="6"/>
       <c r="D531" s="6"/>
       <c r="E531" s="6"/>
-      <c r="F531" s="9"/>
+      <c r="F531" s="10"/>
       <c r="G531" s="6"/>
       <c r="H531" s="6"/>
       <c r="I531" s="6"/>
@@ -15331,7 +15334,7 @@
       <c r="C532" s="6"/>
       <c r="D532" s="6"/>
       <c r="E532" s="6"/>
-      <c r="F532" s="9"/>
+      <c r="F532" s="10"/>
       <c r="G532" s="6"/>
       <c r="H532" s="6"/>
       <c r="I532" s="6"/>
@@ -15359,7 +15362,7 @@
       <c r="C533" s="6"/>
       <c r="D533" s="6"/>
       <c r="E533" s="6"/>
-      <c r="F533" s="9"/>
+      <c r="F533" s="10"/>
       <c r="G533" s="6"/>
       <c r="H533" s="6"/>
       <c r="I533" s="6"/>
@@ -15387,7 +15390,7 @@
       <c r="C534" s="6"/>
       <c r="D534" s="6"/>
       <c r="E534" s="6"/>
-      <c r="F534" s="9"/>
+      <c r="F534" s="10"/>
       <c r="G534" s="6"/>
       <c r="H534" s="6"/>
       <c r="I534" s="6"/>
@@ -15415,7 +15418,7 @@
       <c r="C535" s="6"/>
       <c r="D535" s="6"/>
       <c r="E535" s="6"/>
-      <c r="F535" s="9"/>
+      <c r="F535" s="10"/>
       <c r="G535" s="6"/>
       <c r="H535" s="6"/>
       <c r="I535" s="6"/>
@@ -15443,7 +15446,7 @@
       <c r="C536" s="6"/>
       <c r="D536" s="6"/>
       <c r="E536" s="6"/>
-      <c r="F536" s="9"/>
+      <c r="F536" s="10"/>
       <c r="G536" s="6"/>
       <c r="H536" s="6"/>
       <c r="I536" s="6"/>
@@ -15471,7 +15474,7 @@
       <c r="C537" s="6"/>
       <c r="D537" s="6"/>
       <c r="E537" s="6"/>
-      <c r="F537" s="9"/>
+      <c r="F537" s="10"/>
       <c r="G537" s="6"/>
       <c r="H537" s="6"/>
       <c r="I537" s="6"/>
@@ -15499,7 +15502,7 @@
       <c r="C538" s="6"/>
       <c r="D538" s="6"/>
       <c r="E538" s="6"/>
-      <c r="F538" s="9"/>
+      <c r="F538" s="10"/>
       <c r="G538" s="6"/>
       <c r="H538" s="6"/>
       <c r="I538" s="6"/>
@@ -15527,7 +15530,7 @@
       <c r="C539" s="6"/>
       <c r="D539" s="6"/>
       <c r="E539" s="6"/>
-      <c r="F539" s="9"/>
+      <c r="F539" s="10"/>
       <c r="G539" s="6"/>
       <c r="H539" s="6"/>
       <c r="I539" s="6"/>
@@ -15555,7 +15558,7 @@
       <c r="C540" s="6"/>
       <c r="D540" s="6"/>
       <c r="E540" s="6"/>
-      <c r="F540" s="9"/>
+      <c r="F540" s="10"/>
       <c r="G540" s="6"/>
       <c r="H540" s="6"/>
       <c r="I540" s="6"/>
@@ -15583,7 +15586,7 @@
       <c r="C541" s="6"/>
       <c r="D541" s="6"/>
       <c r="E541" s="6"/>
-      <c r="F541" s="9"/>
+      <c r="F541" s="10"/>
       <c r="G541" s="6"/>
       <c r="H541" s="6"/>
       <c r="I541" s="6"/>
@@ -15611,7 +15614,7 @@
       <c r="C542" s="6"/>
       <c r="D542" s="6"/>
       <c r="E542" s="6"/>
-      <c r="F542" s="9"/>
+      <c r="F542" s="10"/>
       <c r="G542" s="6"/>
       <c r="H542" s="6"/>
       <c r="I542" s="6"/>
@@ -15639,7 +15642,7 @@
       <c r="C543" s="6"/>
       <c r="D543" s="6"/>
       <c r="E543" s="6"/>
-      <c r="F543" s="9"/>
+      <c r="F543" s="10"/>
       <c r="G543" s="6"/>
       <c r="H543" s="6"/>
       <c r="I543" s="6"/>
@@ -15667,7 +15670,7 @@
       <c r="C544" s="6"/>
       <c r="D544" s="6"/>
       <c r="E544" s="6"/>
-      <c r="F544" s="9"/>
+      <c r="F544" s="10"/>
       <c r="G544" s="6"/>
       <c r="H544" s="6"/>
       <c r="I544" s="6"/>
@@ -15695,7 +15698,7 @@
       <c r="C545" s="6"/>
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
-      <c r="F545" s="9"/>
+      <c r="F545" s="10"/>
       <c r="G545" s="6"/>
       <c r="H545" s="6"/>
       <c r="I545" s="6"/>
@@ -15723,7 +15726,7 @@
       <c r="C546" s="6"/>
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
-      <c r="F546" s="9"/>
+      <c r="F546" s="10"/>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
       <c r="I546" s="6"/>
@@ -15751,7 +15754,7 @@
       <c r="C547" s="6"/>
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
-      <c r="F547" s="9"/>
+      <c r="F547" s="10"/>
       <c r="G547" s="6"/>
       <c r="H547" s="6"/>
       <c r="I547" s="6"/>
@@ -15779,7 +15782,7 @@
       <c r="C548" s="6"/>
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
-      <c r="F548" s="9"/>
+      <c r="F548" s="10"/>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
       <c r="I548" s="6"/>
@@ -15807,7 +15810,7 @@
       <c r="C549" s="6"/>
       <c r="D549" s="6"/>
       <c r="E549" s="6"/>
-      <c r="F549" s="9"/>
+      <c r="F549" s="10"/>
       <c r="G549" s="6"/>
       <c r="H549" s="6"/>
       <c r="I549" s="6"/>
@@ -15835,7 +15838,7 @@
       <c r="C550" s="6"/>
       <c r="D550" s="6"/>
       <c r="E550" s="6"/>
-      <c r="F550" s="9"/>
+      <c r="F550" s="10"/>
       <c r="G550" s="6"/>
       <c r="H550" s="6"/>
       <c r="I550" s="6"/>
@@ -15863,7 +15866,7 @@
       <c r="C551" s="6"/>
       <c r="D551" s="6"/>
       <c r="E551" s="6"/>
-      <c r="F551" s="9"/>
+      <c r="F551" s="10"/>
       <c r="G551" s="6"/>
       <c r="H551" s="6"/>
       <c r="I551" s="6"/>
@@ -15891,7 +15894,7 @@
       <c r="C552" s="6"/>
       <c r="D552" s="6"/>
       <c r="E552" s="6"/>
-      <c r="F552" s="9"/>
+      <c r="F552" s="10"/>
       <c r="G552" s="6"/>
       <c r="H552" s="6"/>
       <c r="I552" s="6"/>
@@ -15919,7 +15922,7 @@
       <c r="C553" s="6"/>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
-      <c r="F553" s="9"/>
+      <c r="F553" s="10"/>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
       <c r="I553" s="6"/>
@@ -15947,7 +15950,7 @@
       <c r="C554" s="6"/>
       <c r="D554" s="6"/>
       <c r="E554" s="6"/>
-      <c r="F554" s="9"/>
+      <c r="F554" s="10"/>
       <c r="G554" s="6"/>
       <c r="H554" s="6"/>
       <c r="I554" s="6"/>
@@ -15975,7 +15978,7 @@
       <c r="C555" s="6"/>
       <c r="D555" s="6"/>
       <c r="E555" s="6"/>
-      <c r="F555" s="9"/>
+      <c r="F555" s="10"/>
       <c r="G555" s="6"/>
       <c r="H555" s="6"/>
       <c r="I555" s="6"/>
@@ -16003,7 +16006,7 @@
       <c r="C556" s="6"/>
       <c r="D556" s="6"/>
       <c r="E556" s="6"/>
-      <c r="F556" s="9"/>
+      <c r="F556" s="10"/>
       <c r="G556" s="6"/>
       <c r="H556" s="6"/>
       <c r="I556" s="6"/>
@@ -16031,7 +16034,7 @@
       <c r="C557" s="6"/>
       <c r="D557" s="6"/>
       <c r="E557" s="6"/>
-      <c r="F557" s="9"/>
+      <c r="F557" s="10"/>
       <c r="G557" s="6"/>
       <c r="H557" s="6"/>
       <c r="I557" s="6"/>
@@ -16059,7 +16062,7 @@
       <c r="C558" s="6"/>
       <c r="D558" s="6"/>
       <c r="E558" s="6"/>
-      <c r="F558" s="9"/>
+      <c r="F558" s="10"/>
       <c r="G558" s="6"/>
       <c r="H558" s="6"/>
       <c r="I558" s="6"/>
@@ -16087,7 +16090,7 @@
       <c r="C559" s="6"/>
       <c r="D559" s="6"/>
       <c r="E559" s="6"/>
-      <c r="F559" s="9"/>
+      <c r="F559" s="10"/>
       <c r="G559" s="6"/>
       <c r="H559" s="6"/>
       <c r="I559" s="6"/>
@@ -16115,7 +16118,7 @@
       <c r="C560" s="6"/>
       <c r="D560" s="6"/>
       <c r="E560" s="6"/>
-      <c r="F560" s="9"/>
+      <c r="F560" s="10"/>
       <c r="G560" s="6"/>
       <c r="H560" s="6"/>
       <c r="I560" s="6"/>
@@ -16143,7 +16146,7 @@
       <c r="C561" s="6"/>
       <c r="D561" s="6"/>
       <c r="E561" s="6"/>
-      <c r="F561" s="9"/>
+      <c r="F561" s="10"/>
       <c r="G561" s="6"/>
       <c r="H561" s="6"/>
       <c r="I561" s="6"/>
@@ -16171,7 +16174,7 @@
       <c r="C562" s="6"/>
       <c r="D562" s="6"/>
       <c r="E562" s="6"/>
-      <c r="F562" s="9"/>
+      <c r="F562" s="10"/>
       <c r="G562" s="6"/>
       <c r="H562" s="6"/>
       <c r="I562" s="6"/>
@@ -16199,7 +16202,7 @@
       <c r="C563" s="6"/>
       <c r="D563" s="6"/>
       <c r="E563" s="6"/>
-      <c r="F563" s="9"/>
+      <c r="F563" s="10"/>
       <c r="G563" s="6"/>
       <c r="H563" s="6"/>
       <c r="I563" s="6"/>
@@ -16227,7 +16230,7 @@
       <c r="C564" s="6"/>
       <c r="D564" s="6"/>
       <c r="E564" s="6"/>
-      <c r="F564" s="9"/>
+      <c r="F564" s="10"/>
       <c r="G564" s="6"/>
       <c r="H564" s="6"/>
       <c r="I564" s="6"/>
@@ -16255,7 +16258,7 @@
       <c r="C565" s="6"/>
       <c r="D565" s="6"/>
       <c r="E565" s="6"/>
-      <c r="F565" s="9"/>
+      <c r="F565" s="10"/>
       <c r="G565" s="6"/>
       <c r="H565" s="6"/>
       <c r="I565" s="6"/>
@@ -16283,7 +16286,7 @@
       <c r="C566" s="6"/>
       <c r="D566" s="6"/>
       <c r="E566" s="6"/>
-      <c r="F566" s="9"/>
+      <c r="F566" s="10"/>
       <c r="G566" s="6"/>
       <c r="H566" s="6"/>
       <c r="I566" s="6"/>
@@ -16311,7 +16314,7 @@
       <c r="C567" s="6"/>
       <c r="D567" s="6"/>
       <c r="E567" s="6"/>
-      <c r="F567" s="9"/>
+      <c r="F567" s="10"/>
       <c r="G567" s="6"/>
       <c r="H567" s="6"/>
       <c r="I567" s="6"/>
@@ -16339,7 +16342,7 @@
       <c r="C568" s="6"/>
       <c r="D568" s="6"/>
       <c r="E568" s="6"/>
-      <c r="F568" s="9"/>
+      <c r="F568" s="10"/>
       <c r="G568" s="6"/>
       <c r="H568" s="6"/>
       <c r="I568" s="6"/>
@@ -16367,7 +16370,7 @@
       <c r="C569" s="6"/>
       <c r="D569" s="6"/>
       <c r="E569" s="6"/>
-      <c r="F569" s="9"/>
+      <c r="F569" s="10"/>
       <c r="G569" s="6"/>
       <c r="H569" s="6"/>
       <c r="I569" s="6"/>
@@ -16395,7 +16398,7 @@
       <c r="C570" s="6"/>
       <c r="D570" s="6"/>
       <c r="E570" s="6"/>
-      <c r="F570" s="9"/>
+      <c r="F570" s="10"/>
       <c r="G570" s="6"/>
       <c r="H570" s="6"/>
       <c r="I570" s="6"/>
@@ -16423,7 +16426,7 @@
       <c r="C571" s="6"/>
       <c r="D571" s="6"/>
       <c r="E571" s="6"/>
-      <c r="F571" s="9"/>
+      <c r="F571" s="10"/>
       <c r="G571" s="6"/>
       <c r="H571" s="6"/>
       <c r="I571" s="6"/>
@@ -16451,7 +16454,7 @@
       <c r="C572" s="6"/>
       <c r="D572" s="6"/>
       <c r="E572" s="6"/>
-      <c r="F572" s="9"/>
+      <c r="F572" s="10"/>
       <c r="G572" s="6"/>
       <c r="H572" s="6"/>
       <c r="I572" s="6"/>
@@ -16479,7 +16482,7 @@
       <c r="C573" s="6"/>
       <c r="D573" s="6"/>
       <c r="E573" s="6"/>
-      <c r="F573" s="9"/>
+      <c r="F573" s="10"/>
       <c r="G573" s="6"/>
       <c r="H573" s="6"/>
       <c r="I573" s="6"/>
@@ -16507,7 +16510,7 @@
       <c r="C574" s="6"/>
       <c r="D574" s="6"/>
       <c r="E574" s="6"/>
-      <c r="F574" s="9"/>
+      <c r="F574" s="10"/>
       <c r="G574" s="6"/>
       <c r="H574" s="6"/>
       <c r="I574" s="6"/>
@@ -16535,7 +16538,7 @@
       <c r="C575" s="6"/>
       <c r="D575" s="6"/>
       <c r="E575" s="6"/>
-      <c r="F575" s="9"/>
+      <c r="F575" s="10"/>
       <c r="G575" s="6"/>
       <c r="H575" s="6"/>
       <c r="I575" s="6"/>
@@ -16563,7 +16566,7 @@
       <c r="C576" s="6"/>
       <c r="D576" s="6"/>
       <c r="E576" s="6"/>
-      <c r="F576" s="9"/>
+      <c r="F576" s="10"/>
       <c r="G576" s="6"/>
       <c r="H576" s="6"/>
       <c r="I576" s="6"/>
@@ -16591,7 +16594,7 @@
       <c r="C577" s="6"/>
       <c r="D577" s="6"/>
       <c r="E577" s="6"/>
-      <c r="F577" s="9"/>
+      <c r="F577" s="10"/>
       <c r="G577" s="6"/>
       <c r="H577" s="6"/>
       <c r="I577" s="6"/>
@@ -16619,7 +16622,7 @@
       <c r="C578" s="6"/>
       <c r="D578" s="6"/>
       <c r="E578" s="6"/>
-      <c r="F578" s="9"/>
+      <c r="F578" s="10"/>
       <c r="G578" s="6"/>
       <c r="H578" s="6"/>
       <c r="I578" s="6"/>
@@ -16647,7 +16650,7 @@
       <c r="C579" s="6"/>
       <c r="D579" s="6"/>
       <c r="E579" s="6"/>
-      <c r="F579" s="9"/>
+      <c r="F579" s="10"/>
       <c r="G579" s="6"/>
       <c r="H579" s="6"/>
       <c r="I579" s="6"/>
@@ -16675,7 +16678,7 @@
       <c r="C580" s="6"/>
       <c r="D580" s="6"/>
       <c r="E580" s="6"/>
-      <c r="F580" s="9"/>
+      <c r="F580" s="10"/>
       <c r="G580" s="6"/>
       <c r="H580" s="6"/>
       <c r="I580" s="6"/>
@@ -16703,7 +16706,7 @@
       <c r="C581" s="6"/>
       <c r="D581" s="6"/>
       <c r="E581" s="6"/>
-      <c r="F581" s="9"/>
+      <c r="F581" s="10"/>
       <c r="G581" s="6"/>
       <c r="H581" s="6"/>
       <c r="I581" s="6"/>
@@ -16731,7 +16734,7 @@
       <c r="C582" s="6"/>
       <c r="D582" s="6"/>
       <c r="E582" s="6"/>
-      <c r="F582" s="9"/>
+      <c r="F582" s="10"/>
       <c r="G582" s="6"/>
       <c r="H582" s="6"/>
       <c r="I582" s="6"/>
@@ -16759,7 +16762,7 @@
       <c r="C583" s="6"/>
       <c r="D583" s="6"/>
       <c r="E583" s="6"/>
-      <c r="F583" s="9"/>
+      <c r="F583" s="10"/>
       <c r="G583" s="6"/>
       <c r="H583" s="6"/>
       <c r="I583" s="6"/>
@@ -16787,7 +16790,7 @@
       <c r="C584" s="6"/>
       <c r="D584" s="6"/>
       <c r="E584" s="6"/>
-      <c r="F584" s="9"/>
+      <c r="F584" s="10"/>
       <c r="G584" s="6"/>
       <c r="H584" s="6"/>
       <c r="I584" s="6"/>
@@ -16815,7 +16818,7 @@
       <c r="C585" s="6"/>
       <c r="D585" s="6"/>
       <c r="E585" s="6"/>
-      <c r="F585" s="9"/>
+      <c r="F585" s="10"/>
       <c r="G585" s="6"/>
       <c r="H585" s="6"/>
       <c r="I585" s="6"/>
@@ -16843,7 +16846,7 @@
       <c r="C586" s="6"/>
       <c r="D586" s="6"/>
       <c r="E586" s="6"/>
-      <c r="F586" s="9"/>
+      <c r="F586" s="10"/>
       <c r="G586" s="6"/>
       <c r="H586" s="6"/>
       <c r="I586" s="6"/>
@@ -16871,7 +16874,7 @@
       <c r="C587" s="6"/>
       <c r="D587" s="6"/>
       <c r="E587" s="6"/>
-      <c r="F587" s="9"/>
+      <c r="F587" s="10"/>
       <c r="G587" s="6"/>
       <c r="H587" s="6"/>
       <c r="I587" s="6"/>
@@ -16899,7 +16902,7 @@
       <c r="C588" s="6"/>
       <c r="D588" s="6"/>
       <c r="E588" s="6"/>
-      <c r="F588" s="9"/>
+      <c r="F588" s="10"/>
       <c r="G588" s="6"/>
       <c r="H588" s="6"/>
       <c r="I588" s="6"/>
@@ -16927,7 +16930,7 @@
       <c r="C589" s="6"/>
       <c r="D589" s="6"/>
       <c r="E589" s="6"/>
-      <c r="F589" s="9"/>
+      <c r="F589" s="10"/>
       <c r="G589" s="6"/>
       <c r="H589" s="6"/>
       <c r="I589" s="6"/>
@@ -16955,7 +16958,7 @@
       <c r="C590" s="6"/>
       <c r="D590" s="6"/>
       <c r="E590" s="6"/>
-      <c r="F590" s="9"/>
+      <c r="F590" s="10"/>
       <c r="G590" s="6"/>
       <c r="H590" s="6"/>
       <c r="I590" s="6"/>
@@ -16983,7 +16986,7 @@
       <c r="C591" s="6"/>
       <c r="D591" s="6"/>
       <c r="E591" s="6"/>
-      <c r="F591" s="9"/>
+      <c r="F591" s="10"/>
       <c r="G591" s="6"/>
       <c r="H591" s="6"/>
       <c r="I591" s="6"/>
@@ -17011,7 +17014,7 @@
       <c r="C592" s="6"/>
       <c r="D592" s="6"/>
       <c r="E592" s="6"/>
-      <c r="F592" s="9"/>
+      <c r="F592" s="10"/>
       <c r="G592" s="6"/>
       <c r="H592" s="6"/>
       <c r="I592" s="6"/>
@@ -17039,7 +17042,7 @@
       <c r="C593" s="6"/>
       <c r="D593" s="6"/>
       <c r="E593" s="6"/>
-      <c r="F593" s="9"/>
+      <c r="F593" s="10"/>
       <c r="G593" s="6"/>
       <c r="H593" s="6"/>
       <c r="I593" s="6"/>
@@ -17067,7 +17070,7 @@
       <c r="C594" s="6"/>
       <c r="D594" s="6"/>
       <c r="E594" s="6"/>
-      <c r="F594" s="9"/>
+      <c r="F594" s="10"/>
       <c r="G594" s="6"/>
       <c r="H594" s="6"/>
       <c r="I594" s="6"/>
@@ -17095,7 +17098,7 @@
       <c r="C595" s="6"/>
       <c r="D595" s="6"/>
       <c r="E595" s="6"/>
-      <c r="F595" s="9"/>
+      <c r="F595" s="10"/>
       <c r="G595" s="6"/>
       <c r="H595" s="6"/>
       <c r="I595" s="6"/>
@@ -17123,7 +17126,7 @@
       <c r="C596" s="6"/>
       <c r="D596" s="6"/>
       <c r="E596" s="6"/>
-      <c r="F596" s="9"/>
+      <c r="F596" s="10"/>
       <c r="G596" s="6"/>
       <c r="H596" s="6"/>
       <c r="I596" s="6"/>
@@ -17151,7 +17154,7 @@
       <c r="C597" s="6"/>
       <c r="D597" s="6"/>
       <c r="E597" s="6"/>
-      <c r="F597" s="9"/>
+      <c r="F597" s="10"/>
       <c r="G597" s="6"/>
       <c r="H597" s="6"/>
       <c r="I597" s="6"/>
@@ -17179,7 +17182,7 @@
       <c r="C598" s="6"/>
       <c r="D598" s="6"/>
       <c r="E598" s="6"/>
-      <c r="F598" s="9"/>
+      <c r="F598" s="10"/>
       <c r="G598" s="6"/>
       <c r="H598" s="6"/>
       <c r="I598" s="6"/>
@@ -17207,7 +17210,7 @@
       <c r="C599" s="6"/>
       <c r="D599" s="6"/>
       <c r="E599" s="6"/>
-      <c r="F599" s="9"/>
+      <c r="F599" s="10"/>
       <c r="G599" s="6"/>
       <c r="H599" s="6"/>
       <c r="I599" s="6"/>
@@ -17235,7 +17238,7 @@
       <c r="C600" s="6"/>
       <c r="D600" s="6"/>
       <c r="E600" s="6"/>
-      <c r="F600" s="9"/>
+      <c r="F600" s="10"/>
       <c r="G600" s="6"/>
       <c r="H600" s="6"/>
       <c r="I600" s="6"/>
@@ -17263,7 +17266,7 @@
       <c r="C601" s="6"/>
       <c r="D601" s="6"/>
       <c r="E601" s="6"/>
-      <c r="F601" s="9"/>
+      <c r="F601" s="10"/>
       <c r="G601" s="6"/>
       <c r="H601" s="6"/>
       <c r="I601" s="6"/>
@@ -17291,7 +17294,7 @@
       <c r="C602" s="6"/>
       <c r="D602" s="6"/>
       <c r="E602" s="6"/>
-      <c r="F602" s="9"/>
+      <c r="F602" s="10"/>
       <c r="G602" s="6"/>
       <c r="H602" s="6"/>
       <c r="I602" s="6"/>
@@ -17319,7 +17322,7 @@
       <c r="C603" s="6"/>
       <c r="D603" s="6"/>
       <c r="E603" s="6"/>
-      <c r="F603" s="9"/>
+      <c r="F603" s="10"/>
       <c r="G603" s="6"/>
       <c r="H603" s="6"/>
       <c r="I603" s="6"/>
@@ -17347,7 +17350,7 @@
       <c r="C604" s="6"/>
       <c r="D604" s="6"/>
       <c r="E604" s="6"/>
-      <c r="F604" s="9"/>
+      <c r="F604" s="10"/>
       <c r="G604" s="6"/>
       <c r="H604" s="6"/>
       <c r="I604" s="6"/>
@@ -17375,7 +17378,7 @@
       <c r="C605" s="6"/>
       <c r="D605" s="6"/>
       <c r="E605" s="6"/>
-      <c r="F605" s="9"/>
+      <c r="F605" s="10"/>
       <c r="G605" s="6"/>
       <c r="H605" s="6"/>
       <c r="I605" s="6"/>
@@ -17403,7 +17406,7 @@
       <c r="C606" s="6"/>
       <c r="D606" s="6"/>
       <c r="E606" s="6"/>
-      <c r="F606" s="9"/>
+      <c r="F606" s="10"/>
       <c r="G606" s="6"/>
       <c r="H606" s="6"/>
       <c r="I606" s="6"/>
@@ -17431,7 +17434,7 @@
       <c r="C607" s="6"/>
       <c r="D607" s="6"/>
       <c r="E607" s="6"/>
-      <c r="F607" s="9"/>
+      <c r="F607" s="10"/>
       <c r="G607" s="6"/>
       <c r="H607" s="6"/>
       <c r="I607" s="6"/>
@@ -17459,7 +17462,7 @@
       <c r="C608" s="6"/>
       <c r="D608" s="6"/>
       <c r="E608" s="6"/>
-      <c r="F608" s="9"/>
+      <c r="F608" s="10"/>
       <c r="G608" s="6"/>
       <c r="H608" s="6"/>
       <c r="I608" s="6"/>
@@ -17487,7 +17490,7 @@
       <c r="C609" s="6"/>
       <c r="D609" s="6"/>
       <c r="E609" s="6"/>
-      <c r="F609" s="9"/>
+      <c r="F609" s="10"/>
       <c r="G609" s="6"/>
       <c r="H609" s="6"/>
       <c r="I609" s="6"/>
@@ -17515,7 +17518,7 @@
       <c r="C610" s="6"/>
       <c r="D610" s="6"/>
       <c r="E610" s="6"/>
-      <c r="F610" s="9"/>
+      <c r="F610" s="10"/>
       <c r="G610" s="6"/>
       <c r="H610" s="6"/>
       <c r="I610" s="6"/>
@@ -17543,7 +17546,7 @@
       <c r="C611" s="6"/>
       <c r="D611" s="6"/>
       <c r="E611" s="6"/>
-      <c r="F611" s="9"/>
+      <c r="F611" s="10"/>
       <c r="G611" s="6"/>
       <c r="H611" s="6"/>
       <c r="I611" s="6"/>
@@ -17571,7 +17574,7 @@
       <c r="C612" s="6"/>
       <c r="D612" s="6"/>
       <c r="E612" s="6"/>
-      <c r="F612" s="9"/>
+      <c r="F612" s="10"/>
       <c r="G612" s="6"/>
       <c r="H612" s="6"/>
       <c r="I612" s="6"/>
@@ -17599,7 +17602,7 @@
       <c r="C613" s="6"/>
       <c r="D613" s="6"/>
       <c r="E613" s="6"/>
-      <c r="F613" s="9"/>
+      <c r="F613" s="10"/>
       <c r="G613" s="6"/>
       <c r="H613" s="6"/>
       <c r="I613" s="6"/>
@@ -17627,7 +17630,7 @@
       <c r="C614" s="6"/>
       <c r="D614" s="6"/>
       <c r="E614" s="6"/>
-      <c r="F614" s="9"/>
+      <c r="F614" s="10"/>
       <c r="G614" s="6"/>
       <c r="H614" s="6"/>
       <c r="I614" s="6"/>
@@ -17655,7 +17658,7 @@
       <c r="C615" s="6"/>
       <c r="D615" s="6"/>
       <c r="E615" s="6"/>
-      <c r="F615" s="9"/>
+      <c r="F615" s="10"/>
       <c r="G615" s="6"/>
       <c r="H615" s="6"/>
       <c r="I615" s="6"/>
@@ -17683,7 +17686,7 @@
       <c r="C616" s="6"/>
       <c r="D616" s="6"/>
       <c r="E616" s="6"/>
-      <c r="F616" s="9"/>
+      <c r="F616" s="10"/>
       <c r="G616" s="6"/>
       <c r="H616" s="6"/>
       <c r="I616" s="6"/>
@@ -17711,7 +17714,7 @@
       <c r="C617" s="6"/>
       <c r="D617" s="6"/>
       <c r="E617" s="6"/>
-      <c r="F617" s="9"/>
+      <c r="F617" s="10"/>
       <c r="G617" s="6"/>
       <c r="H617" s="6"/>
       <c r="I617" s="6"/>
@@ -17739,7 +17742,7 @@
       <c r="C618" s="6"/>
       <c r="D618" s="6"/>
       <c r="E618" s="6"/>
-      <c r="F618" s="9"/>
+      <c r="F618" s="10"/>
       <c r="G618" s="6"/>
       <c r="H618" s="6"/>
       <c r="I618" s="6"/>
@@ -17767,7 +17770,7 @@
       <c r="C619" s="6"/>
       <c r="D619" s="6"/>
       <c r="E619" s="6"/>
-      <c r="F619" s="9"/>
+      <c r="F619" s="10"/>
       <c r="G619" s="6"/>
       <c r="H619" s="6"/>
       <c r="I619" s="6"/>
@@ -17795,7 +17798,7 @@
       <c r="C620" s="6"/>
       <c r="D620" s="6"/>
       <c r="E620" s="6"/>
-      <c r="F620" s="9"/>
+      <c r="F620" s="10"/>
       <c r="G620" s="6"/>
       <c r="H620" s="6"/>
       <c r="I620" s="6"/>
@@ -17823,7 +17826,7 @@
       <c r="C621" s="6"/>
       <c r="D621" s="6"/>
       <c r="E621" s="6"/>
-      <c r="F621" s="9"/>
+      <c r="F621" s="10"/>
       <c r="G621" s="6"/>
       <c r="H621" s="6"/>
       <c r="I621" s="6"/>
@@ -17851,7 +17854,7 @@
       <c r="C622" s="6"/>
       <c r="D622" s="6"/>
       <c r="E622" s="6"/>
-      <c r="F622" s="9"/>
+      <c r="F622" s="10"/>
       <c r="G622" s="6"/>
       <c r="H622" s="6"/>
       <c r="I622" s="6"/>
@@ -17879,7 +17882,7 @@
       <c r="C623" s="6"/>
       <c r="D623" s="6"/>
       <c r="E623" s="6"/>
-      <c r="F623" s="9"/>
+      <c r="F623" s="10"/>
       <c r="G623" s="6"/>
       <c r="H623" s="6"/>
       <c r="I623" s="6"/>
@@ -17907,7 +17910,7 @@
       <c r="C624" s="6"/>
       <c r="D624" s="6"/>
       <c r="E624" s="6"/>
-      <c r="F624" s="9"/>
+      <c r="F624" s="10"/>
       <c r="G624" s="6"/>
       <c r="H624" s="6"/>
       <c r="I624" s="6"/>
@@ -17935,7 +17938,7 @@
       <c r="C625" s="6"/>
       <c r="D625" s="6"/>
       <c r="E625" s="6"/>
-      <c r="F625" s="9"/>
+      <c r="F625" s="10"/>
       <c r="G625" s="6"/>
       <c r="H625" s="6"/>
       <c r="I625" s="6"/>
@@ -17963,7 +17966,7 @@
       <c r="C626" s="6"/>
       <c r="D626" s="6"/>
       <c r="E626" s="6"/>
-      <c r="F626" s="9"/>
+      <c r="F626" s="10"/>
       <c r="G626" s="6"/>
       <c r="H626" s="6"/>
       <c r="I626" s="6"/>
@@ -17991,7 +17994,7 @@
       <c r="C627" s="6"/>
       <c r="D627" s="6"/>
       <c r="E627" s="6"/>
-      <c r="F627" s="9"/>
+      <c r="F627" s="10"/>
       <c r="G627" s="6"/>
       <c r="H627" s="6"/>
       <c r="I627" s="6"/>
@@ -18019,7 +18022,7 @@
       <c r="C628" s="6"/>
       <c r="D628" s="6"/>
       <c r="E628" s="6"/>
-      <c r="F628" s="9"/>
+      <c r="F628" s="10"/>
       <c r="G628" s="6"/>
       <c r="H628" s="6"/>
       <c r="I628" s="6"/>
@@ -18047,7 +18050,7 @@
       <c r="C629" s="6"/>
       <c r="D629" s="6"/>
       <c r="E629" s="6"/>
-      <c r="F629" s="9"/>
+      <c r="F629" s="10"/>
       <c r="G629" s="6"/>
       <c r="H629" s="6"/>
       <c r="I629" s="6"/>
@@ -18075,7 +18078,7 @@
       <c r="C630" s="6"/>
       <c r="D630" s="6"/>
       <c r="E630" s="6"/>
-      <c r="F630" s="9"/>
+      <c r="F630" s="10"/>
       <c r="G630" s="6"/>
       <c r="H630" s="6"/>
       <c r="I630" s="6"/>
@@ -18103,7 +18106,7 @@
       <c r="C631" s="6"/>
       <c r="D631" s="6"/>
       <c r="E631" s="6"/>
-      <c r="F631" s="9"/>
+      <c r="F631" s="10"/>
       <c r="G631" s="6"/>
       <c r="H631" s="6"/>
       <c r="I631" s="6"/>
@@ -18131,7 +18134,7 @@
       <c r="C632" s="6"/>
       <c r="D632" s="6"/>
       <c r="E632" s="6"/>
-      <c r="F632" s="9"/>
+      <c r="F632" s="10"/>
       <c r="G632" s="6"/>
       <c r="H632" s="6"/>
       <c r="I632" s="6"/>
@@ -18159,7 +18162,7 @@
       <c r="C633" s="6"/>
       <c r="D633" s="6"/>
       <c r="E633" s="6"/>
-      <c r="F633" s="9"/>
+      <c r="F633" s="10"/>
       <c r="G633" s="6"/>
       <c r="H633" s="6"/>
       <c r="I633" s="6"/>
@@ -18187,7 +18190,7 @@
       <c r="C634" s="6"/>
       <c r="D634" s="6"/>
       <c r="E634" s="6"/>
-      <c r="F634" s="9"/>
+      <c r="F634" s="10"/>
       <c r="G634" s="6"/>
       <c r="H634" s="6"/>
       <c r="I634" s="6"/>
@@ -18215,7 +18218,7 @@
       <c r="C635" s="6"/>
       <c r="D635" s="6"/>
       <c r="E635" s="6"/>
-      <c r="F635" s="9"/>
+      <c r="F635" s="10"/>
       <c r="G635" s="6"/>
       <c r="H635" s="6"/>
       <c r="I635" s="6"/>
@@ -18243,7 +18246,7 @@
       <c r="C636" s="6"/>
       <c r="D636" s="6"/>
       <c r="E636" s="6"/>
-      <c r="F636" s="9"/>
+      <c r="F636" s="10"/>
       <c r="G636" s="6"/>
       <c r="H636" s="6"/>
       <c r="I636" s="6"/>
@@ -18271,7 +18274,7 @@
       <c r="C637" s="6"/>
       <c r="D637" s="6"/>
       <c r="E637" s="6"/>
-      <c r="F637" s="9"/>
+      <c r="F637" s="10"/>
       <c r="G637" s="6"/>
       <c r="H637" s="6"/>
       <c r="I637" s="6"/>
@@ -18299,7 +18302,7 @@
       <c r="C638" s="6"/>
       <c r="D638" s="6"/>
       <c r="E638" s="6"/>
-      <c r="F638" s="9"/>
+      <c r="F638" s="10"/>
       <c r="G638" s="6"/>
       <c r="H638" s="6"/>
       <c r="I638" s="6"/>
@@ -18327,7 +18330,7 @@
       <c r="C639" s="6"/>
       <c r="D639" s="6"/>
       <c r="E639" s="6"/>
-      <c r="F639" s="9"/>
+      <c r="F639" s="10"/>
       <c r="G639" s="6"/>
       <c r="H639" s="6"/>
       <c r="I639" s="6"/>
@@ -18355,7 +18358,7 @@
       <c r="C640" s="6"/>
       <c r="D640" s="6"/>
       <c r="E640" s="6"/>
-      <c r="F640" s="9"/>
+      <c r="F640" s="10"/>
       <c r="G640" s="6"/>
       <c r="H640" s="6"/>
       <c r="I640" s="6"/>
@@ -18383,7 +18386,7 @@
       <c r="C641" s="6"/>
       <c r="D641" s="6"/>
       <c r="E641" s="6"/>
-      <c r="F641" s="9"/>
+      <c r="F641" s="10"/>
       <c r="G641" s="6"/>
       <c r="H641" s="6"/>
       <c r="I641" s="6"/>
@@ -18411,7 +18414,7 @@
       <c r="C642" s="6"/>
       <c r="D642" s="6"/>
       <c r="E642" s="6"/>
-      <c r="F642" s="9"/>
+      <c r="F642" s="10"/>
       <c r="G642" s="6"/>
       <c r="H642" s="6"/>
       <c r="I642" s="6"/>
@@ -18439,7 +18442,7 @@
       <c r="C643" s="6"/>
       <c r="D643" s="6"/>
       <c r="E643" s="6"/>
-      <c r="F643" s="9"/>
+      <c r="F643" s="10"/>
       <c r="G643" s="6"/>
       <c r="H643" s="6"/>
       <c r="I643" s="6"/>
@@ -18467,7 +18470,7 @@
       <c r="C644" s="6"/>
       <c r="D644" s="6"/>
       <c r="E644" s="6"/>
-      <c r="F644" s="9"/>
+      <c r="F644" s="10"/>
       <c r="G644" s="6"/>
       <c r="H644" s="6"/>
       <c r="I644" s="6"/>
@@ -18495,7 +18498,7 @@
       <c r="C645" s="6"/>
       <c r="D645" s="6"/>
       <c r="E645" s="6"/>
-      <c r="F645" s="9"/>
+      <c r="F645" s="10"/>
       <c r="G645" s="6"/>
       <c r="H645" s="6"/>
       <c r="I645" s="6"/>
@@ -18523,7 +18526,7 @@
       <c r="C646" s="6"/>
       <c r="D646" s="6"/>
       <c r="E646" s="6"/>
-      <c r="F646" s="9"/>
+      <c r="F646" s="10"/>
       <c r="G646" s="6"/>
       <c r="H646" s="6"/>
       <c r="I646" s="6"/>
@@ -18551,7 +18554,7 @@
       <c r="C647" s="6"/>
       <c r="D647" s="6"/>
       <c r="E647" s="6"/>
-      <c r="F647" s="9"/>
+      <c r="F647" s="10"/>
       <c r="G647" s="6"/>
       <c r="H647" s="6"/>
       <c r="I647" s="6"/>
@@ -18579,7 +18582,7 @@
       <c r="C648" s="6"/>
       <c r="D648" s="6"/>
       <c r="E648" s="6"/>
-      <c r="F648" s="9"/>
+      <c r="F648" s="10"/>
       <c r="G648" s="6"/>
       <c r="H648" s="6"/>
       <c r="I648" s="6"/>
@@ -18607,7 +18610,7 @@
       <c r="C649" s="6"/>
       <c r="D649" s="6"/>
       <c r="E649" s="6"/>
-      <c r="F649" s="9"/>
+      <c r="F649" s="10"/>
       <c r="G649" s="6"/>
       <c r="H649" s="6"/>
       <c r="I649" s="6"/>
@@ -18635,7 +18638,7 @@
       <c r="C650" s="6"/>
       <c r="D650" s="6"/>
       <c r="E650" s="6"/>
-      <c r="F650" s="9"/>
+      <c r="F650" s="10"/>
       <c r="G650" s="6"/>
       <c r="H650" s="6"/>
       <c r="I650" s="6"/>
@@ -18663,7 +18666,7 @@
       <c r="C651" s="6"/>
       <c r="D651" s="6"/>
       <c r="E651" s="6"/>
-      <c r="F651" s="9"/>
+      <c r="F651" s="10"/>
       <c r="G651" s="6"/>
       <c r="H651" s="6"/>
       <c r="I651" s="6"/>
@@ -18691,7 +18694,7 @@
       <c r="C652" s="6"/>
       <c r="D652" s="6"/>
       <c r="E652" s="6"/>
-      <c r="F652" s="9"/>
+      <c r="F652" s="10"/>
       <c r="G652" s="6"/>
       <c r="H652" s="6"/>
       <c r="I652" s="6"/>
@@ -18719,7 +18722,7 @@
       <c r="C653" s="6"/>
       <c r="D653" s="6"/>
       <c r="E653" s="6"/>
-      <c r="F653" s="9"/>
+      <c r="F653" s="10"/>
       <c r="G653" s="6"/>
       <c r="H653" s="6"/>
       <c r="I653" s="6"/>
@@ -18747,7 +18750,7 @@
       <c r="C654" s="6"/>
       <c r="D654" s="6"/>
       <c r="E654" s="6"/>
-      <c r="F654" s="9"/>
+      <c r="F654" s="10"/>
       <c r="G654" s="6"/>
       <c r="H654" s="6"/>
       <c r="I654" s="6"/>
@@ -18775,7 +18778,7 @@
       <c r="C655" s="6"/>
       <c r="D655" s="6"/>
       <c r="E655" s="6"/>
-      <c r="F655" s="9"/>
+      <c r="F655" s="10"/>
       <c r="G655" s="6"/>
       <c r="H655" s="6"/>
       <c r="I655" s="6"/>
@@ -18803,7 +18806,7 @@
       <c r="C656" s="6"/>
       <c r="D656" s="6"/>
       <c r="E656" s="6"/>
-      <c r="F656" s="9"/>
+      <c r="F656" s="10"/>
       <c r="G656" s="6"/>
       <c r="H656" s="6"/>
       <c r="I656" s="6"/>
@@ -18831,7 +18834,7 @@
       <c r="C657" s="6"/>
       <c r="D657" s="6"/>
       <c r="E657" s="6"/>
-      <c r="F657" s="9"/>
+      <c r="F657" s="10"/>
       <c r="G657" s="6"/>
       <c r="H657" s="6"/>
       <c r="I657" s="6"/>
@@ -18859,7 +18862,7 @@
       <c r="C658" s="6"/>
       <c r="D658" s="6"/>
       <c r="E658" s="6"/>
-      <c r="F658" s="9"/>
+      <c r="F658" s="10"/>
       <c r="G658" s="6"/>
       <c r="H658" s="6"/>
       <c r="I658" s="6"/>
@@ -18887,7 +18890,7 @@
       <c r="C659" s="6"/>
       <c r="D659" s="6"/>
       <c r="E659" s="6"/>
-      <c r="F659" s="9"/>
+      <c r="F659" s="10"/>
       <c r="G659" s="6"/>
       <c r="H659" s="6"/>
       <c r="I659" s="6"/>
@@ -18915,7 +18918,7 @@
       <c r="C660" s="6"/>
       <c r="D660" s="6"/>
       <c r="E660" s="6"/>
-      <c r="F660" s="9"/>
+      <c r="F660" s="10"/>
       <c r="G660" s="6"/>
       <c r="H660" s="6"/>
       <c r="I660" s="6"/>
@@ -18943,7 +18946,7 @@
       <c r="C661" s="6"/>
       <c r="D661" s="6"/>
       <c r="E661" s="6"/>
-      <c r="F661" s="9"/>
+      <c r="F661" s="10"/>
       <c r="G661" s="6"/>
       <c r="H661" s="6"/>
       <c r="I661" s="6"/>
@@ -18971,7 +18974,7 @@
       <c r="C662" s="6"/>
       <c r="D662" s="6"/>
       <c r="E662" s="6"/>
-      <c r="F662" s="9"/>
+      <c r="F662" s="10"/>
       <c r="G662" s="6"/>
       <c r="H662" s="6"/>
       <c r="I662" s="6"/>
@@ -18999,7 +19002,7 @@
       <c r="C663" s="6"/>
       <c r="D663" s="6"/>
       <c r="E663" s="6"/>
-      <c r="F663" s="9"/>
+      <c r="F663" s="10"/>
       <c r="G663" s="6"/>
       <c r="H663" s="6"/>
       <c r="I663" s="6"/>
@@ -19027,7 +19030,7 @@
       <c r="C664" s="6"/>
       <c r="D664" s="6"/>
       <c r="E664" s="6"/>
-      <c r="F664" s="9"/>
+      <c r="F664" s="10"/>
       <c r="G664" s="6"/>
       <c r="H664" s="6"/>
       <c r="I664" s="6"/>
@@ -19055,7 +19058,7 @@
       <c r="C665" s="6"/>
       <c r="D665" s="6"/>
       <c r="E665" s="6"/>
-      <c r="F665" s="9"/>
+      <c r="F665" s="10"/>
       <c r="G665" s="6"/>
       <c r="H665" s="6"/>
       <c r="I665" s="6"/>
@@ -19083,7 +19086,7 @@
       <c r="C666" s="6"/>
       <c r="D666" s="6"/>
       <c r="E666" s="6"/>
-      <c r="F666" s="9"/>
+      <c r="F666" s="10"/>
       <c r="G666" s="6"/>
       <c r="H666" s="6"/>
       <c r="I666" s="6"/>
@@ -19111,7 +19114,7 @@
       <c r="C667" s="6"/>
       <c r="D667" s="6"/>
       <c r="E667" s="6"/>
-      <c r="F667" s="9"/>
+      <c r="F667" s="10"/>
       <c r="G667" s="6"/>
       <c r="H667" s="6"/>
       <c r="I667" s="6"/>
@@ -19139,7 +19142,7 @@
       <c r="C668" s="6"/>
       <c r="D668" s="6"/>
       <c r="E668" s="6"/>
-      <c r="F668" s="9"/>
+      <c r="F668" s="10"/>
       <c r="G668" s="6"/>
       <c r="H668" s="6"/>
       <c r="I668" s="6"/>
@@ -19167,7 +19170,7 @@
       <c r="C669" s="6"/>
       <c r="D669" s="6"/>
       <c r="E669" s="6"/>
-      <c r="F669" s="9"/>
+      <c r="F669" s="10"/>
       <c r="G669" s="6"/>
       <c r="H669" s="6"/>
       <c r="I669" s="6"/>
@@ -19195,7 +19198,7 @@
       <c r="C670" s="6"/>
       <c r="D670" s="6"/>
       <c r="E670" s="6"/>
-      <c r="F670" s="9"/>
+      <c r="F670" s="10"/>
       <c r="G670" s="6"/>
       <c r="H670" s="6"/>
       <c r="I670" s="6"/>
@@ -19223,7 +19226,7 @@
       <c r="C671" s="6"/>
       <c r="D671" s="6"/>
       <c r="E671" s="6"/>
-      <c r="F671" s="9"/>
+      <c r="F671" s="10"/>
       <c r="G671" s="6"/>
       <c r="H671" s="6"/>
       <c r="I671" s="6"/>
@@ -19251,7 +19254,7 @@
       <c r="C672" s="6"/>
       <c r="D672" s="6"/>
       <c r="E672" s="6"/>
-      <c r="F672" s="9"/>
+      <c r="F672" s="10"/>
       <c r="G672" s="6"/>
       <c r="H672" s="6"/>
       <c r="I672" s="6"/>
@@ -19279,7 +19282,7 @@
       <c r="C673" s="6"/>
       <c r="D673" s="6"/>
       <c r="E673" s="6"/>
-      <c r="F673" s="9"/>
+      <c r="F673" s="10"/>
       <c r="G673" s="6"/>
       <c r="H673" s="6"/>
       <c r="I673" s="6"/>
@@ -19307,7 +19310,7 @@
       <c r="C674" s="6"/>
       <c r="D674" s="6"/>
       <c r="E674" s="6"/>
-      <c r="F674" s="9"/>
+      <c r="F674" s="10"/>
       <c r="G674" s="6"/>
       <c r="H674" s="6"/>
       <c r="I674" s="6"/>
@@ -19335,7 +19338,7 @@
       <c r="C675" s="6"/>
       <c r="D675" s="6"/>
       <c r="E675" s="6"/>
-      <c r="F675" s="9"/>
+      <c r="F675" s="10"/>
       <c r="G675" s="6"/>
       <c r="H675" s="6"/>
       <c r="I675" s="6"/>
@@ -19363,7 +19366,7 @@
       <c r="C676" s="6"/>
       <c r="D676" s="6"/>
       <c r="E676" s="6"/>
-      <c r="F676" s="9"/>
+      <c r="F676" s="10"/>
       <c r="G676" s="6"/>
       <c r="H676" s="6"/>
       <c r="I676" s="6"/>
@@ -19391,7 +19394,7 @@
       <c r="C677" s="6"/>
       <c r="D677" s="6"/>
       <c r="E677" s="6"/>
-      <c r="F677" s="9"/>
+      <c r="F677" s="10"/>
       <c r="G677" s="6"/>
       <c r="H677" s="6"/>
       <c r="I677" s="6"/>
@@ -19419,7 +19422,7 @@
       <c r="C678" s="6"/>
       <c r="D678" s="6"/>
       <c r="E678" s="6"/>
-      <c r="F678" s="9"/>
+      <c r="F678" s="10"/>
       <c r="G678" s="6"/>
       <c r="H678" s="6"/>
       <c r="I678" s="6"/>
@@ -19447,7 +19450,7 @@
       <c r="C679" s="6"/>
       <c r="D679" s="6"/>
       <c r="E679" s="6"/>
-      <c r="F679" s="9"/>
+      <c r="F679" s="10"/>
       <c r="G679" s="6"/>
       <c r="H679" s="6"/>
       <c r="I679" s="6"/>
@@ -19475,7 +19478,7 @@
       <c r="C680" s="6"/>
       <c r="D680" s="6"/>
       <c r="E680" s="6"/>
-      <c r="F680" s="9"/>
+      <c r="F680" s="10"/>
       <c r="G680" s="6"/>
       <c r="H680" s="6"/>
       <c r="I680" s="6"/>
@@ -19503,7 +19506,7 @@
       <c r="C681" s="6"/>
       <c r="D681" s="6"/>
       <c r="E681" s="6"/>
-      <c r="F681" s="9"/>
+      <c r="F681" s="10"/>
       <c r="G681" s="6"/>
       <c r="H681" s="6"/>
       <c r="I681" s="6"/>
@@ -19531,7 +19534,7 @@
       <c r="C682" s="6"/>
       <c r="D682" s="6"/>
       <c r="E682" s="6"/>
-      <c r="F682" s="9"/>
+      <c r="F682" s="10"/>
       <c r="G682" s="6"/>
       <c r="H682" s="6"/>
       <c r="I682" s="6"/>
@@ -19559,7 +19562,7 @@
       <c r="C683" s="6"/>
       <c r="D683" s="6"/>
       <c r="E683" s="6"/>
-      <c r="F683" s="9"/>
+      <c r="F683" s="10"/>
       <c r="G683" s="6"/>
       <c r="H683" s="6"/>
       <c r="I683" s="6"/>
@@ -19587,7 +19590,7 @@
       <c r="C684" s="6"/>
       <c r="D684" s="6"/>
       <c r="E684" s="6"/>
-      <c r="F684" s="9"/>
+      <c r="F684" s="10"/>
       <c r="G684" s="6"/>
       <c r="H684" s="6"/>
       <c r="I684" s="6"/>
@@ -19615,7 +19618,7 @@
       <c r="C685" s="6"/>
       <c r="D685" s="6"/>
       <c r="E685" s="6"/>
-      <c r="F685" s="9"/>
+      <c r="F685" s="10"/>
       <c r="G685" s="6"/>
       <c r="H685" s="6"/>
       <c r="I685" s="6"/>
@@ -19643,7 +19646,7 @@
       <c r="C686" s="6"/>
       <c r="D686" s="6"/>
       <c r="E686" s="6"/>
-      <c r="F686" s="9"/>
+      <c r="F686" s="10"/>
       <c r="G686" s="6"/>
       <c r="H686" s="6"/>
       <c r="I686" s="6"/>
@@ -19671,7 +19674,7 @@
       <c r="C687" s="6"/>
       <c r="D687" s="6"/>
       <c r="E687" s="6"/>
-      <c r="F687" s="9"/>
+      <c r="F687" s="10"/>
       <c r="G687" s="6"/>
       <c r="H687" s="6"/>
       <c r="I687" s="6"/>
@@ -19699,7 +19702,7 @@
       <c r="C688" s="6"/>
       <c r="D688" s="6"/>
       <c r="E688" s="6"/>
-      <c r="F688" s="9"/>
+      <c r="F688" s="10"/>
       <c r="G688" s="6"/>
       <c r="H688" s="6"/>
       <c r="I688" s="6"/>
@@ -19727,7 +19730,7 @@
       <c r="C689" s="6"/>
       <c r="D689" s="6"/>
       <c r="E689" s="6"/>
-      <c r="F689" s="9"/>
+      <c r="F689" s="10"/>
       <c r="G689" s="6"/>
       <c r="H689" s="6"/>
       <c r="I689" s="6"/>
@@ -19755,7 +19758,7 @@
       <c r="C690" s="6"/>
       <c r="D690" s="6"/>
       <c r="E690" s="6"/>
-      <c r="F690" s="9"/>
+      <c r="F690" s="10"/>
       <c r="G690" s="6"/>
       <c r="H690" s="6"/>
       <c r="I690" s="6"/>
@@ -19783,7 +19786,7 @@
       <c r="C691" s="6"/>
       <c r="D691" s="6"/>
       <c r="E691" s="6"/>
-      <c r="F691" s="9"/>
+      <c r="F691" s="10"/>
       <c r="G691" s="6"/>
       <c r="H691" s="6"/>
       <c r="I691" s="6"/>
@@ -19811,7 +19814,7 @@
       <c r="C692" s="6"/>
       <c r="D692" s="6"/>
       <c r="E692" s="6"/>
-      <c r="F692" s="9"/>
+      <c r="F692" s="10"/>
       <c r="G692" s="6"/>
       <c r="H692" s="6"/>
       <c r="I692" s="6"/>
@@ -19839,7 +19842,7 @@
       <c r="C693" s="6"/>
       <c r="D693" s="6"/>
       <c r="E693" s="6"/>
-      <c r="F693" s="9"/>
+      <c r="F693" s="10"/>
       <c r="G693" s="6"/>
       <c r="H693" s="6"/>
       <c r="I693" s="6"/>
@@ -19867,7 +19870,7 @@
       <c r="C694" s="6"/>
       <c r="D694" s="6"/>
       <c r="E694" s="6"/>
-      <c r="F694" s="9"/>
+      <c r="F694" s="10"/>
       <c r="G694" s="6"/>
       <c r="H694" s="6"/>
       <c r="I694" s="6"/>
@@ -19895,7 +19898,7 @@
       <c r="C695" s="6"/>
       <c r="D695" s="6"/>
       <c r="E695" s="6"/>
-      <c r="F695" s="9"/>
+      <c r="F695" s="10"/>
       <c r="G695" s="6"/>
       <c r="H695" s="6"/>
       <c r="I695" s="6"/>
@@ -19923,7 +19926,7 @@
       <c r="C696" s="6"/>
       <c r="D696" s="6"/>
       <c r="E696" s="6"/>
-      <c r="F696" s="9"/>
+      <c r="F696" s="10"/>
       <c r="G696" s="6"/>
       <c r="H696" s="6"/>
       <c r="I696" s="6"/>
@@ -19951,7 +19954,7 @@
       <c r="C697" s="6"/>
       <c r="D697" s="6"/>
       <c r="E697" s="6"/>
-      <c r="F697" s="9"/>
+      <c r="F697" s="10"/>
       <c r="G697" s="6"/>
       <c r="H697" s="6"/>
       <c r="I697" s="6"/>
@@ -19979,7 +19982,7 @@
       <c r="C698" s="6"/>
       <c r="D698" s="6"/>
       <c r="E698" s="6"/>
-      <c r="F698" s="9"/>
+      <c r="F698" s="10"/>
       <c r="G698" s="6"/>
       <c r="H698" s="6"/>
       <c r="I698" s="6"/>
@@ -20007,7 +20010,7 @@
       <c r="C699" s="6"/>
       <c r="D699" s="6"/>
       <c r="E699" s="6"/>
-      <c r="F699" s="9"/>
+      <c r="F699" s="10"/>
       <c r="G699" s="6"/>
       <c r="H699" s="6"/>
       <c r="I699" s="6"/>
@@ -20035,7 +20038,7 @@
       <c r="C700" s="6"/>
       <c r="D700" s="6"/>
       <c r="E700" s="6"/>
-      <c r="F700" s="9"/>
+      <c r="F700" s="10"/>
       <c r="G700" s="6"/>
       <c r="H700" s="6"/>
       <c r="I700" s="6"/>
@@ -20063,7 +20066,7 @@
       <c r="C701" s="6"/>
       <c r="D701" s="6"/>
       <c r="E701" s="6"/>
-      <c r="F701" s="9"/>
+      <c r="F701" s="10"/>
       <c r="G701" s="6"/>
       <c r="H701" s="6"/>
       <c r="I701" s="6"/>
@@ -20091,7 +20094,7 @@
       <c r="C702" s="6"/>
       <c r="D702" s="6"/>
       <c r="E702" s="6"/>
-      <c r="F702" s="9"/>
+      <c r="F702" s="10"/>
       <c r="G702" s="6"/>
       <c r="H702" s="6"/>
       <c r="I702" s="6"/>
@@ -20119,7 +20122,7 @@
       <c r="C703" s="6"/>
       <c r="D703" s="6"/>
       <c r="E703" s="6"/>
-      <c r="F703" s="9"/>
+      <c r="F703" s="10"/>
       <c r="G703" s="6"/>
       <c r="H703" s="6"/>
       <c r="I703" s="6"/>
@@ -20147,7 +20150,7 @@
       <c r="C704" s="6"/>
       <c r="D704" s="6"/>
       <c r="E704" s="6"/>
-      <c r="F704" s="9"/>
+      <c r="F704" s="10"/>
       <c r="G704" s="6"/>
       <c r="H704" s="6"/>
       <c r="I704" s="6"/>
@@ -20175,7 +20178,7 @@
       <c r="C705" s="6"/>
       <c r="D705" s="6"/>
       <c r="E705" s="6"/>
-      <c r="F705" s="9"/>
+      <c r="F705" s="10"/>
       <c r="G705" s="6"/>
       <c r="H705" s="6"/>
       <c r="I705" s="6"/>
@@ -20203,7 +20206,7 @@
       <c r="C706" s="6"/>
       <c r="D706" s="6"/>
       <c r="E706" s="6"/>
-      <c r="F706" s="9"/>
+      <c r="F706" s="10"/>
       <c r="G706" s="6"/>
       <c r="H706" s="6"/>
       <c r="I706" s="6"/>
@@ -20231,7 +20234,7 @@
       <c r="C707" s="6"/>
       <c r="D707" s="6"/>
       <c r="E707" s="6"/>
-      <c r="F707" s="9"/>
+      <c r="F707" s="10"/>
       <c r="G707" s="6"/>
       <c r="H707" s="6"/>
       <c r="I707" s="6"/>
@@ -20259,7 +20262,7 @@
       <c r="C708" s="6"/>
       <c r="D708" s="6"/>
       <c r="E708" s="6"/>
-      <c r="F708" s="9"/>
+      <c r="F708" s="10"/>
       <c r="G708" s="6"/>
       <c r="H708" s="6"/>
       <c r="I708" s="6"/>
@@ -20287,7 +20290,7 @@
       <c r="C709" s="6"/>
       <c r="D709" s="6"/>
       <c r="E709" s="6"/>
-      <c r="F709" s="9"/>
+      <c r="F709" s="10"/>
       <c r="G709" s="6"/>
       <c r="H709" s="6"/>
       <c r="I709" s="6"/>
@@ -20315,7 +20318,7 @@
       <c r="C710" s="6"/>
       <c r="D710" s="6"/>
       <c r="E710" s="6"/>
-      <c r="F710" s="9"/>
+      <c r="F710" s="10"/>
       <c r="G710" s="6"/>
       <c r="H710" s="6"/>
       <c r="I710" s="6"/>
@@ -20343,7 +20346,7 @@
       <c r="C711" s="6"/>
       <c r="D711" s="6"/>
       <c r="E711" s="6"/>
-      <c r="F711" s="9"/>
+      <c r="F711" s="10"/>
       <c r="G711" s="6"/>
       <c r="H711" s="6"/>
       <c r="I711" s="6"/>
@@ -20371,7 +20374,7 @@
       <c r="C712" s="6"/>
       <c r="D712" s="6"/>
       <c r="E712" s="6"/>
-      <c r="F712" s="9"/>
+      <c r="F712" s="10"/>
       <c r="G712" s="6"/>
       <c r="H712" s="6"/>
       <c r="I712" s="6"/>
@@ -20399,7 +20402,7 @@
       <c r="C713" s="6"/>
       <c r="D713" s="6"/>
       <c r="E713" s="6"/>
-      <c r="F713" s="9"/>
+      <c r="F713" s="10"/>
       <c r="G713" s="6"/>
       <c r="H713" s="6"/>
       <c r="I713" s="6"/>
@@ -20427,7 +20430,7 @@
       <c r="C714" s="6"/>
       <c r="D714" s="6"/>
       <c r="E714" s="6"/>
-      <c r="F714" s="9"/>
+      <c r="F714" s="10"/>
       <c r="G714" s="6"/>
       <c r="H714" s="6"/>
       <c r="I714" s="6"/>
@@ -20455,7 +20458,7 @@
       <c r="C715" s="6"/>
       <c r="D715" s="6"/>
       <c r="E715" s="6"/>
-      <c r="F715" s="9"/>
+      <c r="F715" s="10"/>
       <c r="G715" s="6"/>
       <c r="H715" s="6"/>
       <c r="I715" s="6"/>
@@ -20483,7 +20486,7 @@
       <c r="C716" s="6"/>
       <c r="D716" s="6"/>
       <c r="E716" s="6"/>
-      <c r="F716" s="9"/>
+      <c r="F716" s="10"/>
       <c r="G716" s="6"/>
       <c r="H716" s="6"/>
       <c r="I716" s="6"/>
@@ -20511,7 +20514,7 @@
       <c r="C717" s="6"/>
       <c r="D717" s="6"/>
       <c r="E717" s="6"/>
-      <c r="F717" s="9"/>
+      <c r="F717" s="10"/>
       <c r="G717" s="6"/>
       <c r="H717" s="6"/>
       <c r="I717" s="6"/>
@@ -20539,7 +20542,7 @@
       <c r="C718" s="6"/>
       <c r="D718" s="6"/>
       <c r="E718" s="6"/>
-      <c r="F718" s="9"/>
+      <c r="F718" s="10"/>
       <c r="G718" s="6"/>
       <c r="H718" s="6"/>
       <c r="I718" s="6"/>
@@ -20567,7 +20570,7 @@
       <c r="C719" s="6"/>
       <c r="D719" s="6"/>
       <c r="E719" s="6"/>
-      <c r="F719" s="9"/>
+      <c r="F719" s="10"/>
       <c r="G719" s="6"/>
       <c r="H719" s="6"/>
       <c r="I719" s="6"/>
@@ -20595,7 +20598,7 @@
       <c r="C720" s="6"/>
       <c r="D720" s="6"/>
       <c r="E720" s="6"/>
-      <c r="F720" s="9"/>
+      <c r="F720" s="10"/>
       <c r="G720" s="6"/>
       <c r="H720" s="6"/>
       <c r="I720" s="6"/>
@@ -20623,7 +20626,7 @@
       <c r="C721" s="6"/>
       <c r="D721" s="6"/>
       <c r="E721" s="6"/>
-      <c r="F721" s="9"/>
+      <c r="F721" s="10"/>
       <c r="G721" s="6"/>
       <c r="H721" s="6"/>
       <c r="I721" s="6"/>
@@ -20651,7 +20654,7 @@
       <c r="C722" s="6"/>
       <c r="D722" s="6"/>
       <c r="E722" s="6"/>
-      <c r="F722" s="9"/>
+      <c r="F722" s="10"/>
       <c r="G722" s="6"/>
       <c r="H722" s="6"/>
       <c r="I722" s="6"/>
@@ -20679,7 +20682,7 @@
       <c r="C723" s="6"/>
       <c r="D723" s="6"/>
       <c r="E723" s="6"/>
-      <c r="F723" s="9"/>
+      <c r="F723" s="10"/>
       <c r="G723" s="6"/>
       <c r="H723" s="6"/>
       <c r="I723" s="6"/>
@@ -20707,7 +20710,7 @@
       <c r="C724" s="6"/>
       <c r="D724" s="6"/>
       <c r="E724" s="6"/>
-      <c r="F724" s="9"/>
+      <c r="F724" s="10"/>
       <c r="G724" s="6"/>
       <c r="H724" s="6"/>
       <c r="I724" s="6"/>
@@ -20735,7 +20738,7 @@
       <c r="C725" s="6"/>
       <c r="D725" s="6"/>
       <c r="E725" s="6"/>
-      <c r="F725" s="9"/>
+      <c r="F725" s="10"/>
       <c r="G725" s="6"/>
       <c r="H725" s="6"/>
       <c r="I725" s="6"/>
@@ -20763,7 +20766,7 @@
       <c r="C726" s="6"/>
       <c r="D726" s="6"/>
       <c r="E726" s="6"/>
-      <c r="F726" s="9"/>
+      <c r="F726" s="10"/>
       <c r="G726" s="6"/>
       <c r="H726" s="6"/>
       <c r="I726" s="6"/>
@@ -20791,7 +20794,7 @@
       <c r="C727" s="6"/>
       <c r="D727" s="6"/>
       <c r="E727" s="6"/>
-      <c r="F727" s="9"/>
+      <c r="F727" s="10"/>
       <c r="G727" s="6"/>
       <c r="H727" s="6"/>
       <c r="I727" s="6"/>
@@ -20819,7 +20822,7 @@
       <c r="C728" s="6"/>
       <c r="D728" s="6"/>
       <c r="E728" s="6"/>
-      <c r="F728" s="9"/>
+      <c r="F728" s="10"/>
       <c r="G728" s="6"/>
       <c r="H728" s="6"/>
       <c r="I728" s="6"/>
@@ -20847,7 +20850,7 @@
       <c r="C729" s="6"/>
       <c r="D729" s="6"/>
       <c r="E729" s="6"/>
-      <c r="F729" s="9"/>
+      <c r="F729" s="10"/>
       <c r="G729" s="6"/>
       <c r="H729" s="6"/>
       <c r="I729" s="6"/>
@@ -20875,7 +20878,7 @@
       <c r="C730" s="6"/>
       <c r="D730" s="6"/>
       <c r="E730" s="6"/>
-      <c r="F730" s="9"/>
+      <c r="F730" s="10"/>
       <c r="G730" s="6"/>
       <c r="H730" s="6"/>
       <c r="I730" s="6"/>
@@ -20903,7 +20906,7 @@
       <c r="C731" s="6"/>
       <c r="D731" s="6"/>
       <c r="E731" s="6"/>
-      <c r="F731" s="9"/>
+      <c r="F731" s="10"/>
       <c r="G731" s="6"/>
       <c r="H731" s="6"/>
       <c r="I731" s="6"/>
@@ -20931,7 +20934,7 @@
       <c r="C732" s="6"/>
       <c r="D732" s="6"/>
       <c r="E732" s="6"/>
-      <c r="F732" s="9"/>
+      <c r="F732" s="10"/>
       <c r="G732" s="6"/>
       <c r="H732" s="6"/>
       <c r="I732" s="6"/>
@@ -20959,7 +20962,7 @@
       <c r="C733" s="6"/>
       <c r="D733" s="6"/>
       <c r="E733" s="6"/>
-      <c r="F733" s="9"/>
+      <c r="F733" s="10"/>
       <c r="G733" s="6"/>
       <c r="H733" s="6"/>
       <c r="I733" s="6"/>
@@ -20987,7 +20990,7 @@
       <c r="C734" s="6"/>
       <c r="D734" s="6"/>
       <c r="E734" s="6"/>
-      <c r="F734" s="9"/>
+      <c r="F734" s="10"/>
       <c r="G734" s="6"/>
       <c r="H734" s="6"/>
       <c r="I734" s="6"/>
@@ -21015,7 +21018,7 @@
       <c r="C735" s="6"/>
       <c r="D735" s="6"/>
       <c r="E735" s="6"/>
-      <c r="F735" s="9"/>
+      <c r="F735" s="10"/>
       <c r="G735" s="6"/>
       <c r="H735" s="6"/>
       <c r="I735" s="6"/>
@@ -21043,7 +21046,7 @@
       <c r="C736" s="6"/>
       <c r="D736" s="6"/>
       <c r="E736" s="6"/>
-      <c r="F736" s="9"/>
+      <c r="F736" s="10"/>
       <c r="G736" s="6"/>
       <c r="H736" s="6"/>
       <c r="I736" s="6"/>
@@ -21071,7 +21074,7 @@
       <c r="C737" s="6"/>
       <c r="D737" s="6"/>
       <c r="E737" s="6"/>
-      <c r="F737" s="9"/>
+      <c r="F737" s="10"/>
       <c r="G737" s="6"/>
       <c r="H737" s="6"/>
       <c r="I737" s="6"/>
@@ -21099,7 +21102,7 @@
       <c r="C738" s="6"/>
       <c r="D738" s="6"/>
       <c r="E738" s="6"/>
-      <c r="F738" s="9"/>
+      <c r="F738" s="10"/>
       <c r="G738" s="6"/>
       <c r="H738" s="6"/>
       <c r="I738" s="6"/>
@@ -21127,7 +21130,7 @@
       <c r="C739" s="6"/>
       <c r="D739" s="6"/>
       <c r="E739" s="6"/>
-      <c r="F739" s="9"/>
+      <c r="F739" s="10"/>
       <c r="G739" s="6"/>
       <c r="H739" s="6"/>
       <c r="I739" s="6"/>
@@ -21155,7 +21158,7 @@
       <c r="C740" s="6"/>
       <c r="D740" s="6"/>
       <c r="E740" s="6"/>
-      <c r="F740" s="9"/>
+      <c r="F740" s="10"/>
       <c r="G740" s="6"/>
       <c r="H740" s="6"/>
       <c r="I740" s="6"/>
@@ -21183,7 +21186,7 @@
       <c r="C741" s="6"/>
       <c r="D741" s="6"/>
       <c r="E741" s="6"/>
-      <c r="F741" s="9"/>
+      <c r="F741" s="10"/>
       <c r="G741" s="6"/>
       <c r="H741" s="6"/>
       <c r="I741" s="6"/>
@@ -21211,7 +21214,7 @@
       <c r="C742" s="6"/>
       <c r="D742" s="6"/>
       <c r="E742" s="6"/>
-      <c r="F742" s="9"/>
+      <c r="F742" s="10"/>
       <c r="G742" s="6"/>
       <c r="H742" s="6"/>
       <c r="I742" s="6"/>
@@ -21239,7 +21242,7 @@
       <c r="C743" s="6"/>
       <c r="D743" s="6"/>
       <c r="E743" s="6"/>
-      <c r="F743" s="9"/>
+      <c r="F743" s="10"/>
       <c r="G743" s="6"/>
       <c r="H743" s="6"/>
       <c r="I743" s="6"/>
@@ -21267,7 +21270,7 @@
       <c r="C744" s="6"/>
       <c r="D744" s="6"/>
       <c r="E744" s="6"/>
-      <c r="F744" s="9"/>
+      <c r="F744" s="10"/>
       <c r="G744" s="6"/>
       <c r="H744" s="6"/>
       <c r="I744" s="6"/>
@@ -21295,7 +21298,7 @@
       <c r="C745" s="6"/>
       <c r="D745" s="6"/>
       <c r="E745" s="6"/>
-      <c r="F745" s="9"/>
+      <c r="F745" s="10"/>
       <c r="G745" s="6"/>
       <c r="H745" s="6"/>
       <c r="I745" s="6"/>
@@ -21323,7 +21326,7 @@
       <c r="C746" s="6"/>
       <c r="D746" s="6"/>
       <c r="E746" s="6"/>
-      <c r="F746" s="9"/>
+      <c r="F746" s="10"/>
       <c r="G746" s="6"/>
       <c r="H746" s="6"/>
       <c r="I746" s="6"/>
@@ -21351,7 +21354,7 @@
       <c r="C747" s="6"/>
       <c r="D747" s="6"/>
       <c r="E747" s="6"/>
-      <c r="F747" s="9"/>
+      <c r="F747" s="10"/>
       <c r="G747" s="6"/>
       <c r="H747" s="6"/>
       <c r="I747" s="6"/>
@@ -21379,7 +21382,7 @@
       <c r="C748" s="6"/>
       <c r="D748" s="6"/>
       <c r="E748" s="6"/>
-      <c r="F748" s="9"/>
+      <c r="F748" s="10"/>
       <c r="G748" s="6"/>
       <c r="H748" s="6"/>
       <c r="I748" s="6"/>
@@ -21407,7 +21410,7 @@
       <c r="C749" s="6"/>
       <c r="D749" s="6"/>
       <c r="E749" s="6"/>
-      <c r="F749" s="9"/>
+      <c r="F749" s="10"/>
       <c r="G749" s="6"/>
       <c r="H749" s="6"/>
       <c r="I749" s="6"/>
@@ -21435,7 +21438,7 @@
       <c r="C750" s="6"/>
       <c r="D750" s="6"/>
       <c r="E750" s="6"/>
-      <c r="F750" s="9"/>
+      <c r="F750" s="10"/>
       <c r="G750" s="6"/>
       <c r="H750" s="6"/>
       <c r="I750" s="6"/>
@@ -21463,7 +21466,7 @@
       <c r="C751" s="6"/>
       <c r="D751" s="6"/>
       <c r="E751" s="6"/>
-      <c r="F751" s="9"/>
+      <c r="F751" s="10"/>
       <c r="G751" s="6"/>
       <c r="H751" s="6"/>
       <c r="I751" s="6"/>
@@ -21491,7 +21494,7 @@
       <c r="C752" s="6"/>
       <c r="D752" s="6"/>
       <c r="E752" s="6"/>
-      <c r="F752" s="9"/>
+      <c r="F752" s="10"/>
       <c r="G752" s="6"/>
       <c r="H752" s="6"/>
       <c r="I752" s="6"/>
@@ -21519,7 +21522,7 @@
       <c r="C753" s="6"/>
       <c r="D753" s="6"/>
       <c r="E753" s="6"/>
-      <c r="F753" s="9"/>
+      <c r="F753" s="10"/>
       <c r="G753" s="6"/>
       <c r="H753" s="6"/>
       <c r="I753" s="6"/>
@@ -21547,7 +21550,7 @@
       <c r="C754" s="6"/>
       <c r="D754" s="6"/>
       <c r="E754" s="6"/>
-      <c r="F754" s="9"/>
+      <c r="F754" s="10"/>
       <c r="G754" s="6"/>
       <c r="H754" s="6"/>
       <c r="I754" s="6"/>
@@ -21575,7 +21578,7 @@
       <c r="C755" s="6"/>
       <c r="D755" s="6"/>
       <c r="E755" s="6"/>
-      <c r="F755" s="9"/>
+      <c r="F755" s="10"/>
       <c r="G755" s="6"/>
       <c r="H755" s="6"/>
       <c r="I755" s="6"/>
@@ -21603,7 +21606,7 @@
       <c r="C756" s="6"/>
       <c r="D756" s="6"/>
       <c r="E756" s="6"/>
-      <c r="F756" s="9"/>
+      <c r="F756" s="10"/>
       <c r="G756" s="6"/>
       <c r="H756" s="6"/>
       <c r="I756" s="6"/>
@@ -21631,7 +21634,7 @@
       <c r="C757" s="6"/>
       <c r="D757" s="6"/>
       <c r="E757" s="6"/>
-      <c r="F757" s="9"/>
+      <c r="F757" s="10"/>
       <c r="G757" s="6"/>
       <c r="H757" s="6"/>
       <c r="I757" s="6"/>
@@ -21659,7 +21662,7 @@
       <c r="C758" s="6"/>
       <c r="D758" s="6"/>
       <c r="E758" s="6"/>
-      <c r="F758" s="9"/>
+      <c r="F758" s="10"/>
       <c r="G758" s="6"/>
       <c r="H758" s="6"/>
       <c r="I758" s="6"/>
@@ -21687,7 +21690,7 @@
       <c r="C759" s="6"/>
       <c r="D759" s="6"/>
       <c r="E759" s="6"/>
-      <c r="F759" s="9"/>
+      <c r="F759" s="10"/>
       <c r="G759" s="6"/>
       <c r="H759" s="6"/>
       <c r="I759" s="6"/>
@@ -21715,7 +21718,7 @@
       <c r="C760" s="6"/>
       <c r="D760" s="6"/>
       <c r="E760" s="6"/>
-      <c r="F760" s="9"/>
+      <c r="F760" s="10"/>
       <c r="G760" s="6"/>
       <c r="H760" s="6"/>
       <c r="I760" s="6"/>
@@ -21743,7 +21746,7 @@
       <c r="C761" s="6"/>
       <c r="D761" s="6"/>
       <c r="E761" s="6"/>
-      <c r="F761" s="9"/>
+      <c r="F761" s="10"/>
       <c r="G761" s="6"/>
       <c r="H761" s="6"/>
       <c r="I761" s="6"/>
@@ -21771,7 +21774,7 @@
       <c r="C762" s="6"/>
       <c r="D762" s="6"/>
       <c r="E762" s="6"/>
-      <c r="F762" s="9"/>
+      <c r="F762" s="10"/>
       <c r="G762" s="6"/>
       <c r="H762" s="6"/>
       <c r="I762" s="6"/>
@@ -21799,7 +21802,7 @@
       <c r="C763" s="6"/>
       <c r="D763" s="6"/>
       <c r="E763" s="6"/>
-      <c r="F763" s="9"/>
+      <c r="F763" s="10"/>
       <c r="G763" s="6"/>
       <c r="H763" s="6"/>
       <c r="I763" s="6"/>
@@ -21827,7 +21830,7 @@
       <c r="C764" s="6"/>
       <c r="D764" s="6"/>
       <c r="E764" s="6"/>
-      <c r="F764" s="9"/>
+      <c r="F764" s="10"/>
       <c r="G764" s="6"/>
       <c r="H764" s="6"/>
       <c r="I764" s="6"/>
@@ -21855,7 +21858,7 @@
       <c r="C765" s="6"/>
       <c r="D765" s="6"/>
       <c r="E765" s="6"/>
-      <c r="F765" s="9"/>
+      <c r="F765" s="10"/>
       <c r="G765" s="6"/>
       <c r="H765" s="6"/>
       <c r="I765" s="6"/>
@@ -21883,7 +21886,7 @@
       <c r="C766" s="6"/>
       <c r="D766" s="6"/>
       <c r="E766" s="6"/>
-      <c r="F766" s="9"/>
+      <c r="F766" s="10"/>
       <c r="G766" s="6"/>
       <c r="H766" s="6"/>
       <c r="I766" s="6"/>
@@ -21911,7 +21914,7 @@
       <c r="C767" s="6"/>
       <c r="D767" s="6"/>
       <c r="E767" s="6"/>
-      <c r="F767" s="9"/>
+      <c r="F767" s="10"/>
       <c r="G767" s="6"/>
       <c r="H767" s="6"/>
       <c r="I767" s="6"/>
@@ -21939,7 +21942,7 @@
       <c r="C768" s="6"/>
       <c r="D768" s="6"/>
       <c r="E768" s="6"/>
-      <c r="F768" s="9"/>
+      <c r="F768" s="10"/>
       <c r="G768" s="6"/>
       <c r="H768" s="6"/>
       <c r="I768" s="6"/>
@@ -21967,7 +21970,7 @@
       <c r="C769" s="6"/>
       <c r="D769" s="6"/>
       <c r="E769" s="6"/>
-      <c r="F769" s="9"/>
+      <c r="F769" s="10"/>
       <c r="G769" s="6"/>
       <c r="H769" s="6"/>
       <c r="I769" s="6"/>
@@ -21995,7 +21998,7 @@
       <c r="C770" s="6"/>
       <c r="D770" s="6"/>
       <c r="E770" s="6"/>
-      <c r="F770" s="9"/>
+      <c r="F770" s="10"/>
       <c r="G770" s="6"/>
       <c r="H770" s="6"/>
       <c r="I770" s="6"/>
@@ -22023,7 +22026,7 @@
       <c r="C771" s="6"/>
       <c r="D771" s="6"/>
       <c r="E771" s="6"/>
-      <c r="F771" s="9"/>
+      <c r="F771" s="10"/>
       <c r="G771" s="6"/>
       <c r="H771" s="6"/>
       <c r="I771" s="6"/>
@@ -22051,7 +22054,7 @@
       <c r="C772" s="6"/>
       <c r="D772" s="6"/>
       <c r="E772" s="6"/>
-      <c r="F772" s="9"/>
+      <c r="F772" s="10"/>
       <c r="G772" s="6"/>
       <c r="H772" s="6"/>
       <c r="I772" s="6"/>
@@ -22079,7 +22082,7 @@
       <c r="C773" s="6"/>
       <c r="D773" s="6"/>
       <c r="E773" s="6"/>
-      <c r="F773" s="9"/>
+      <c r="F773" s="10"/>
       <c r="G773" s="6"/>
       <c r="H773" s="6"/>
       <c r="I773" s="6"/>
@@ -22107,7 +22110,7 @@
       <c r="C774" s="6"/>
       <c r="D774" s="6"/>
       <c r="E774" s="6"/>
-      <c r="F774" s="9"/>
+      <c r="F774" s="10"/>
       <c r="G774" s="6"/>
       <c r="H774" s="6"/>
       <c r="I774" s="6"/>
@@ -22135,7 +22138,7 @@
       <c r="C775" s="6"/>
       <c r="D775" s="6"/>
       <c r="E775" s="6"/>
-      <c r="F775" s="9"/>
+      <c r="F775" s="10"/>
       <c r="G775" s="6"/>
       <c r="H775" s="6"/>
       <c r="I775" s="6"/>
@@ -22163,7 +22166,7 @@
       <c r="C776" s="6"/>
       <c r="D776" s="6"/>
       <c r="E776" s="6"/>
-      <c r="F776" s="9"/>
+      <c r="F776" s="10"/>
       <c r="G776" s="6"/>
       <c r="H776" s="6"/>
       <c r="I776" s="6"/>
@@ -22191,7 +22194,7 @@
       <c r="C777" s="6"/>
       <c r="D777" s="6"/>
       <c r="E777" s="6"/>
-      <c r="F777" s="9"/>
+      <c r="F777" s="10"/>
       <c r="G777" s="6"/>
       <c r="H777" s="6"/>
       <c r="I777" s="6"/>
@@ -22219,7 +22222,7 @@
       <c r="C778" s="6"/>
       <c r="D778" s="6"/>
       <c r="E778" s="6"/>
-      <c r="F778" s="9"/>
+      <c r="F778" s="10"/>
       <c r="G778" s="6"/>
       <c r="H778" s="6"/>
       <c r="I778" s="6"/>
@@ -22247,7 +22250,7 @@
       <c r="C779" s="6"/>
       <c r="D779" s="6"/>
       <c r="E779" s="6"/>
-      <c r="F779" s="9"/>
+      <c r="F779" s="10"/>
       <c r="G779" s="6"/>
       <c r="H779" s="6"/>
       <c r="I779" s="6"/>
@@ -22275,7 +22278,7 @@
       <c r="C780" s="6"/>
       <c r="D780" s="6"/>
       <c r="E780" s="6"/>
-      <c r="F780" s="9"/>
+      <c r="F780" s="10"/>
       <c r="G780" s="6"/>
       <c r="H780" s="6"/>
       <c r="I780" s="6"/>
@@ -22303,7 +22306,7 @@
       <c r="C781" s="6"/>
       <c r="D781" s="6"/>
       <c r="E781" s="6"/>
-      <c r="F781" s="9"/>
+      <c r="F781" s="10"/>
       <c r="G781" s="6"/>
       <c r="H781" s="6"/>
       <c r="I781" s="6"/>
@@ -22331,7 +22334,7 @@
       <c r="C782" s="6"/>
       <c r="D782" s="6"/>
       <c r="E782" s="6"/>
-      <c r="F782" s="9"/>
+      <c r="F782" s="10"/>
       <c r="G782" s="6"/>
       <c r="H782" s="6"/>
       <c r="I782" s="6"/>
@@ -22359,7 +22362,7 @@
       <c r="C783" s="6"/>
       <c r="D783" s="6"/>
       <c r="E783" s="6"/>
-      <c r="F783" s="9"/>
+      <c r="F783" s="10"/>
       <c r="G783" s="6"/>
       <c r="H783" s="6"/>
       <c r="I783" s="6"/>
@@ -22387,7 +22390,7 @@
       <c r="C784" s="6"/>
       <c r="D784" s="6"/>
       <c r="E784" s="6"/>
-      <c r="F784" s="9"/>
+      <c r="F784" s="10"/>
       <c r="G784" s="6"/>
       <c r="H784" s="6"/>
       <c r="I784" s="6"/>
@@ -22415,7 +22418,7 @@
       <c r="C785" s="6"/>
       <c r="D785" s="6"/>
       <c r="E785" s="6"/>
-      <c r="F785" s="9"/>
+      <c r="F785" s="10"/>
       <c r="G785" s="6"/>
       <c r="H785" s="6"/>
       <c r="I785" s="6"/>
@@ -22443,7 +22446,7 @@
       <c r="C786" s="6"/>
       <c r="D786" s="6"/>
       <c r="E786" s="6"/>
-      <c r="F786" s="9"/>
+      <c r="F786" s="10"/>
       <c r="G786" s="6"/>
       <c r="H786" s="6"/>
       <c r="I786" s="6"/>
@@ -22471,7 +22474,7 @@
       <c r="C787" s="6"/>
       <c r="D787" s="6"/>
       <c r="E787" s="6"/>
-      <c r="F787" s="9"/>
+      <c r="F787" s="10"/>
       <c r="G787" s="6"/>
       <c r="H787" s="6"/>
       <c r="I787" s="6"/>
@@ -22499,7 +22502,7 @@
       <c r="C788" s="6"/>
       <c r="D788" s="6"/>
       <c r="E788" s="6"/>
-      <c r="F788" s="9"/>
+      <c r="F788" s="10"/>
       <c r="G788" s="6"/>
       <c r="H788" s="6"/>
       <c r="I788" s="6"/>
@@ -22527,7 +22530,7 @@
       <c r="C789" s="6"/>
       <c r="D789" s="6"/>
       <c r="E789" s="6"/>
-      <c r="F789" s="9"/>
+      <c r="F789" s="10"/>
       <c r="G789" s="6"/>
       <c r="H789" s="6"/>
       <c r="I789" s="6"/>
@@ -22555,7 +22558,7 @@
       <c r="C790" s="6"/>
       <c r="D790" s="6"/>
       <c r="E790" s="6"/>
-      <c r="F790" s="9"/>
+      <c r="F790" s="10"/>
       <c r="G790" s="6"/>
       <c r="H790" s="6"/>
       <c r="I790" s="6"/>
@@ -22583,7 +22586,7 @@
       <c r="C791" s="6"/>
       <c r="D791" s="6"/>
       <c r="E791" s="6"/>
-      <c r="F791" s="9"/>
+      <c r="F791" s="10"/>
       <c r="G791" s="6"/>
       <c r="H791" s="6"/>
       <c r="I791" s="6"/>
@@ -22611,7 +22614,7 @@
       <c r="C792" s="6"/>
       <c r="D792" s="6"/>
       <c r="E792" s="6"/>
-      <c r="F792" s="9"/>
+      <c r="F792" s="10"/>
       <c r="G792" s="6"/>
       <c r="H792" s="6"/>
       <c r="I792" s="6"/>
@@ -22639,7 +22642,7 @@
       <c r="C793" s="6"/>
       <c r="D793" s="6"/>
       <c r="E793" s="6"/>
-      <c r="F793" s="9"/>
+      <c r="F793" s="10"/>
       <c r="G793" s="6"/>
       <c r="H793" s="6"/>
       <c r="I793" s="6"/>
@@ -22667,7 +22670,7 @@
       <c r="C794" s="6"/>
       <c r="D794" s="6"/>
       <c r="E794" s="6"/>
-      <c r="F794" s="9"/>
+      <c r="F794" s="10"/>
       <c r="G794" s="6"/>
       <c r="H794" s="6"/>
       <c r="I794" s="6"/>
@@ -22695,7 +22698,7 @@
       <c r="C795" s="6"/>
       <c r="D795" s="6"/>
       <c r="E795" s="6"/>
-      <c r="F795" s="9"/>
+      <c r="F795" s="10"/>
       <c r="G795" s="6"/>
       <c r="H795" s="6"/>
       <c r="I795" s="6"/>
@@ -22723,7 +22726,7 @@
       <c r="C796" s="6"/>
       <c r="D796" s="6"/>
       <c r="E796" s="6"/>
-      <c r="F796" s="9"/>
+      <c r="F796" s="10"/>
       <c r="G796" s="6"/>
       <c r="H796" s="6"/>
       <c r="I796" s="6"/>
@@ -22751,7 +22754,7 @@
       <c r="C797" s="6"/>
       <c r="D797" s="6"/>
       <c r="E797" s="6"/>
-      <c r="F797" s="9"/>
+      <c r="F797" s="10"/>
       <c r="G797" s="6"/>
       <c r="H797" s="6"/>
       <c r="I797" s="6"/>
@@ -22779,7 +22782,7 @@
       <c r="C798" s="6"/>
       <c r="D798" s="6"/>
       <c r="E798" s="6"/>
-      <c r="F798" s="9"/>
+      <c r="F798" s="10"/>
       <c r="G798" s="6"/>
       <c r="H798" s="6"/>
       <c r="I798" s="6"/>
@@ -22807,7 +22810,7 @@
       <c r="C799" s="6"/>
       <c r="D799" s="6"/>
       <c r="E799" s="6"/>
-      <c r="F799" s="9"/>
+      <c r="F799" s="10"/>
       <c r="G799" s="6"/>
       <c r="H799" s="6"/>
       <c r="I799" s="6"/>
@@ -22835,7 +22838,7 @@
       <c r="C800" s="6"/>
       <c r="D800" s="6"/>
       <c r="E800" s="6"/>
-      <c r="F800" s="9"/>
+      <c r="F800" s="10"/>
       <c r="G800" s="6"/>
       <c r="H800" s="6"/>
       <c r="I800" s="6"/>
@@ -22863,7 +22866,7 @@
       <c r="C801" s="6"/>
       <c r="D801" s="6"/>
       <c r="E801" s="6"/>
-      <c r="F801" s="9"/>
+      <c r="F801" s="10"/>
       <c r="G801" s="6"/>
       <c r="H801" s="6"/>
       <c r="I801" s="6"/>
@@ -22891,7 +22894,7 @@
       <c r="C802" s="6"/>
       <c r="D802" s="6"/>
       <c r="E802" s="6"/>
-      <c r="F802" s="9"/>
+      <c r="F802" s="10"/>
       <c r="G802" s="6"/>
       <c r="H802" s="6"/>
       <c r="I802" s="6"/>
@@ -22919,7 +22922,7 @@
       <c r="C803" s="6"/>
       <c r="D803" s="6"/>
       <c r="E803" s="6"/>
-      <c r="F803" s="9"/>
+      <c r="F803" s="10"/>
       <c r="G803" s="6"/>
       <c r="H803" s="6"/>
       <c r="I803" s="6"/>
@@ -22947,7 +22950,7 @@
       <c r="C804" s="6"/>
       <c r="D804" s="6"/>
       <c r="E804" s="6"/>
-      <c r="F804" s="9"/>
+      <c r="F804" s="10"/>
       <c r="G804" s="6"/>
       <c r="H804" s="6"/>
       <c r="I804" s="6"/>
@@ -22975,7 +22978,7 @@
       <c r="C805" s="6"/>
       <c r="D805" s="6"/>
       <c r="E805" s="6"/>
-      <c r="F805" s="9"/>
+      <c r="F805" s="10"/>
       <c r="G805" s="6"/>
       <c r="H805" s="6"/>
       <c r="I805" s="6"/>
@@ -23003,7 +23006,7 @@
       <c r="C806" s="6"/>
       <c r="D806" s="6"/>
       <c r="E806" s="6"/>
-      <c r="F806" s="9"/>
+      <c r="F806" s="10"/>
       <c r="G806" s="6"/>
       <c r="H806" s="6"/>
       <c r="I806" s="6"/>
@@ -23031,7 +23034,7 @@
       <c r="C807" s="6"/>
       <c r="D807" s="6"/>
       <c r="E807" s="6"/>
-      <c r="F807" s="9"/>
+      <c r="F807" s="10"/>
       <c r="G807" s="6"/>
       <c r="H807" s="6"/>
       <c r="I807" s="6"/>
@@ -23059,7 +23062,7 @@
       <c r="C808" s="6"/>
       <c r="D808" s="6"/>
       <c r="E808" s="6"/>
-      <c r="F808" s="9"/>
+      <c r="F808" s="10"/>
       <c r="G808" s="6"/>
       <c r="H808" s="6"/>
       <c r="I808" s="6"/>
@@ -23087,7 +23090,7 @@
       <c r="C809" s="6"/>
       <c r="D809" s="6"/>
       <c r="E809" s="6"/>
-      <c r="F809" s="9"/>
+      <c r="F809" s="10"/>
       <c r="G809" s="6"/>
       <c r="H809" s="6"/>
       <c r="I809" s="6"/>
@@ -23115,7 +23118,7 @@
       <c r="C810" s="6"/>
       <c r="D810" s="6"/>
       <c r="E810" s="6"/>
-      <c r="F810" s="9"/>
+      <c r="F810" s="10"/>
       <c r="G810" s="6"/>
       <c r="H810" s="6"/>
       <c r="I810" s="6"/>
@@ -23143,7 +23146,7 @@
       <c r="C811" s="6"/>
       <c r="D811" s="6"/>
       <c r="E811" s="6"/>
-      <c r="F811" s="9"/>
+      <c r="F811" s="10"/>
       <c r="G811" s="6"/>
       <c r="H811" s="6"/>
       <c r="I811" s="6"/>
@@ -23171,7 +23174,7 @@
       <c r="C812" s="6"/>
       <c r="D812" s="6"/>
       <c r="E812" s="6"/>
-      <c r="F812" s="9"/>
+      <c r="F812" s="10"/>
       <c r="G812" s="6"/>
       <c r="H812" s="6"/>
       <c r="I812" s="6"/>
@@ -23199,7 +23202,7 @@
       <c r="C813" s="6"/>
       <c r="D813" s="6"/>
       <c r="E813" s="6"/>
-      <c r="F813" s="9"/>
+      <c r="F813" s="10"/>
       <c r="G813" s="6"/>
       <c r="H813" s="6"/>
       <c r="I813" s="6"/>
@@ -23227,7 +23230,7 @@
       <c r="C814" s="6"/>
       <c r="D814" s="6"/>
       <c r="E814" s="6"/>
-      <c r="F814" s="9"/>
+      <c r="F814" s="10"/>
       <c r="G814" s="6"/>
       <c r="H814" s="6"/>
       <c r="I814" s="6"/>
@@ -23255,7 +23258,7 @@
       <c r="C815" s="6"/>
       <c r="D815" s="6"/>
       <c r="E815" s="6"/>
-      <c r="F815" s="9"/>
+      <c r="F815" s="10"/>
       <c r="G815" s="6"/>
       <c r="H815" s="6"/>
       <c r="I815" s="6"/>
@@ -23283,7 +23286,7 @@
       <c r="C816" s="6"/>
       <c r="D816" s="6"/>
       <c r="E816" s="6"/>
-      <c r="F816" s="9"/>
+      <c r="F816" s="10"/>
       <c r="G816" s="6"/>
       <c r="H816" s="6"/>
       <c r="I816" s="6"/>
@@ -23311,7 +23314,7 @@
       <c r="C817" s="6"/>
       <c r="D817" s="6"/>
       <c r="E817" s="6"/>
-      <c r="F817" s="9"/>
+      <c r="F817" s="10"/>
       <c r="G817" s="6"/>
       <c r="H817" s="6"/>
       <c r="I817" s="6"/>
@@ -23339,7 +23342,7 @@
       <c r="C818" s="6"/>
       <c r="D818" s="6"/>
       <c r="E818" s="6"/>
-      <c r="F818" s="9"/>
+      <c r="F818" s="10"/>
       <c r="G818" s="6"/>
       <c r="H818" s="6"/>
       <c r="I818" s="6"/>
@@ -23367,7 +23370,7 @@
       <c r="C819" s="6"/>
       <c r="D819" s="6"/>
       <c r="E819" s="6"/>
-      <c r="F819" s="9"/>
+      <c r="F819" s="10"/>
       <c r="G819" s="6"/>
       <c r="H819" s="6"/>
       <c r="I819" s="6"/>
@@ -23395,7 +23398,7 @@
       <c r="C820" s="6"/>
       <c r="D820" s="6"/>
       <c r="E820" s="6"/>
-      <c r="F820" s="9"/>
+      <c r="F820" s="10"/>
       <c r="G820" s="6"/>
       <c r="H820" s="6"/>
       <c r="I820" s="6"/>
@@ -23423,7 +23426,7 @@
       <c r="C821" s="6"/>
       <c r="D821" s="6"/>
       <c r="E821" s="6"/>
-      <c r="F821" s="9"/>
+      <c r="F821" s="10"/>
       <c r="G821" s="6"/>
       <c r="H821" s="6"/>
       <c r="I821" s="6"/>
@@ -23451,7 +23454,7 @@
       <c r="C822" s="6"/>
       <c r="D822" s="6"/>
       <c r="E822" s="6"/>
-      <c r="F822" s="9"/>
+      <c r="F822" s="10"/>
       <c r="G822" s="6"/>
       <c r="H822" s="6"/>
       <c r="I822" s="6"/>
@@ -23479,7 +23482,7 @@
       <c r="C823" s="6"/>
       <c r="D823" s="6"/>
       <c r="E823" s="6"/>
-      <c r="F823" s="9"/>
+      <c r="F823" s="10"/>
       <c r="G823" s="6"/>
       <c r="H823" s="6"/>
       <c r="I823" s="6"/>
@@ -23507,7 +23510,7 @@
       <c r="C824" s="6"/>
       <c r="D824" s="6"/>
       <c r="E824" s="6"/>
-      <c r="F824" s="9"/>
+      <c r="F824" s="10"/>
       <c r="G824" s="6"/>
       <c r="H824" s="6"/>
       <c r="I824" s="6"/>
@@ -23535,7 +23538,7 @@
       <c r="C825" s="6"/>
       <c r="D825" s="6"/>
       <c r="E825" s="6"/>
-      <c r="F825" s="9"/>
+      <c r="F825" s="10"/>
       <c r="G825" s="6"/>
       <c r="H825" s="6"/>
       <c r="I825" s="6"/>
@@ -23563,7 +23566,7 @@
       <c r="C826" s="6"/>
       <c r="D826" s="6"/>
       <c r="E826" s="6"/>
-      <c r="F826" s="9"/>
+      <c r="F826" s="10"/>
       <c r="G826" s="6"/>
       <c r="H826" s="6"/>
       <c r="I826" s="6"/>
@@ -23591,7 +23594,7 @@
       <c r="C827" s="6"/>
       <c r="D827" s="6"/>
       <c r="E827" s="6"/>
-      <c r="F827" s="9"/>
+      <c r="F827" s="10"/>
       <c r="G827" s="6"/>
       <c r="H827" s="6"/>
       <c r="I827" s="6"/>
@@ -23619,7 +23622,7 @@
       <c r="C828" s="6"/>
       <c r="D828" s="6"/>
       <c r="E828" s="6"/>
-      <c r="F828" s="9"/>
+      <c r="F828" s="10"/>
       <c r="G828" s="6"/>
       <c r="H828" s="6"/>
       <c r="I828" s="6"/>
@@ -23647,7 +23650,7 @@
       <c r="C829" s="6"/>
       <c r="D829" s="6"/>
       <c r="E829" s="6"/>
-      <c r="F829" s="9"/>
+      <c r="F829" s="10"/>
       <c r="G829" s="6"/>
       <c r="H829" s="6"/>
       <c r="I829" s="6"/>
@@ -23675,7 +23678,7 @@
       <c r="C830" s="6"/>
       <c r="D830" s="6"/>
       <c r="E830" s="6"/>
-      <c r="F830" s="9"/>
+      <c r="F830" s="10"/>
       <c r="G830" s="6"/>
       <c r="H830" s="6"/>
       <c r="I830" s="6"/>
@@ -23703,7 +23706,7 @@
       <c r="C831" s="6"/>
       <c r="D831" s="6"/>
       <c r="E831" s="6"/>
-      <c r="F831" s="9"/>
+      <c r="F831" s="10"/>
       <c r="G831" s="6"/>
       <c r="H831" s="6"/>
       <c r="I831" s="6"/>
@@ -23731,7 +23734,7 @@
       <c r="C832" s="6"/>
       <c r="D832" s="6"/>
       <c r="E832" s="6"/>
-      <c r="F832" s="9"/>
+      <c r="F832" s="10"/>
       <c r="G832" s="6"/>
       <c r="H832" s="6"/>
       <c r="I832" s="6"/>
@@ -23759,7 +23762,7 @@
       <c r="C833" s="6"/>
       <c r="D833" s="6"/>
       <c r="E833" s="6"/>
-      <c r="F833" s="9"/>
+      <c r="F833" s="10"/>
       <c r="G833" s="6"/>
       <c r="H833" s="6"/>
       <c r="I833" s="6"/>
@@ -23787,7 +23790,7 @@
       <c r="C834" s="6"/>
       <c r="D834" s="6"/>
       <c r="E834" s="6"/>
-      <c r="F834" s="9"/>
+      <c r="F834" s="10"/>
       <c r="G834" s="6"/>
       <c r="H834" s="6"/>
       <c r="I834" s="6"/>
@@ -23815,7 +23818,7 @@
       <c r="C835" s="6"/>
       <c r="D835" s="6"/>
       <c r="E835" s="6"/>
-      <c r="F835" s="9"/>
+      <c r="F835" s="10"/>
       <c r="G835" s="6"/>
       <c r="H835" s="6"/>
       <c r="I835" s="6"/>
@@ -23843,7 +23846,7 @@
       <c r="C836" s="6"/>
       <c r="D836" s="6"/>
       <c r="E836" s="6"/>
-      <c r="F836" s="9"/>
+      <c r="F836" s="10"/>
       <c r="G836" s="6"/>
       <c r="H836" s="6"/>
       <c r="I836" s="6"/>
@@ -23871,7 +23874,7 @@
       <c r="C837" s="6"/>
       <c r="D837" s="6"/>
       <c r="E837" s="6"/>
-      <c r="F837" s="9"/>
+      <c r="F837" s="10"/>
       <c r="G837" s="6"/>
       <c r="H837" s="6"/>
       <c r="I837" s="6"/>
@@ -23899,7 +23902,7 @@
       <c r="C838" s="6"/>
       <c r="D838" s="6"/>
       <c r="E838" s="6"/>
-      <c r="F838" s="9"/>
+      <c r="F838" s="10"/>
       <c r="G838" s="6"/>
       <c r="H838" s="6"/>
       <c r="I838" s="6"/>
@@ -23927,7 +23930,7 @@
       <c r="C839" s="6"/>
       <c r="D839" s="6"/>
       <c r="E839" s="6"/>
-      <c r="F839" s="9"/>
+      <c r="F839" s="10"/>
       <c r="G839" s="6"/>
       <c r="H839" s="6"/>
       <c r="I839" s="6"/>
@@ -23955,7 +23958,7 @@
       <c r="C840" s="6"/>
       <c r="D840" s="6"/>
       <c r="E840" s="6"/>
-      <c r="F840" s="9"/>
+      <c r="F840" s="10"/>
       <c r="G840" s="6"/>
       <c r="H840" s="6"/>
       <c r="I840" s="6"/>
@@ -23983,7 +23986,7 @@
       <c r="C841" s="6"/>
       <c r="D841" s="6"/>
       <c r="E841" s="6"/>
-      <c r="F841" s="9"/>
+      <c r="F841" s="10"/>
       <c r="G841" s="6"/>
       <c r="H841" s="6"/>
       <c r="I841" s="6"/>
@@ -24011,7 +24014,7 @@
       <c r="C842" s="6"/>
       <c r="D842" s="6"/>
       <c r="E842" s="6"/>
-      <c r="F842" s="9"/>
+      <c r="F842" s="10"/>
       <c r="G842" s="6"/>
       <c r="H842" s="6"/>
       <c r="I842" s="6"/>
@@ -24039,7 +24042,7 @@
       <c r="C843" s="6"/>
       <c r="D843" s="6"/>
       <c r="E843" s="6"/>
-      <c r="F843" s="9"/>
+      <c r="F843" s="10"/>
       <c r="G843" s="6"/>
       <c r="H843" s="6"/>
       <c r="I843" s="6"/>
@@ -24067,7 +24070,7 @@
       <c r="C844" s="6"/>
       <c r="D844" s="6"/>
       <c r="E844" s="6"/>
-      <c r="F844" s="9"/>
+      <c r="F844" s="10"/>
       <c r="G844" s="6"/>
       <c r="H844" s="6"/>
       <c r="I844" s="6"/>
@@ -24095,7 +24098,7 @@
       <c r="C845" s="6"/>
       <c r="D845" s="6"/>
       <c r="E845" s="6"/>
-      <c r="F845" s="9"/>
+      <c r="F845" s="10"/>
       <c r="G845" s="6"/>
       <c r="H845" s="6"/>
       <c r="I845" s="6"/>
@@ -24123,7 +24126,7 @@
       <c r="C846" s="6"/>
       <c r="D846" s="6"/>
       <c r="E846" s="6"/>
-      <c r="F846" s="9"/>
+      <c r="F846" s="10"/>
       <c r="G846" s="6"/>
       <c r="H846" s="6"/>
       <c r="I846" s="6"/>
@@ -24151,7 +24154,7 @@
       <c r="C847" s="6"/>
       <c r="D847" s="6"/>
       <c r="E847" s="6"/>
-      <c r="F847" s="9"/>
+      <c r="F847" s="10"/>
       <c r="G847" s="6"/>
       <c r="H847" s="6"/>
       <c r="I847" s="6"/>
@@ -24179,7 +24182,7 @@
       <c r="C848" s="6"/>
       <c r="D848" s="6"/>
       <c r="E848" s="6"/>
-      <c r="F848" s="9"/>
+      <c r="F848" s="10"/>
       <c r="G848" s="6"/>
       <c r="H848" s="6"/>
       <c r="I848" s="6"/>
@@ -24207,7 +24210,7 @@
       <c r="C849" s="6"/>
       <c r="D849" s="6"/>
       <c r="E849" s="6"/>
-      <c r="F849" s="9"/>
+      <c r="F849" s="10"/>
       <c r="G849" s="6"/>
       <c r="H849" s="6"/>
       <c r="I849" s="6"/>
@@ -24235,7 +24238,7 @@
       <c r="C850" s="6"/>
       <c r="D850" s="6"/>
       <c r="E850" s="6"/>
-      <c r="F850" s="9"/>
+      <c r="F850" s="10"/>
       <c r="G850" s="6"/>
       <c r="H850" s="6"/>
       <c r="I850" s="6"/>
@@ -24263,7 +24266,7 @@
       <c r="C851" s="6"/>
       <c r="D851" s="6"/>
       <c r="E851" s="6"/>
-      <c r="F851" s="9"/>
+      <c r="F851" s="10"/>
       <c r="G851" s="6"/>
       <c r="H851" s="6"/>
       <c r="I851" s="6"/>
@@ -24291,7 +24294,7 @@
       <c r="C852" s="6"/>
       <c r="D852" s="6"/>
       <c r="E852" s="6"/>
-      <c r="F852" s="9"/>
+      <c r="F852" s="10"/>
       <c r="G852" s="6"/>
       <c r="H852" s="6"/>
       <c r="I852" s="6"/>
@@ -24319,7 +24322,7 @@
       <c r="C853" s="6"/>
       <c r="D853" s="6"/>
       <c r="E853" s="6"/>
-      <c r="F853" s="9"/>
+      <c r="F853" s="10"/>
       <c r="G853" s="6"/>
       <c r="H853" s="6"/>
       <c r="I853" s="6"/>
@@ -24347,7 +24350,7 @@
       <c r="C854" s="6"/>
       <c r="D854" s="6"/>
       <c r="E854" s="6"/>
-      <c r="F854" s="9"/>
+      <c r="F854" s="10"/>
       <c r="G854" s="6"/>
       <c r="H854" s="6"/>
       <c r="I854" s="6"/>
@@ -24375,7 +24378,7 @@
       <c r="C855" s="6"/>
       <c r="D855" s="6"/>
       <c r="E855" s="6"/>
-      <c r="F855" s="9"/>
+      <c r="F855" s="10"/>
       <c r="G855" s="6"/>
       <c r="H855" s="6"/>
       <c r="I855" s="6"/>
@@ -24403,7 +24406,7 @@
       <c r="C856" s="6"/>
       <c r="D856" s="6"/>
       <c r="E856" s="6"/>
-      <c r="F856" s="9"/>
+      <c r="F856" s="10"/>
       <c r="G856" s="6"/>
       <c r="H856" s="6"/>
       <c r="I856" s="6"/>
@@ -24431,7 +24434,7 @@
       <c r="C857" s="6"/>
       <c r="D857" s="6"/>
       <c r="E857" s="6"/>
-      <c r="F857" s="9"/>
+      <c r="F857" s="10"/>
       <c r="G857" s="6"/>
       <c r="H857" s="6"/>
       <c r="I857" s="6"/>
@@ -24459,7 +24462,7 @@
       <c r="C858" s="6"/>
       <c r="D858" s="6"/>
       <c r="E858" s="6"/>
-      <c r="F858" s="9"/>
+      <c r="F858" s="10"/>
       <c r="G858" s="6"/>
       <c r="H858" s="6"/>
       <c r="I858" s="6"/>
@@ -24487,7 +24490,7 @@
       <c r="C859" s="6"/>
       <c r="D859" s="6"/>
       <c r="E859" s="6"/>
-      <c r="F859" s="9"/>
+      <c r="F859" s="10"/>
       <c r="G859" s="6"/>
       <c r="H859" s="6"/>
       <c r="I859" s="6"/>
@@ -24515,7 +24518,7 @@
       <c r="C860" s="6"/>
       <c r="D860" s="6"/>
       <c r="E860" s="6"/>
-      <c r="F860" s="9"/>
+      <c r="F860" s="10"/>
       <c r="G860" s="6"/>
       <c r="H860" s="6"/>
       <c r="I860" s="6"/>
@@ -24543,7 +24546,7 @@
       <c r="C861" s="6"/>
       <c r="D861" s="6"/>
       <c r="E861" s="6"/>
-      <c r="F861" s="9"/>
+      <c r="F861" s="10"/>
       <c r="G861" s="6"/>
       <c r="H861" s="6"/>
       <c r="I861" s="6"/>
@@ -24571,7 +24574,7 @@
       <c r="C862" s="6"/>
       <c r="D862" s="6"/>
       <c r="E862" s="6"/>
-      <c r="F862" s="9"/>
+      <c r="F862" s="10"/>
       <c r="G862" s="6"/>
       <c r="H862" s="6"/>
       <c r="I862" s="6"/>
@@ -24599,7 +24602,7 @@
       <c r="C863" s="6"/>
       <c r="D863" s="6"/>
       <c r="E863" s="6"/>
-      <c r="F863" s="9"/>
+      <c r="F863" s="10"/>
       <c r="G863" s="6"/>
       <c r="H863" s="6"/>
       <c r="I863" s="6"/>
@@ -24627,7 +24630,7 @@
       <c r="C864" s="6"/>
       <c r="D864" s="6"/>
       <c r="E864" s="6"/>
-      <c r="F864" s="9"/>
+      <c r="F864" s="10"/>
       <c r="G864" s="6"/>
       <c r="H864" s="6"/>
       <c r="I864" s="6"/>
@@ -24655,7 +24658,7 @@
       <c r="C865" s="6"/>
       <c r="D865" s="6"/>
       <c r="E865" s="6"/>
-      <c r="F865" s="9"/>
+      <c r="F865" s="10"/>
       <c r="G865" s="6"/>
       <c r="H865" s="6"/>
       <c r="I865" s="6"/>
@@ -24683,7 +24686,7 @@
       <c r="C866" s="6"/>
       <c r="D866" s="6"/>
       <c r="E866" s="6"/>
-      <c r="F866" s="9"/>
+      <c r="F866" s="10"/>
       <c r="G866" s="6"/>
       <c r="H866" s="6"/>
       <c r="I866" s="6"/>
@@ -24711,7 +24714,7 @@
       <c r="C867" s="6"/>
       <c r="D867" s="6"/>
       <c r="E867" s="6"/>
-      <c r="F867" s="9"/>
+      <c r="F867" s="10"/>
       <c r="G867" s="6"/>
       <c r="H867" s="6"/>
       <c r="I867" s="6"/>
@@ -24739,7 +24742,7 @@
       <c r="C868" s="6"/>
       <c r="D868" s="6"/>
       <c r="E868" s="6"/>
-      <c r="F868" s="9"/>
+      <c r="F868" s="10"/>
       <c r="G868" s="6"/>
       <c r="H868" s="6"/>
       <c r="I868" s="6"/>
@@ -24767,7 +24770,7 @@
       <c r="C869" s="6"/>
       <c r="D869" s="6"/>
       <c r="E869" s="6"/>
-      <c r="F869" s="9"/>
+      <c r="F869" s="10"/>
       <c r="G869" s="6"/>
       <c r="H869" s="6"/>
       <c r="I869" s="6"/>
@@ -24795,7 +24798,7 @@
       <c r="C870" s="6"/>
       <c r="D870" s="6"/>
       <c r="E870" s="6"/>
-      <c r="F870" s="9"/>
+      <c r="F870" s="10"/>
       <c r="G870" s="6"/>
       <c r="H870" s="6"/>
       <c r="I870" s="6"/>
@@ -24823,7 +24826,7 @@
       <c r="C871" s="6"/>
       <c r="D871" s="6"/>
       <c r="E871" s="6"/>
-      <c r="F871" s="9"/>
+      <c r="F871" s="10"/>
       <c r="G871" s="6"/>
       <c r="H871" s="6"/>
       <c r="I871" s="6"/>
@@ -24851,7 +24854,7 @@
       <c r="C872" s="6"/>
       <c r="D872" s="6"/>
       <c r="E872" s="6"/>
-      <c r="F872" s="9"/>
+      <c r="F872" s="10"/>
       <c r="G872" s="6"/>
       <c r="H872" s="6"/>
       <c r="I872" s="6"/>
@@ -24879,7 +24882,7 @@
       <c r="C873" s="6"/>
       <c r="D873" s="6"/>
       <c r="E873" s="6"/>
-      <c r="F873" s="9"/>
+      <c r="F873" s="10"/>
       <c r="G873" s="6"/>
       <c r="H873" s="6"/>
       <c r="I873" s="6"/>
@@ -24907,7 +24910,7 @@
       <c r="C874" s="6"/>
       <c r="D874" s="6"/>
       <c r="E874" s="6"/>
-      <c r="F874" s="9"/>
+      <c r="F874" s="10"/>
       <c r="G874" s="6"/>
       <c r="H874" s="6"/>
       <c r="I874" s="6"/>
@@ -24935,7 +24938,7 @@
       <c r="C875" s="6"/>
       <c r="D875" s="6"/>
       <c r="E875" s="6"/>
-      <c r="F875" s="9"/>
+      <c r="F875" s="10"/>
       <c r="G875" s="6"/>
       <c r="H875" s="6"/>
       <c r="I875" s="6"/>
@@ -24963,7 +24966,7 @@
       <c r="C876" s="6"/>
       <c r="D876" s="6"/>
       <c r="E876" s="6"/>
-      <c r="F876" s="9"/>
+      <c r="F876" s="10"/>
       <c r="G876" s="6"/>
       <c r="H876" s="6"/>
       <c r="I876" s="6"/>
@@ -24991,7 +24994,7 @@
       <c r="C877" s="6"/>
       <c r="D877" s="6"/>
       <c r="E877" s="6"/>
-      <c r="F877" s="9"/>
+      <c r="F877" s="10"/>
       <c r="G877" s="6"/>
       <c r="H877" s="6"/>
       <c r="I877" s="6"/>
@@ -25019,7 +25022,7 @@
       <c r="C878" s="6"/>
       <c r="D878" s="6"/>
       <c r="E878" s="6"/>
-      <c r="F878" s="9"/>
+      <c r="F878" s="10"/>
       <c r="G878" s="6"/>
       <c r="H878" s="6"/>
       <c r="I878" s="6"/>
@@ -25047,7 +25050,7 @@
       <c r="C879" s="6"/>
       <c r="D879" s="6"/>
       <c r="E879" s="6"/>
-      <c r="F879" s="9"/>
+      <c r="F879" s="10"/>
       <c r="G879" s="6"/>
       <c r="H879" s="6"/>
       <c r="I879" s="6"/>
@@ -25075,7 +25078,7 @@
       <c r="C880" s="6"/>
       <c r="D880" s="6"/>
       <c r="E880" s="6"/>
-      <c r="F880" s="9"/>
+      <c r="F880" s="10"/>
       <c r="G880" s="6"/>
       <c r="H880" s="6"/>
       <c r="I880" s="6"/>
@@ -25103,7 +25106,7 @@
       <c r="C881" s="6"/>
       <c r="D881" s="6"/>
       <c r="E881" s="6"/>
-      <c r="F881" s="9"/>
+      <c r="F881" s="10"/>
       <c r="G881" s="6"/>
       <c r="H881" s="6"/>
       <c r="I881" s="6"/>
@@ -25131,7 +25134,7 @@
       <c r="C882" s="6"/>
       <c r="D882" s="6"/>
       <c r="E882" s="6"/>
-      <c r="F882" s="9"/>
+      <c r="F882" s="10"/>
       <c r="G882" s="6"/>
       <c r="H882" s="6"/>
       <c r="I882" s="6"/>
@@ -25159,7 +25162,7 @@
       <c r="C883" s="6"/>
       <c r="D883" s="6"/>
       <c r="E883" s="6"/>
-      <c r="F883" s="9"/>
+      <c r="F883" s="10"/>
       <c r="G883" s="6"/>
       <c r="H883" s="6"/>
       <c r="I883" s="6"/>
@@ -25187,7 +25190,7 @@
       <c r="C884" s="6"/>
       <c r="D884" s="6"/>
       <c r="E884" s="6"/>
-      <c r="F884" s="9"/>
+      <c r="F884" s="10"/>
       <c r="G884" s="6"/>
       <c r="H884" s="6"/>
       <c r="I884" s="6"/>
@@ -25215,7 +25218,7 @@
       <c r="C885" s="6"/>
       <c r="D885" s="6"/>
       <c r="E885" s="6"/>
-      <c r="F885" s="9"/>
+      <c r="F885" s="10"/>
       <c r="G885" s="6"/>
       <c r="H885" s="6"/>
       <c r="I885" s="6"/>
@@ -25243,7 +25246,7 @@
       <c r="C886" s="6"/>
       <c r="D886" s="6"/>
       <c r="E886" s="6"/>
-      <c r="F886" s="9"/>
+      <c r="F886" s="10"/>
       <c r="G886" s="6"/>
       <c r="H886" s="6"/>
       <c r="I886" s="6"/>
@@ -25271,7 +25274,7 @@
       <c r="C887" s="6"/>
       <c r="D887" s="6"/>
       <c r="E887" s="6"/>
-      <c r="F887" s="9"/>
+      <c r="F887" s="10"/>
       <c r="G887" s="6"/>
       <c r="H887" s="6"/>
       <c r="I887" s="6"/>
@@ -25299,7 +25302,7 @@
       <c r="C888" s="6"/>
       <c r="D888" s="6"/>
       <c r="E888" s="6"/>
-      <c r="F888" s="9"/>
+      <c r="F888" s="10"/>
       <c r="G888" s="6"/>
       <c r="H888" s="6"/>
       <c r="I888" s="6"/>
@@ -25327,7 +25330,7 @@
       <c r="C889" s="6"/>
       <c r="D889" s="6"/>
       <c r="E889" s="6"/>
-      <c r="F889" s="9"/>
+      <c r="F889" s="10"/>
       <c r="G889" s="6"/>
       <c r="H889" s="6"/>
       <c r="I889" s="6"/>
@@ -25355,7 +25358,7 @@
       <c r="C890" s="6"/>
       <c r="D890" s="6"/>
       <c r="E890" s="6"/>
-      <c r="F890" s="9"/>
+      <c r="F890" s="10"/>
       <c r="G890" s="6"/>
       <c r="H890" s="6"/>
       <c r="I890" s="6"/>
@@ -25383,7 +25386,7 @@
       <c r="C891" s="6"/>
       <c r="D891" s="6"/>
       <c r="E891" s="6"/>
-      <c r="F891" s="9"/>
+      <c r="F891" s="10"/>
       <c r="G891" s="6"/>
       <c r="H891" s="6"/>
       <c r="I891" s="6"/>
@@ -25411,7 +25414,7 @@
       <c r="C892" s="6"/>
       <c r="D892" s="6"/>
       <c r="E892" s="6"/>
-      <c r="F892" s="9"/>
+      <c r="F892" s="10"/>
       <c r="G892" s="6"/>
       <c r="H892" s="6"/>
       <c r="I892" s="6"/>
@@ -25439,7 +25442,7 @@
       <c r="C893" s="6"/>
       <c r="D893" s="6"/>
       <c r="E893" s="6"/>
-      <c r="F893" s="9"/>
+      <c r="F893" s="10"/>
       <c r="G893" s="6"/>
       <c r="H893" s="6"/>
       <c r="I893" s="6"/>
@@ -25467,7 +25470,7 @@
       <c r="C894" s="6"/>
       <c r="D894" s="6"/>
       <c r="E894" s="6"/>
-      <c r="F894" s="9"/>
+      <c r="F894" s="10"/>
       <c r="G894" s="6"/>
       <c r="H894" s="6"/>
       <c r="I894" s="6"/>
@@ -25495,7 +25498,7 @@
       <c r="C895" s="6"/>
       <c r="D895" s="6"/>
       <c r="E895" s="6"/>
-      <c r="F895" s="9"/>
+      <c r="F895" s="10"/>
       <c r="G895" s="6"/>
       <c r="H895" s="6"/>
       <c r="I895" s="6"/>
@@ -25523,7 +25526,7 @@
       <c r="C896" s="6"/>
       <c r="D896" s="6"/>
       <c r="E896" s="6"/>
-      <c r="F896" s="9"/>
+      <c r="F896" s="10"/>
       <c r="G896" s="6"/>
       <c r="H896" s="6"/>
       <c r="I896" s="6"/>
@@ -25551,7 +25554,7 @@
       <c r="C897" s="6"/>
       <c r="D897" s="6"/>
       <c r="E897" s="6"/>
-      <c r="F897" s="9"/>
+      <c r="F897" s="10"/>
       <c r="G897" s="6"/>
       <c r="H897" s="6"/>
       <c r="I897" s="6"/>
@@ -25579,7 +25582,7 @@
       <c r="C898" s="6"/>
       <c r="D898" s="6"/>
       <c r="E898" s="6"/>
-      <c r="F898" s="9"/>
+      <c r="F898" s="10"/>
       <c r="G898" s="6"/>
       <c r="H898" s="6"/>
       <c r="I898" s="6"/>
@@ -25607,7 +25610,7 @@
       <c r="C899" s="6"/>
       <c r="D899" s="6"/>
       <c r="E899" s="6"/>
-      <c r="F899" s="9"/>
+      <c r="F899" s="10"/>
       <c r="G899" s="6"/>
       <c r="H899" s="6"/>
       <c r="I899" s="6"/>
@@ -25635,7 +25638,7 @@
       <c r="C900" s="6"/>
       <c r="D900" s="6"/>
       <c r="E900" s="6"/>
-      <c r="F900" s="9"/>
+      <c r="F900" s="10"/>
       <c r="G900" s="6"/>
       <c r="H900" s="6"/>
       <c r="I900" s="6"/>
@@ -25663,7 +25666,7 @@
       <c r="C901" s="6"/>
       <c r="D901" s="6"/>
       <c r="E901" s="6"/>
-      <c r="F901" s="9"/>
+      <c r="F901" s="10"/>
       <c r="G901" s="6"/>
       <c r="H901" s="6"/>
       <c r="I901" s="6"/>
@@ -25691,7 +25694,7 @@
       <c r="C902" s="6"/>
       <c r="D902" s="6"/>
       <c r="E902" s="6"/>
-      <c r="F902" s="9"/>
+      <c r="F902" s="10"/>
       <c r="G902" s="6"/>
       <c r="H902" s="6"/>
       <c r="I902" s="6"/>
@@ -25719,7 +25722,7 @@
       <c r="C903" s="6"/>
       <c r="D903" s="6"/>
       <c r="E903" s="6"/>
-      <c r="F903" s="9"/>
+      <c r="F903" s="10"/>
       <c r="G903" s="6"/>
       <c r="H903" s="6"/>
       <c r="I903" s="6"/>
@@ -25747,7 +25750,7 @@
       <c r="C904" s="6"/>
       <c r="D904" s="6"/>
       <c r="E904" s="6"/>
-      <c r="F904" s="9"/>
+      <c r="F904" s="10"/>
       <c r="G904" s="6"/>
       <c r="H904" s="6"/>
       <c r="I904" s="6"/>
@@ -25775,7 +25778,7 @@
       <c r="C905" s="6"/>
       <c r="D905" s="6"/>
       <c r="E905" s="6"/>
-      <c r="F905" s="9"/>
+      <c r="F905" s="10"/>
       <c r="G905" s="6"/>
       <c r="H905" s="6"/>
       <c r="I905" s="6"/>
@@ -25803,7 +25806,7 @@
       <c r="C906" s="6"/>
       <c r="D906" s="6"/>
       <c r="E906" s="6"/>
-      <c r="F906" s="9"/>
+      <c r="F906" s="10"/>
       <c r="G906" s="6"/>
       <c r="H906" s="6"/>
       <c r="I906" s="6"/>
@@ -25831,7 +25834,7 @@
       <c r="C907" s="6"/>
       <c r="D907" s="6"/>
       <c r="E907" s="6"/>
-      <c r="F907" s="9"/>
+      <c r="F907" s="10"/>
       <c r="G907" s="6"/>
       <c r="H907" s="6"/>
       <c r="I907" s="6"/>
@@ -25859,7 +25862,7 @@
       <c r="C908" s="6"/>
       <c r="D908" s="6"/>
       <c r="E908" s="6"/>
-      <c r="F908" s="9"/>
+      <c r="F908" s="10"/>
       <c r="G908" s="6"/>
       <c r="H908" s="6"/>
       <c r="I908" s="6"/>
@@ -25887,7 +25890,7 @@
       <c r="C909" s="6"/>
       <c r="D909" s="6"/>
       <c r="E909" s="6"/>
-      <c r="F909" s="9"/>
+      <c r="F909" s="10"/>
       <c r="G909" s="6"/>
       <c r="H909" s="6"/>
       <c r="I909" s="6"/>
@@ -25915,7 +25918,7 @@
       <c r="C910" s="6"/>
       <c r="D910" s="6"/>
       <c r="E910" s="6"/>
-      <c r="F910" s="9"/>
+      <c r="F910" s="10"/>
       <c r="G910" s="6"/>
       <c r="H910" s="6"/>
       <c r="I910" s="6"/>
@@ -25943,7 +25946,7 @@
       <c r="C911" s="6"/>
       <c r="D911" s="6"/>
       <c r="E911" s="6"/>
-      <c r="F911" s="9"/>
+      <c r="F911" s="10"/>
       <c r="G911" s="6"/>
       <c r="H911" s="6"/>
       <c r="I911" s="6"/>
@@ -25971,7 +25974,7 @@
       <c r="C912" s="6"/>
       <c r="D912" s="6"/>
       <c r="E912" s="6"/>
-      <c r="F912" s="9"/>
+      <c r="F912" s="10"/>
       <c r="G912" s="6"/>
       <c r="H912" s="6"/>
       <c r="I912" s="6"/>
@@ -25999,7 +26002,7 @@
       <c r="C913" s="6"/>
       <c r="D913" s="6"/>
       <c r="E913" s="6"/>
-      <c r="F913" s="9"/>
+      <c r="F913" s="10"/>
       <c r="G913" s="6"/>
       <c r="H913" s="6"/>
       <c r="I913" s="6"/>
@@ -26027,7 +26030,7 @@
       <c r="C914" s="6"/>
       <c r="D914" s="6"/>
       <c r="E914" s="6"/>
-      <c r="F914" s="9"/>
+      <c r="F914" s="10"/>
       <c r="G914" s="6"/>
       <c r="H914" s="6"/>
       <c r="I914" s="6"/>
@@ -26055,7 +26058,7 @@
       <c r="C915" s="6"/>
       <c r="D915" s="6"/>
       <c r="E915" s="6"/>
-      <c r="F915" s="9"/>
+      <c r="F915" s="10"/>
       <c r="G915" s="6"/>
       <c r="H915" s="6"/>
       <c r="I915" s="6"/>
@@ -26083,7 +26086,7 @@
       <c r="C916" s="6"/>
       <c r="D916" s="6"/>
       <c r="E916" s="6"/>
-      <c r="F916" s="9"/>
+      <c r="F916" s="10"/>
       <c r="G916" s="6"/>
       <c r="H916" s="6"/>
       <c r="I916" s="6"/>
@@ -26111,7 +26114,7 @@
       <c r="C917" s="6"/>
       <c r="D917" s="6"/>
       <c r="E917" s="6"/>
-      <c r="F917" s="9"/>
+      <c r="F917" s="10"/>
       <c r="G917" s="6"/>
       <c r="H917" s="6"/>
       <c r="I917" s="6"/>
@@ -26139,7 +26142,7 @@
       <c r="C918" s="6"/>
       <c r="D918" s="6"/>
       <c r="E918" s="6"/>
-      <c r="F918" s="9"/>
+      <c r="F918" s="10"/>
       <c r="G918" s="6"/>
       <c r="H918" s="6"/>
       <c r="I918" s="6"/>
@@ -26167,7 +26170,7 @@
       <c r="C919" s="6"/>
       <c r="D919" s="6"/>
       <c r="E919" s="6"/>
-      <c r="F919" s="9"/>
+      <c r="F919" s="10"/>
       <c r="G919" s="6"/>
       <c r="H919" s="6"/>
       <c r="I919" s="6"/>
@@ -26195,7 +26198,7 @@
       <c r="C920" s="6"/>
       <c r="D920" s="6"/>
       <c r="E920" s="6"/>
-      <c r="F920" s="9"/>
+      <c r="F920" s="10"/>
       <c r="G920" s="6"/>
       <c r="H920" s="6"/>
       <c r="I920" s="6"/>
@@ -26223,7 +26226,7 @@
       <c r="C921" s="6"/>
       <c r="D921" s="6"/>
       <c r="E921" s="6"/>
-      <c r="F921" s="9"/>
+      <c r="F921" s="10"/>
       <c r="G921" s="6"/>
       <c r="H921" s="6"/>
       <c r="I921" s="6"/>
@@ -26251,7 +26254,7 @@
       <c r="C922" s="6"/>
       <c r="D922" s="6"/>
       <c r="E922" s="6"/>
-      <c r="F922" s="9"/>
+      <c r="F922" s="10"/>
       <c r="G922" s="6"/>
       <c r="H922" s="6"/>
       <c r="I922" s="6"/>
@@ -26279,7 +26282,7 @@
       <c r="C923" s="6"/>
       <c r="D923" s="6"/>
       <c r="E923" s="6"/>
-      <c r="F923" s="9"/>
+      <c r="F923" s="10"/>
       <c r="G923" s="6"/>
       <c r="H923" s="6"/>
       <c r="I923" s="6"/>
@@ -26307,7 +26310,7 @@
       <c r="C924" s="6"/>
       <c r="D924" s="6"/>
       <c r="E924" s="6"/>
-      <c r="F924" s="9"/>
+      <c r="F924" s="10"/>
       <c r="G924" s="6"/>
       <c r="H924" s="6"/>
       <c r="I924" s="6"/>
@@ -26335,7 +26338,7 @@
       <c r="C925" s="6"/>
       <c r="D925" s="6"/>
       <c r="E925" s="6"/>
-      <c r="F925" s="9"/>
+      <c r="F925" s="10"/>
       <c r="G925" s="6"/>
       <c r="H925" s="6"/>
       <c r="I925" s="6"/>
@@ -26363,7 +26366,7 @@
       <c r="C926" s="6"/>
       <c r="D926" s="6"/>
       <c r="E926" s="6"/>
-      <c r="F926" s="9"/>
+      <c r="F926" s="10"/>
       <c r="G926" s="6"/>
       <c r="H926" s="6"/>
       <c r="I926" s="6"/>
@@ -26391,7 +26394,7 @@
       <c r="C927" s="6"/>
       <c r="D927" s="6"/>
       <c r="E927" s="6"/>
-      <c r="F927" s="9"/>
+      <c r="F927" s="10"/>
       <c r="G927" s="6"/>
       <c r="H927" s="6"/>
       <c r="I927" s="6"/>
@@ -26419,7 +26422,7 @@
       <c r="C928" s="6"/>
       <c r="D928" s="6"/>
       <c r="E928" s="6"/>
-      <c r="F928" s="9"/>
+      <c r="F928" s="10"/>
       <c r="G928" s="6"/>
       <c r="H928" s="6"/>
       <c r="I928" s="6"/>
@@ -26447,7 +26450,7 @@
       <c r="C929" s="6"/>
       <c r="D929" s="6"/>
       <c r="E929" s="6"/>
-      <c r="F929" s="9"/>
+      <c r="F929" s="10"/>
       <c r="G929" s="6"/>
       <c r="H929" s="6"/>
       <c r="I929" s="6"/>
@@ -26475,7 +26478,7 @@
       <c r="C930" s="6"/>
       <c r="D930" s="6"/>
       <c r="E930" s="6"/>
-      <c r="F930" s="9"/>
+      <c r="F930" s="10"/>
       <c r="G930" s="6"/>
       <c r="H930" s="6"/>
       <c r="I930" s="6"/>
@@ -26503,7 +26506,7 @@
       <c r="C931" s="6"/>
       <c r="D931" s="6"/>
       <c r="E931" s="6"/>
-      <c r="F931" s="9"/>
+      <c r="F931" s="10"/>
       <c r="G931" s="6"/>
       <c r="H931" s="6"/>
       <c r="I931" s="6"/>
@@ -26531,7 +26534,7 @@
       <c r="C932" s="6"/>
       <c r="D932" s="6"/>
       <c r="E932" s="6"/>
-      <c r="F932" s="9"/>
+      <c r="F932" s="10"/>
       <c r="G932" s="6"/>
       <c r="H932" s="6"/>
       <c r="I932" s="6"/>
@@ -26559,7 +26562,7 @@
       <c r="C933" s="6"/>
       <c r="D933" s="6"/>
       <c r="E933" s="6"/>
-      <c r="F933" s="9"/>
+      <c r="F933" s="10"/>
       <c r="G933" s="6"/>
       <c r="H933" s="6"/>
       <c r="I933" s="6"/>
@@ -26587,7 +26590,7 @@
       <c r="C934" s="6"/>
       <c r="D934" s="6"/>
       <c r="E934" s="6"/>
-      <c r="F934" s="9"/>
+      <c r="F934" s="10"/>
       <c r="G934" s="6"/>
       <c r="H934" s="6"/>
       <c r="I934" s="6"/>
@@ -26615,7 +26618,7 @@
       <c r="C935" s="6"/>
       <c r="D935" s="6"/>
       <c r="E935" s="6"/>
-      <c r="F935" s="9"/>
+      <c r="F935" s="10"/>
       <c r="G935" s="6"/>
       <c r="H935" s="6"/>
       <c r="I935" s="6"/>
@@ -26643,7 +26646,7 @@
       <c r="C936" s="6"/>
       <c r="D936" s="6"/>
       <c r="E936" s="6"/>
-      <c r="F936" s="9"/>
+      <c r="F936" s="10"/>
       <c r="G936" s="6"/>
       <c r="H936" s="6"/>
       <c r="I936" s="6"/>
@@ -26671,7 +26674,7 @@
       <c r="C937" s="6"/>
       <c r="D937" s="6"/>
       <c r="E937" s="6"/>
-      <c r="F937" s="9"/>
+      <c r="F937" s="10"/>
       <c r="G937" s="6"/>
       <c r="H937" s="6"/>
       <c r="I937" s="6"/>
@@ -26699,7 +26702,7 @@
       <c r="C938" s="6"/>
       <c r="D938" s="6"/>
       <c r="E938" s="6"/>
-      <c r="F938" s="9"/>
+      <c r="F938" s="10"/>
       <c r="G938" s="6"/>
       <c r="H938" s="6"/>
       <c r="I938" s="6"/>
@@ -26727,7 +26730,7 @@
       <c r="C939" s="6"/>
       <c r="D939" s="6"/>
       <c r="E939" s="6"/>
-      <c r="F939" s="9"/>
+      <c r="F939" s="10"/>
       <c r="G939" s="6"/>
       <c r="H939" s="6"/>
       <c r="I939" s="6"/>
@@ -26755,7 +26758,7 @@
       <c r="C940" s="6"/>
       <c r="D940" s="6"/>
       <c r="E940" s="6"/>
-      <c r="F940" s="9"/>
+      <c r="F940" s="10"/>
       <c r="G940" s="6"/>
       <c r="H940" s="6"/>
       <c r="I940" s="6"/>
@@ -26783,7 +26786,7 @@
       <c r="C941" s="6"/>
       <c r="D941" s="6"/>
       <c r="E941" s="6"/>
-      <c r="F941" s="9"/>
+      <c r="F941" s="10"/>
       <c r="G941" s="6"/>
       <c r="H941" s="6"/>
       <c r="I941" s="6"/>
@@ -26811,7 +26814,7 @@
       <c r="C942" s="6"/>
       <c r="D942" s="6"/>
       <c r="E942" s="6"/>
-      <c r="F942" s="9"/>
+      <c r="F942" s="10"/>
       <c r="G942" s="6"/>
       <c r="H942" s="6"/>
       <c r="I942" s="6"/>
@@ -26839,7 +26842,7 @@
       <c r="C943" s="6"/>
       <c r="D943" s="6"/>
       <c r="E943" s="6"/>
-      <c r="F943" s="9"/>
+      <c r="F943" s="10"/>
       <c r="G943" s="6"/>
       <c r="H943" s="6"/>
       <c r="I943" s="6"/>
@@ -26867,7 +26870,7 @@
       <c r="C944" s="6"/>
       <c r="D944" s="6"/>
       <c r="E944" s="6"/>
-      <c r="F944" s="9"/>
+      <c r="F944" s="10"/>
       <c r="G944" s="6"/>
       <c r="H944" s="6"/>
       <c r="I944" s="6"/>
@@ -26895,7 +26898,7 @@
       <c r="C945" s="6"/>
       <c r="D945" s="6"/>
       <c r="E945" s="6"/>
-      <c r="F945" s="9"/>
+      <c r="F945" s="10"/>
       <c r="G945" s="6"/>
       <c r="H945" s="6"/>
       <c r="I945" s="6"/>
@@ -26923,7 +26926,7 @@
       <c r="C946" s="6"/>
       <c r="D946" s="6"/>
       <c r="E946" s="6"/>
-      <c r="F946" s="9"/>
+      <c r="F946" s="10"/>
       <c r="G946" s="6"/>
       <c r="H946" s="6"/>
       <c r="I946" s="6"/>
@@ -26951,7 +26954,7 @@
       <c r="C947" s="6"/>
       <c r="D947" s="6"/>
       <c r="E947" s="6"/>
-      <c r="F947" s="9"/>
+      <c r="F947" s="10"/>
       <c r="G947" s="6"/>
       <c r="H947" s="6"/>
       <c r="I947" s="6"/>
@@ -26979,7 +26982,7 @@
       <c r="C948" s="6"/>
       <c r="D948" s="6"/>
       <c r="E948" s="6"/>
-      <c r="F948" s="9"/>
+      <c r="F948" s="10"/>
       <c r="G948" s="6"/>
       <c r="H948" s="6"/>
       <c r="I948" s="6"/>
@@ -27007,7 +27010,7 @@
       <c r="C949" s="6"/>
       <c r="D949" s="6"/>
       <c r="E949" s="6"/>
-      <c r="F949" s="9"/>
+      <c r="F949" s="10"/>
       <c r="G949" s="6"/>
       <c r="H949" s="6"/>
       <c r="I949" s="6"/>
@@ -27035,7 +27038,7 @@
       <c r="C950" s="6"/>
       <c r="D950" s="6"/>
       <c r="E950" s="6"/>
-      <c r="F950" s="9"/>
+      <c r="F950" s="10"/>
       <c r="G950" s="6"/>
       <c r="H950" s="6"/>
       <c r="I950" s="6"/>
@@ -27063,7 +27066,7 @@
       <c r="C951" s="6"/>
       <c r="D951" s="6"/>
       <c r="E951" s="6"/>
-      <c r="F951" s="9"/>
+      <c r="F951" s="10"/>
       <c r="G951" s="6"/>
       <c r="H951" s="6"/>
       <c r="I951" s="6"/>
@@ -27091,7 +27094,7 @@
       <c r="C952" s="6"/>
       <c r="D952" s="6"/>
       <c r="E952" s="6"/>
-      <c r="F952" s="9"/>
+      <c r="F952" s="10"/>
       <c r="G952" s="6"/>
       <c r="H952" s="6"/>
       <c r="I952" s="6"/>
@@ -27119,7 +27122,7 @@
       <c r="C953" s="6"/>
       <c r="D953" s="6"/>
       <c r="E953" s="6"/>
-      <c r="F953" s="9"/>
+      <c r="F953" s="10"/>
       <c r="G953" s="6"/>
       <c r="H953" s="6"/>
       <c r="I953" s="6"/>
@@ -27147,7 +27150,7 @@
       <c r="C954" s="6"/>
       <c r="D954" s="6"/>
       <c r="E954" s="6"/>
-      <c r="F954" s="9"/>
+      <c r="F954" s="10"/>
       <c r="G954" s="6"/>
       <c r="H954" s="6"/>
       <c r="I954" s="6"/>
@@ -27175,7 +27178,7 @@
       <c r="C955" s="6"/>
       <c r="D955" s="6"/>
       <c r="E955" s="6"/>
-      <c r="F955" s="9"/>
+      <c r="F955" s="10"/>
       <c r="G955" s="6"/>
       <c r="H955" s="6"/>
       <c r="I955" s="6"/>
@@ -27203,7 +27206,7 @@
       <c r="C956" s="6"/>
       <c r="D956" s="6"/>
       <c r="E956" s="6"/>
-      <c r="F956" s="9"/>
+      <c r="F956" s="10"/>
       <c r="G956" s="6"/>
       <c r="H956" s="6"/>
       <c r="I956" s="6"/>
@@ -27231,7 +27234,7 @@
       <c r="C957" s="6"/>
       <c r="D957" s="6"/>
       <c r="E957" s="6"/>
-      <c r="F957" s="9"/>
+      <c r="F957" s="10"/>
       <c r="G957" s="6"/>
       <c r="H957" s="6"/>
       <c r="I957" s="6"/>
@@ -27259,7 +27262,7 @@
       <c r="C958" s="6"/>
       <c r="D958" s="6"/>
       <c r="E958" s="6"/>
-      <c r="F958" s="9"/>
+      <c r="F958" s="10"/>
       <c r="G958" s="6"/>
       <c r="H958" s="6"/>
       <c r="I958" s="6"/>
@@ -27287,7 +27290,7 @@
       <c r="C959" s="6"/>
       <c r="D959" s="6"/>
       <c r="E959" s="6"/>
-      <c r="F959" s="9"/>
+      <c r="F959" s="10"/>
       <c r="G959" s="6"/>
       <c r="H959" s="6"/>
       <c r="I959" s="6"/>
@@ -27315,7 +27318,7 @@
       <c r="C960" s="6"/>
       <c r="D960" s="6"/>
       <c r="E960" s="6"/>
-      <c r="F960" s="9"/>
+      <c r="F960" s="10"/>
       <c r="G960" s="6"/>
       <c r="H960" s="6"/>
       <c r="I960" s="6"/>
@@ -27343,7 +27346,7 @@
       <c r="C961" s="6"/>
       <c r="D961" s="6"/>
       <c r="E961" s="6"/>
-      <c r="F961" s="9"/>
+      <c r="F961" s="10"/>
       <c r="G961" s="6"/>
       <c r="H961" s="6"/>
       <c r="I961" s="6"/>
@@ -27371,7 +27374,7 @@
       <c r="C962" s="6"/>
       <c r="D962" s="6"/>
       <c r="E962" s="6"/>
-      <c r="F962" s="9"/>
+      <c r="F962" s="10"/>
       <c r="G962" s="6"/>
       <c r="H962" s="6"/>
       <c r="I962" s="6"/>
@@ -27399,7 +27402,7 @@
       <c r="C963" s="6"/>
       <c r="D963" s="6"/>
       <c r="E963" s="6"/>
-      <c r="F963" s="9"/>
+      <c r="F963" s="10"/>
       <c r="G963" s="6"/>
       <c r="H963" s="6"/>
       <c r="I963" s="6"/>
@@ -27427,7 +27430,7 @@
       <c r="C964" s="6"/>
       <c r="D964" s="6"/>
       <c r="E964" s="6"/>
-      <c r="F964" s="9"/>
+      <c r="F964" s="10"/>
       <c r="G964" s="6"/>
       <c r="H964" s="6"/>
       <c r="I964" s="6"/>
@@ -27455,7 +27458,7 @@
       <c r="C965" s="6"/>
       <c r="D965" s="6"/>
       <c r="E965" s="6"/>
-      <c r="F965" s="9"/>
+      <c r="F965" s="10"/>
       <c r="G965" s="6"/>
       <c r="H965" s="6"/>
       <c r="I965" s="6"/>
@@ -27483,7 +27486,7 @@
       <c r="C966" s="6"/>
       <c r="D966" s="6"/>
       <c r="E966" s="6"/>
-      <c r="F966" s="9"/>
+      <c r="F966" s="10"/>
       <c r="G966" s="6"/>
       <c r="H966" s="6"/>
       <c r="I966" s="6"/>
@@ -27511,7 +27514,7 @@
       <c r="C967" s="6"/>
       <c r="D967" s="6"/>
       <c r="E967" s="6"/>
-      <c r="F967" s="9"/>
+      <c r="F967" s="10"/>
       <c r="G967" s="6"/>
       <c r="H967" s="6"/>
       <c r="I967" s="6"/>
@@ -27539,7 +27542,7 @@
       <c r="C968" s="6"/>
       <c r="D968" s="6"/>
       <c r="E968" s="6"/>
-      <c r="F968" s="9"/>
+      <c r="F968" s="10"/>
       <c r="G968" s="6"/>
       <c r="H968" s="6"/>
       <c r="I968" s="6"/>
@@ -27567,7 +27570,7 @@
       <c r="C969" s="6"/>
       <c r="D969" s="6"/>
       <c r="E969" s="6"/>
-      <c r="F969" s="9"/>
+      <c r="F969" s="10"/>
       <c r="G969" s="6"/>
       <c r="H969" s="6"/>
       <c r="I969" s="6"/>
@@ -27595,7 +27598,7 @@
       <c r="C970" s="6"/>
       <c r="D970" s="6"/>
       <c r="E970" s="6"/>
-      <c r="F970" s="9"/>
+      <c r="F970" s="10"/>
       <c r="G970" s="6"/>
       <c r="H970" s="6"/>
       <c r="I970" s="6"/>
@@ -27623,7 +27626,7 @@
       <c r="C971" s="6"/>
       <c r="D971" s="6"/>
       <c r="E971" s="6"/>
-      <c r="F971" s="9"/>
+      <c r="F971" s="10"/>
       <c r="G971" s="6"/>
       <c r="H971" s="6"/>
       <c r="I971" s="6"/>
@@ -27651,7 +27654,7 @@
       <c r="C972" s="6"/>
       <c r="D972" s="6"/>
       <c r="E972" s="6"/>
-      <c r="F972" s="9"/>
+      <c r="F972" s="10"/>
       <c r="G972" s="6"/>
       <c r="H972" s="6"/>
       <c r="I972" s="6"/>
@@ -27679,7 +27682,7 @@
       <c r="C973" s="6"/>
       <c r="D973" s="6"/>
       <c r="E973" s="6"/>
-      <c r="F973" s="9"/>
+      <c r="F973" s="10"/>
       <c r="G973" s="6"/>
       <c r="H973" s="6"/>
       <c r="I973" s="6"/>
@@ -27707,7 +27710,7 @@
       <c r="C974" s="6"/>
       <c r="D974" s="6"/>
       <c r="E974" s="6"/>
-      <c r="F974" s="9"/>
+      <c r="F974" s="10"/>
       <c r="G974" s="6"/>
       <c r="H974" s="6"/>
       <c r="I974" s="6"/>
@@ -27735,7 +27738,7 @@
       <c r="C975" s="6"/>
       <c r="D975" s="6"/>
       <c r="E975" s="6"/>
-      <c r="F975" s="9"/>
+      <c r="F975" s="10"/>
       <c r="G975" s="6"/>
       <c r="H975" s="6"/>
       <c r="I975" s="6"/>
@@ -27763,7 +27766,7 @@
       <c r="C976" s="6"/>
       <c r="D976" s="6"/>
       <c r="E976" s="6"/>
-      <c r="F976" s="9"/>
+      <c r="F976" s="10"/>
       <c r="G976" s="6"/>
       <c r="H976" s="6"/>
       <c r="I976" s="6"/>
@@ -27791,7 +27794,7 @@
       <c r="C977" s="6"/>
       <c r="D977" s="6"/>
       <c r="E977" s="6"/>
-      <c r="F977" s="9"/>
+      <c r="F977" s="10"/>
       <c r="G977" s="6"/>
       <c r="H977" s="6"/>
       <c r="I977" s="6"/>
@@ -27819,7 +27822,7 @@
       <c r="C978" s="6"/>
       <c r="D978" s="6"/>
       <c r="E978" s="6"/>
-      <c r="F978" s="9"/>
+      <c r="F978" s="10"/>
       <c r="G978" s="6"/>
       <c r="H978" s="6"/>
       <c r="I978" s="6"/>
@@ -27847,7 +27850,7 @@
       <c r="C979" s="6"/>
       <c r="D979" s="6"/>
       <c r="E979" s="6"/>
-      <c r="F979" s="9"/>
+      <c r="F979" s="10"/>
       <c r="G979" s="6"/>
       <c r="H979" s="6"/>
       <c r="I979" s="6"/>
@@ -27875,7 +27878,7 @@
       <c r="C980" s="6"/>
       <c r="D980" s="6"/>
       <c r="E980" s="6"/>
-      <c r="F980" s="9"/>
+      <c r="F980" s="10"/>
       <c r="G980" s="6"/>
       <c r="H980" s="6"/>
       <c r="I980" s="6"/>
@@ -27903,7 +27906,7 @@
       <c r="C981" s="6"/>
       <c r="D981" s="6"/>
       <c r="E981" s="6"/>
-      <c r="F981" s="9"/>
+      <c r="F981" s="10"/>
       <c r="G981" s="6"/>
       <c r="H981" s="6"/>
       <c r="I981" s="6"/>
@@ -27931,7 +27934,7 @@
       <c r="C982" s="6"/>
       <c r="D982" s="6"/>
       <c r="E982" s="6"/>
-      <c r="F982" s="9"/>
+      <c r="F982" s="10"/>
       <c r="G982" s="6"/>
       <c r="H982" s="6"/>
       <c r="I982" s="6"/>
@@ -27959,7 +27962,7 @@
       <c r="C983" s="6"/>
       <c r="D983" s="6"/>
       <c r="E983" s="6"/>
-      <c r="F983" s="9"/>
+      <c r="F983" s="10"/>
       <c r="G983" s="6"/>
       <c r="H983" s="6"/>
       <c r="I983" s="6"/>
@@ -27987,7 +27990,7 @@
       <c r="C984" s="6"/>
       <c r="D984" s="6"/>
       <c r="E984" s="6"/>
-      <c r="F984" s="9"/>
+      <c r="F984" s="10"/>
       <c r="G984" s="6"/>
       <c r="H984" s="6"/>
       <c r="I984" s="6"/>
@@ -28015,7 +28018,7 @@
       <c r="C985" s="6"/>
       <c r="D985" s="6"/>
       <c r="E985" s="6"/>
-      <c r="F985" s="9"/>
+      <c r="F985" s="10"/>
       <c r="G985" s="6"/>
       <c r="H985" s="6"/>
       <c r="I985" s="6"/>
@@ -28043,7 +28046,7 @@
       <c r="C986" s="6"/>
       <c r="D986" s="6"/>
       <c r="E986" s="6"/>
-      <c r="F986" s="9"/>
+      <c r="F986" s="10"/>
       <c r="G986" s="6"/>
       <c r="H986" s="6"/>
       <c r="I986" s="6"/>
@@ -28071,7 +28074,7 @@
       <c r="C987" s="6"/>
       <c r="D987" s="6"/>
       <c r="E987" s="6"/>
-      <c r="F987" s="9"/>
+      <c r="F987" s="10"/>
       <c r="G987" s="6"/>
       <c r="H987" s="6"/>
       <c r="I987" s="6"/>
@@ -28099,7 +28102,7 @@
       <c r="C988" s="6"/>
       <c r="D988" s="6"/>
       <c r="E988" s="6"/>
-      <c r="F988" s="9"/>
+      <c r="F988" s="10"/>
       <c r="G988" s="6"/>
       <c r="H988" s="6"/>
       <c r="I988" s="6"/>
@@ -28127,7 +28130,7 @@
       <c r="C989" s="6"/>
       <c r="D989" s="6"/>
       <c r="E989" s="6"/>
-      <c r="F989" s="9"/>
+      <c r="F989" s="10"/>
       <c r="G989" s="6"/>
       <c r="H989" s="6"/>
       <c r="I989" s="6"/>
@@ -28155,7 +28158,7 @@
       <c r="C990" s="6"/>
       <c r="D990" s="6"/>
       <c r="E990" s="6"/>
-      <c r="F990" s="9"/>
+      <c r="F990" s="10"/>
       <c r="G990" s="6"/>
       <c r="H990" s="6"/>
       <c r="I990" s="6"/>
@@ -28183,7 +28186,7 @@
       <c r="C991" s="6"/>
       <c r="D991" s="6"/>
       <c r="E991" s="6"/>
-      <c r="F991" s="9"/>
+      <c r="F991" s="10"/>
       <c r="G991" s="6"/>
       <c r="H991" s="6"/>
       <c r="I991" s="6"/>
@@ -28211,7 +28214,7 @@
       <c r="C992" s="6"/>
       <c r="D992" s="6"/>
       <c r="E992" s="6"/>
-      <c r="F992" s="9"/>
+      <c r="F992" s="10"/>
       <c r="G992" s="6"/>
       <c r="H992" s="6"/>
       <c r="I992" s="6"/>
@@ -28239,7 +28242,7 @@
       <c r="C993" s="6"/>
       <c r="D993" s="6"/>
       <c r="E993" s="6"/>
-      <c r="F993" s="9"/>
+      <c r="F993" s="10"/>
       <c r="G993" s="6"/>
       <c r="H993" s="6"/>
       <c r="I993" s="6"/>
@@ -28267,7 +28270,7 @@
       <c r="C994" s="6"/>
       <c r="D994" s="6"/>
       <c r="E994" s="6"/>
-      <c r="F994" s="9"/>
+      <c r="F994" s="10"/>
       <c r="G994" s="6"/>
       <c r="H994" s="6"/>
       <c r="I994" s="6"/>
@@ -28295,7 +28298,7 @@
       <c r="C995" s="6"/>
       <c r="D995" s="6"/>
       <c r="E995" s="6"/>
-      <c r="F995" s="9"/>
+      <c r="F995" s="10"/>
       <c r="G995" s="6"/>
       <c r="H995" s="6"/>
       <c r="I995" s="6"/>
@@ -28323,7 +28326,7 @@
       <c r="C996" s="6"/>
       <c r="D996" s="6"/>
       <c r="E996" s="6"/>
-      <c r="F996" s="9"/>
+      <c r="F996" s="10"/>
       <c r="G996" s="6"/>
       <c r="H996" s="6"/>
       <c r="I996" s="6"/>
@@ -28351,7 +28354,7 @@
       <c r="C997" s="6"/>
       <c r="D997" s="6"/>
       <c r="E997" s="6"/>
-      <c r="F997" s="9"/>
+      <c r="F997" s="10"/>
       <c r="G997" s="6"/>
       <c r="H997" s="6"/>
       <c r="I997" s="6"/>
@@ -28379,7 +28382,7 @@
       <c r="C998" s="6"/>
       <c r="D998" s="6"/>
       <c r="E998" s="6"/>
-      <c r="F998" s="9"/>
+      <c r="F998" s="10"/>
       <c r="G998" s="6"/>
       <c r="H998" s="6"/>
       <c r="I998" s="6"/>
@@ -28407,7 +28410,7 @@
       <c r="C999" s="6"/>
       <c r="D999" s="6"/>
       <c r="E999" s="6"/>
-      <c r="F999" s="9"/>
+      <c r="F999" s="10"/>
       <c r="G999" s="6"/>
       <c r="H999" s="6"/>
       <c r="I999" s="6"/>
@@ -28435,7 +28438,7 @@
       <c r="C1000" s="6"/>
       <c r="D1000" s="6"/>
       <c r="E1000" s="6"/>
-      <c r="F1000" s="9"/>
+      <c r="F1000" s="10"/>
       <c r="G1000" s="6"/>
       <c r="H1000" s="6"/>
       <c r="I1000" s="6"/>

--- a/cypress/fixtures/CapJuntaDir.xlsx
+++ b/cypress/fixtures/CapJuntaDir.xlsx
@@ -475,8 +475,8 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""),3))) &amp; ""2 "" &amp; (RIGHT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 10)) "),"0102 1997 33101")</f>
-        <v>0102 1997 33101</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""),3))) &amp; ""2 "" &amp; (RIGHT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 10)) "),"0102 1997 33133")</f>
+        <v>0102 1997 33133</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>

--- a/cypress/fixtures/CapJuntaDir.xlsx
+++ b/cypress/fixtures/CapJuntaDir.xlsx
@@ -475,8 +475,8 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""),3))) &amp; ""2 "" &amp; (RIGHT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 10)) "),"0102 1997 33133")</f>
-        <v>0102 1997 33133</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""),3))) &amp; ""2 "" &amp; (RIGHT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 10)) "),"0102 1997 33141")</f>
+        <v>0102 1997 33141</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>

--- a/cypress/fixtures/CapJuntaDir.xlsx
+++ b/cypress/fixtures/CapJuntaDir.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>AuthPor</t>
   </si>
@@ -73,13 +73,13 @@
     <t>Plata</t>
   </si>
   <si>
-    <t>Juan</t>
+    <t>Ruiz</t>
   </si>
   <si>
-    <t>Carlos</t>
+    <t>Leonel</t>
   </si>
   <si>
-    <t>Pin</t>
+    <t>Andres</t>
   </si>
   <si>
     <t>Representante legal</t>
@@ -475,8 +475,8 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""),3))) &amp; ""2 "" &amp; (RIGHT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 10)) "),"0102 1997 33158")</f>
-        <v>0102 1997 33158</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("((LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""),3))) &amp; ""2 "" &amp; (RIGHT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 10)) "),"0102 1997 33226")</f>
+        <v>0102 1997 33226</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>
@@ -488,17 +488,15 @@
         <v>19</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="8" t="s">
         <v>22</v>
       </c>
+      <c r="L2" s="8"/>
       <c r="M2" s="9" t="s">
         <v>23</v>
       </c>
@@ -657,11 +655,11 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
       <c r="F8" s="10"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
